--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,13 +54,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Appointment</t>
+    <t>This StructureDefinition contains the maps for VistA APPOINTMENT (file 2.98) to FHIR Appointment</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3339" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,10 +383,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>The free/busy status of an appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/appointmentstatus|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VFAppointmentStatus</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -3030,11 +3027,9 @@
       <c r="X11" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="Y11" s="2"/>
+      <c r="Z11" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>35</v>
@@ -3067,36 +3062,36 @@
         <v>58</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AP11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AQ11" t="s" s="2">
+      <c r="AR11" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AR11" t="s" s="2">
-        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3119,13 +3114,13 @@
         <v>47</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3152,11 +3147,11 @@
         <v>35</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>35</v>
@@ -3174,7 +3169,7 @@
         <v>35</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -3192,7 +3187,7 @@
         <v>35</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>35</v>
@@ -3215,10 +3210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3241,13 +3236,13 @@
         <v>35</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3298,7 +3293,7 @@
         <v>35</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
@@ -3316,7 +3311,7 @@
         <v>35</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>35</v>
@@ -3339,10 +3334,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3371,7 +3366,7 @@
         <v>93</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>95</v>
@@ -3412,19 +3407,19 @@
         <v>35</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE14" t="s" s="2">
+      <c r="AF14" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
@@ -3442,7 +3437,7 @@
         <v>35</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>35</v>
@@ -3465,10 +3460,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3491,19 +3486,19 @@
         <v>47</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>35</v>
@@ -3552,7 +3547,7 @@
         <v>35</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
@@ -3570,16 +3565,16 @@
         <v>35</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>35</v>
@@ -3593,10 +3588,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3619,13 +3614,13 @@
         <v>35</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3676,7 +3671,7 @@
         <v>35</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
@@ -3694,7 +3689,7 @@
         <v>35</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>35</v>
@@ -3717,10 +3712,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3749,7 +3744,7 @@
         <v>93</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>95</v>
@@ -3790,19 +3785,19 @@
         <v>35</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC17" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC17" t="s" s="2">
+      <c r="AD17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD17" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE17" t="s" s="2">
+      <c r="AF17" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
@@ -3820,7 +3815,7 @@
         <v>35</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>35</v>
@@ -3843,10 +3838,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3872,16 +3867,16 @@
         <v>60</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>35</v>
@@ -3930,7 +3925,7 @@
         <v>35</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
@@ -3948,16 +3943,16 @@
         <v>35</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>35</v>
@@ -3971,10 +3966,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3997,16 +3992,16 @@
         <v>47</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4056,7 +4051,7 @@
         <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -4074,16 +4069,16 @@
         <v>35</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>35</v>
@@ -4097,10 +4092,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4126,14 +4121,14 @@
         <v>66</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>35</v>
@@ -4182,7 +4177,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -4200,22 +4195,22 @@
         <v>35</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>35</v>
@@ -4223,10 +4218,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4249,17 +4244,17 @@
         <v>47</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>35</v>
@@ -4308,7 +4303,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -4326,16 +4321,16 @@
         <v>35</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>35</v>
@@ -4349,10 +4344,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4375,19 +4370,19 @@
         <v>47</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
@@ -4436,7 +4431,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4454,16 +4449,16 @@
         <v>35</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>35</v>
@@ -4477,10 +4472,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4503,19 +4498,19 @@
         <v>47</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
@@ -4564,7 +4559,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4582,16 +4577,16 @@
         <v>35</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>35</v>
@@ -4605,10 +4600,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4631,13 +4626,13 @@
         <v>47</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4664,11 +4659,11 @@
         <v>35</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>35</v>
@@ -4686,7 +4681,7 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4704,10 +4699,10 @@
         <v>35</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>35</v>
@@ -4727,10 +4722,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4753,13 +4748,13 @@
         <v>35</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4810,7 +4805,7 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
@@ -4828,7 +4823,7 @@
         <v>35</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>35</v>
@@ -4851,10 +4846,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4883,7 +4878,7 @@
         <v>93</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>95</v>
@@ -4924,19 +4919,19 @@
         <v>35</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC26" t="s" s="2">
+      <c r="AD26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE26" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE26" t="s" s="2">
+      <c r="AF26" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -4954,7 +4949,7 @@
         <v>35</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>35</v>
@@ -4977,10 +4972,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5003,19 +4998,19 @@
         <v>47</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>35</v>
@@ -5064,7 +5059,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -5082,16 +5077,16 @@
         <v>35</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>35</v>
@@ -5105,10 +5100,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5131,13 +5126,13 @@
         <v>35</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5188,7 +5183,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -5206,7 +5201,7 @@
         <v>35</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>35</v>
@@ -5229,10 +5224,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5261,7 +5256,7 @@
         <v>93</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>95</v>
@@ -5302,19 +5297,19 @@
         <v>35</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -5332,7 +5327,7 @@
         <v>35</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>35</v>
@@ -5355,10 +5350,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5384,16 +5379,16 @@
         <v>60</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>35</v>
@@ -5442,7 +5437,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5460,16 +5455,16 @@
         <v>35</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>35</v>
@@ -5483,10 +5478,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5509,16 +5504,16 @@
         <v>47</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5568,7 +5563,7 @@
         <v>35</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5586,16 +5581,16 @@
         <v>35</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>35</v>
@@ -5609,10 +5604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5638,14 +5633,14 @@
         <v>66</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>35</v>
@@ -5694,7 +5689,7 @@
         <v>35</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -5712,33 +5707,33 @@
         <v>35</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AP32" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AQ32" t="s" s="2">
+      <c r="AR32" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5761,17 +5756,17 @@
         <v>47</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>35</v>
@@ -5820,7 +5815,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -5838,16 +5833,16 @@
         <v>35</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>35</v>
@@ -5861,10 +5856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5887,19 +5882,19 @@
         <v>47</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>35</v>
@@ -5948,7 +5943,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5966,16 +5961,16 @@
         <v>35</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>35</v>
@@ -5989,10 +5984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6015,19 +6010,19 @@
         <v>47</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>35</v>
@@ -6076,7 +6071,7 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -6094,16 +6089,16 @@
         <v>35</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>35</v>
@@ -6117,10 +6112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6143,16 +6138,16 @@
         <v>47</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6178,11 +6173,11 @@
         <v>35</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>35</v>
@@ -6200,7 +6195,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -6215,10 +6210,10 @@
         <v>58</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>35</v>
@@ -6241,10 +6236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6267,13 +6262,13 @@
         <v>35</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6324,7 +6319,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -6342,7 +6337,7 @@
         <v>35</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>35</v>
@@ -6365,10 +6360,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6397,7 +6392,7 @@
         <v>93</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>95</v>
@@ -6438,19 +6433,19 @@
         <v>35</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC38" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC38" t="s" s="2">
+      <c r="AD38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE38" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD38" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE38" t="s" s="2">
+      <c r="AF38" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6468,7 +6463,7 @@
         <v>35</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>35</v>
@@ -6491,10 +6486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6517,19 +6512,19 @@
         <v>47</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>35</v>
@@ -6578,7 +6573,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -6596,16 +6591,16 @@
         <v>35</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>35</v>
@@ -6619,10 +6614,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6645,13 +6640,13 @@
         <v>35</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6702,7 +6697,7 @@
         <v>35</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -6720,7 +6715,7 @@
         <v>35</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>35</v>
@@ -6743,10 +6738,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6775,7 +6770,7 @@
         <v>93</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>95</v>
@@ -6816,19 +6811,19 @@
         <v>35</v>
       </c>
       <c r="AB41" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC41" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC41" t="s" s="2">
+      <c r="AD41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE41" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE41" t="s" s="2">
+      <c r="AF41" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -6846,7 +6841,7 @@
         <v>35</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>35</v>
@@ -6869,10 +6864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6898,16 +6893,16 @@
         <v>60</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>35</v>
@@ -6956,7 +6951,7 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6974,16 +6969,16 @@
         <v>35</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>35</v>
@@ -6997,10 +6992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7023,16 +7018,16 @@
         <v>47</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7082,7 +7077,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -7100,16 +7095,16 @@
         <v>35</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>35</v>
@@ -7123,10 +7118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7152,14 +7147,14 @@
         <v>66</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>35</v>
@@ -7208,7 +7203,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -7226,33 +7221,33 @@
         <v>35</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AP44" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AQ44" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>239</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7275,17 +7270,17 @@
         <v>47</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>35</v>
@@ -7334,7 +7329,7 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -7352,16 +7347,16 @@
         <v>35</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>35</v>
@@ -7375,10 +7370,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7401,19 +7396,19 @@
         <v>47</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>35</v>
@@ -7462,7 +7457,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -7480,16 +7475,16 @@
         <v>35</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>35</v>
@@ -7503,10 +7498,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7529,19 +7524,19 @@
         <v>47</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>35</v>
@@ -7590,7 +7585,7 @@
         <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -7608,16 +7603,16 @@
         <v>35</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>35</v>
@@ -7631,10 +7626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7657,13 +7652,13 @@
         <v>47</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7694,7 +7689,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>35</v>
@@ -7712,7 +7707,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7730,22 +7725,22 @@
         <v>35</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>35</v>
@@ -7753,10 +7748,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7779,13 +7774,13 @@
         <v>47</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7816,7 +7811,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>35</v>
@@ -7834,7 +7829,7 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7852,16 +7847,16 @@
         <v>35</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>35</v>
@@ -7875,10 +7870,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7901,13 +7896,13 @@
         <v>35</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7958,7 +7953,7 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7976,7 +7971,7 @@
         <v>35</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>35</v>
@@ -7999,10 +7994,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8031,7 +8026,7 @@
         <v>93</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>95</v>
@@ -8072,19 +8067,19 @@
         <v>35</v>
       </c>
       <c r="AB51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC51" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC51" t="s" s="2">
+      <c r="AD51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE51" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD51" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE51" t="s" s="2">
+      <c r="AF51" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -8102,7 +8097,7 @@
         <v>35</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>35</v>
@@ -8125,10 +8120,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8151,19 +8146,19 @@
         <v>47</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>35</v>
@@ -8212,7 +8207,7 @@
         <v>35</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -8230,16 +8225,16 @@
         <v>35</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>35</v>
@@ -8253,10 +8248,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8279,13 +8274,13 @@
         <v>35</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8336,7 +8331,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -8354,7 +8349,7 @@
         <v>35</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>35</v>
@@ -8377,10 +8372,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8409,7 +8404,7 @@
         <v>93</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>95</v>
@@ -8450,19 +8445,19 @@
         <v>35</v>
       </c>
       <c r="AB54" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AC54" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AC54" t="s" s="2">
+      <c r="AD54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE54" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AD54" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE54" t="s" s="2">
+      <c r="AF54" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8480,7 +8475,7 @@
         <v>35</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>35</v>
@@ -8503,10 +8498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8532,16 +8527,16 @@
         <v>60</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -8590,7 +8585,7 @@
         <v>35</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -8608,16 +8603,16 @@
         <v>35</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>35</v>
@@ -8631,10 +8626,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8657,16 +8652,16 @@
         <v>47</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8716,7 +8711,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -8734,16 +8729,16 @@
         <v>35</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>35</v>
@@ -8757,10 +8752,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8786,14 +8781,14 @@
         <v>66</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>35</v>
@@ -8842,7 +8837,7 @@
         <v>35</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
@@ -8860,33 +8855,33 @@
         <v>35</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AP57" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AQ57" t="s" s="2">
+      <c r="AR57" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8909,17 +8904,17 @@
         <v>47</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>35</v>
@@ -8968,7 +8963,7 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -8986,16 +8981,16 @@
         <v>35</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>35</v>
@@ -9009,10 +9004,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9035,19 +9030,19 @@
         <v>47</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>35</v>
@@ -9096,7 +9091,7 @@
         <v>35</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
@@ -9114,16 +9109,16 @@
         <v>35</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>35</v>
@@ -9137,10 +9132,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9163,19 +9158,19 @@
         <v>47</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>35</v>
@@ -9224,7 +9219,7 @@
         <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
@@ -9242,16 +9237,16 @@
         <v>35</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>35</v>
@@ -9265,10 +9260,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9291,13 +9286,13 @@
         <v>47</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9327,11 +9322,11 @@
         <v>70</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>35</v>
       </c>
@@ -9348,7 +9343,7 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -9363,25 +9358,25 @@
         <v>58</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>35</v>
@@ -9389,10 +9384,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9415,13 +9410,13 @@
         <v>35</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9472,7 +9467,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -9487,25 +9482,25 @@
         <v>58</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>35</v>
@@ -9513,10 +9508,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9539,16 +9534,16 @@
         <v>35</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9598,7 +9593,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -9613,19 +9608,19 @@
         <v>58</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>35</v>
@@ -9639,10 +9634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9665,13 +9660,13 @@
         <v>35</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9722,7 +9717,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -9740,16 +9735,16 @@
         <v>35</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>35</v>
@@ -9763,10 +9758,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9789,13 +9784,13 @@
         <v>35</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9846,7 +9841,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -9861,16 +9856,16 @@
         <v>58</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>35</v>
@@ -9887,10 +9882,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9913,13 +9908,13 @@
         <v>47</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9970,7 +9965,7 @@
         <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -9985,25 +9980,25 @@
         <v>58</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AO66" t="s" s="2">
+      <c r="AP66" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AP66" t="s" s="2">
+      <c r="AQ66" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>35</v>
@@ -10011,10 +10006,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10037,13 +10032,13 @@
         <v>47</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10094,7 +10089,7 @@
         <v>35</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -10109,25 +10104,25 @@
         <v>58</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AO67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AP67" t="s" s="2">
+      <c r="AQ67" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>35</v>
@@ -10135,10 +10130,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10161,13 +10156,13 @@
         <v>35</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10218,7 +10213,7 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
@@ -10233,25 +10228,25 @@
         <v>58</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AN68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>35</v>
@@ -10259,10 +10254,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10285,13 +10280,13 @@
         <v>35</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10342,7 +10337,7 @@
         <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -10360,7 +10355,7 @@
         <v>35</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>35</v>
@@ -10383,10 +10378,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10409,16 +10404,16 @@
         <v>35</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10468,7 +10463,7 @@
         <v>35</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -10483,25 +10478,25 @@
         <v>58</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AM70" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN70" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>35</v>
@@ -10509,10 +10504,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10535,16 +10530,16 @@
         <v>35</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10594,7 +10589,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -10609,25 +10604,25 @@
         <v>58</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>35</v>
@@ -10635,10 +10630,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10661,13 +10656,13 @@
         <v>35</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10718,7 +10713,7 @@
         <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -10736,16 +10731,16 @@
         <v>35</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>35</v>
@@ -10759,14 +10754,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10785,13 +10780,13 @@
         <v>35</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10842,7 +10837,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -10857,10 +10852,10 @@
         <v>58</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>35</v>
@@ -10883,10 +10878,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10909,13 +10904,13 @@
         <v>35</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10966,7 +10961,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>46</v>
@@ -10978,22 +10973,22 @@
         <v>35</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AK74" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AK74" t="s" s="2">
+      <c r="AL74" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>35</v>
@@ -11007,10 +11002,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11033,13 +11028,13 @@
         <v>35</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11090,7 +11085,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -11108,7 +11103,7 @@
         <v>35</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>35</v>
@@ -11131,10 +11126,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11163,7 +11158,7 @@
         <v>93</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>95</v>
@@ -11216,7 +11211,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -11234,7 +11229,7 @@
         <v>35</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>35</v>
@@ -11257,14 +11252,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11286,10 +11281,10 @@
         <v>92</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>95</v>
@@ -11344,7 +11339,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -11385,10 +11380,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11411,16 +11406,16 @@
         <v>47</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11446,14 +11441,14 @@
         <v>35</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>35</v>
       </c>
@@ -11470,7 +11465,7 @@
         <v>35</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -11488,16 +11483,16 @@
         <v>35</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>35</v>
@@ -11511,10 +11506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11537,13 +11532,13 @@
         <v>47</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11594,7 +11589,7 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -11612,33 +11607,33 @@
         <v>35</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AP79" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
+      <c r="AR79" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11664,10 +11659,10 @@
         <v>66</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11697,11 +11692,11 @@
         <v>116</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>35</v>
       </c>
@@ -11718,7 +11713,7 @@
         <v>35</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -11736,10 +11731,10 @@
         <v>35</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>35</v>
@@ -11759,10 +11754,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11788,10 +11783,10 @@
         <v>66</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11821,11 +11816,11 @@
         <v>116</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>35</v>
       </c>
@@ -11842,7 +11837,7 @@
         <v>35</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>46</v>
@@ -11860,16 +11855,16 @@
         <v>35</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>35</v>
@@ -11883,10 +11878,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11909,13 +11904,13 @@
         <v>35</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11966,7 +11961,7 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -11984,7 +11979,7 @@
         <v>35</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>35</v>
@@ -12007,10 +12002,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12033,16 +12028,16 @@
         <v>35</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12092,7 +12087,7 @@
         <v>35</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
@@ -12107,19 +12102,19 @@
         <v>58</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>35</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,10 +243,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Mapping: Virtual Patient Record (VPR)</t>
@@ -533,10 +533,10 @@
     <t>SCH-25</t>
   </si>
   <si>
+    <t>748: transform using "waitlist" on SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
+  </si>
+  <si>
     <t>Appt.Appointment.AppointmentStatus</t>
-  </si>
-  <si>
-    <t>748: transform using "waitlist" on SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
   </si>
   <si>
     <t>appointment.apptStatus</t>
@@ -699,10 +699,10 @@
     <t>C*E.1</t>
   </si>
   <si>
+    <t>735: source value from APPOINTMENT - CANCELLATION REASON (#2.98-16)</t>
+  </si>
+  <si>
     <t>Appt.Appointment.CancellationReasonIEN</t>
-  </si>
-  <si>
-    <t>735: source value from APPOINTMENT - CANCELLATION REASON (#2.98-16)</t>
   </si>
   <si>
     <t>Appointment.cancelationReason.coding.display</t>
@@ -820,12 +820,12 @@
     <t>Appointment.serviceCategory.coding.code</t>
   </si>
   <si>
+    <t>749: source value from SD WAIT LIST - APPT STOP CODE (#409.3-13.4)</t>
+  </si>
+  <si>
     <t>Appt.Appointment.LocationIEN</t>
   </si>
   <si>
-    <t>749: source value from SD WAIT LIST - APPT STOP CODE (#409.3-13.4)</t>
-  </si>
-  <si>
     <t>appointment.service</t>
   </si>
   <si>
@@ -961,10 +961,10 @@
     <t>Appointment.appointmentType.coding.code</t>
   </si>
   <si>
+    <t>740: source value from APPOINTMENT - APPOINTMENT TYPE (#2.98-9.5)</t>
+  </si>
+  <si>
     <t>Appt.Appointment.AppointmentTypeIEN</t>
-  </si>
-  <si>
-    <t>740: source value from APPOINTMENT - APPOINTMENT TYPE (#2.98-9.5)</t>
   </si>
   <si>
     <t>appointment.type</t>
@@ -1129,12 +1129,12 @@
     <t>ARQ-11.1, SCH-11.4 / TQ1-7</t>
   </si>
   <si>
+    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (#409.3-22)</t>
+  </si>
+  <si>
     <t>Appt.WaitList.AppointmentDesiredDate</t>
   </si>
   <si>
-    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (#409.3-22)</t>
-  </si>
-  <si>
     <t>Appointment.end</t>
   </si>
   <si>
@@ -1156,10 +1156,10 @@
     <t>SCH-11.5 / TQ1-8/ calculated based on the start and the duration which is in ARQ-9</t>
   </si>
   <si>
+    <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (#2.98-21 &gt; 409.68-.07)</t>
+  </si>
+  <si>
     <t>Appt.Appointment.VisitIEN</t>
-  </si>
-  <si>
-    <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (#2.98-21 &gt; 409.68-.07)</t>
   </si>
   <si>
     <t>Appointment.minutesDuration</t>
@@ -1181,13 +1181,13 @@
     <t>DURATION (e.g. PT15M)</t>
   </si>
   <si>
+    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
+  </si>
+  <si>
     <t>Appt.Appointment.LengthOfAppointment
 Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
-    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
-  </si>
-  <si>
     <t>Appointment.slot</t>
   </si>
   <si>
@@ -1229,10 +1229,10 @@
     <t>CREATED</t>
   </si>
   <si>
+    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (#409.3-1)</t>
+  </si>
+  <si>
     <t>Appt.WaitList.OriginatingDate</t>
-  </si>
-  <si>
-    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (#409.3-1)</t>
   </si>
   <si>
     <t>Appointment.comment</t>
@@ -1258,10 +1258,10 @@
     <t>DESCRIPTION (for internal use)</t>
   </si>
   <si>
+    <t>752: source value from SD WAIT LIST - COMMENTS (#409.3-25)</t>
+  </si>
+  <si>
     <t>Appt.WaitList.WaitListComments</t>
-  </si>
-  <si>
-    <t>752: source value from SD WAIT LIST - COMMENTS (#409.3-25)</t>
   </si>
   <si>
     <t>Appointment.patientInstruction</t>
@@ -1834,8 +1834,8 @@
     <col min="39" max="39" width="155.20703125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="77.55859375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="46.01171875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="146.90625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="146.90625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="46.01171875" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -7500,10 +7500,10 @@
         <v>220</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>282</v>
@@ -8004,10 +8004,10 @@
         <v>79</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>79</v>
@@ -9640,10 +9640,10 @@
         <v>321</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>79</v>
@@ -9764,10 +9764,10 @@
         <v>79</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>79</v>
@@ -11886,10 +11886,10 @@
         <v>448</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>261</v>
+        <v>449</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>449</v>
+        <v>262</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>450</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -539,7 +539,8 @@
     <t>Appt.Appointment.AppointmentStatus</t>
   </si>
   <si>
-    <t>appointment.apptStatus</t>
+    <t>appointment.apptStatus
+appointment.patientClass</t>
   </si>
   <si>
     <t>Appointment.cancelationReason</t>
@@ -1135,6 +1136,9 @@
     <t>Appt.WaitList.AppointmentDesiredDate</t>
   </si>
   <si>
+    <t>appointment.dateTime</t>
+  </si>
+  <si>
     <t>Appointment.end</t>
   </si>
   <si>
@@ -1179,13 +1183,6 @@
   </si>
   <si>
     <t>DURATION (e.g. PT15M)</t>
-  </si>
-  <si>
-    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.LengthOfAppointment
-Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
     <t>Appointment.slot</t>
@@ -1385,7 +1382,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device|HealthcareService|Location)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -1408,11 +1405,6 @@
   </si>
   <si>
     <t>754: reference from SD WAIT LIST - APPT CLINIC (#409.3-13.2)</t>
-  </si>
-  <si>
-    <t>appointment.clinStop
-Appointment.facility
-appointment.location</t>
   </si>
   <si>
     <t>Appointment.participant.required</t>
@@ -1804,7 +1796,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="91.39453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.65625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1835,7 +1827,7 @@
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="77.55859375" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="146.90625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="46.01171875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -10268,15 +10260,15 @@
         <v>363</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10302,10 +10294,10 @@
         <v>354</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10356,7 +10348,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10374,22 +10366,22 @@
         <v>357</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>79</v>
@@ -10397,10 +10389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10423,13 +10415,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10480,7 +10472,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10498,10 +10490,10 @@
         <v>357</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10510,10 +10502,10 @@
         <v>79</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>79</v>
@@ -10521,10 +10513,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10547,13 +10539,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10604,7 +10596,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10622,7 +10614,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10645,10 +10637,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10671,16 +10663,16 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10730,7 +10722,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10745,25 +10737,25 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>79</v>
@@ -10771,10 +10763,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10800,13 +10792,13 @@
         <v>178</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10856,7 +10848,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10871,13 +10863,13 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10886,10 +10878,10 @@
         <v>344</v>
       </c>
       <c r="AP72" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>79</v>
@@ -10897,10 +10889,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10926,10 +10918,10 @@
         <v>178</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10980,7 +10972,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10998,10 +10990,10 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
@@ -11021,14 +11013,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11047,13 +11039,13 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11104,7 +11096,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11119,10 +11111,10 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -11145,10 +11137,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11171,13 +11163,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11228,7 +11220,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11240,22 +11232,22 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AK75" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AK75" t="s" s="2">
+      <c r="AL75" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11269,10 +11261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11393,10 +11385,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11519,14 +11511,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11548,10 +11540,10 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>139</v>
@@ -11606,7 +11598,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11647,10 +11639,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11676,13 +11668,13 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11708,14 +11700,14 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Y79" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Y79" t="s" s="2">
+      <c r="Z79" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="Z79" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
       </c>
@@ -11732,7 +11724,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11750,7 +11742,7 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>176</v>
@@ -11759,7 +11751,7 @@
         <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
@@ -11773,10 +11765,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11799,13 +11791,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11856,7 +11848,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11874,33 +11866,33 @@
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AO80" t="s" s="2">
+      <c r="AP80" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>262</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11926,10 +11918,10 @@
         <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11959,10 +11951,10 @@
         <v>160</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11980,7 +11972,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11998,10 +11990,10 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
@@ -12021,10 +12013,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12050,10 +12042,10 @@
         <v>110</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12083,10 +12075,10 @@
         <v>160</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -12104,7 +12096,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12122,16 +12114,16 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>79</v>
@@ -12145,10 +12137,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12171,13 +12163,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12228,7 +12220,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12269,10 +12261,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12295,16 +12287,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12354,7 +12346,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12372,7 +12364,7 @@
         <v>357</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
@@ -12381,7 +12373,7 @@
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA APPOINTMENT (file 2.98) to FHIR Appointment</t>
+    <t>This StructureDefinition contains the maps for VistA file APPOINTMENT (#2.98) to Appointment</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$84</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="476">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1183,6 +1186,13 @@
   </si>
   <si>
     <t>DURATION (e.g. PT15M)</t>
+  </si>
+  <si>
+    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
+  </si>
+  <si>
+    <t>Appt.Appointment.LengthOfAppointment
+Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
     <t>Appointment.slot</t>
@@ -1610,6 +1620,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1827,7 +1852,7 @@
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="77.55859375" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="146.90625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="46.01171875" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1965,7 +1990,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>7</v>
       </c>
@@ -2089,7 +2114,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2215,7 +2240,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2339,7 +2364,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2465,7 +2490,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2591,7 +2616,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2717,7 +2742,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2843,7 +2868,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2969,7 +2994,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3097,7 +3122,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -3221,7 +3246,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -3240,7 +3265,7 @@
         <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>91</v>
@@ -3345,7 +3370,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>170</v>
       </c>
@@ -3467,7 +3492,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -3591,7 +3616,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>182</v>
       </c>
@@ -3717,7 +3742,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>188</v>
       </c>
@@ -3845,7 +3870,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>197</v>
       </c>
@@ -3969,7 +3994,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>198</v>
       </c>
@@ -4095,7 +4120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>199</v>
       </c>
@@ -4223,7 +4248,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -4349,7 +4374,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>214</v>
       </c>
@@ -4368,7 +4393,7 @@
         <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>79</v>
@@ -4475,7 +4500,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>223</v>
       </c>
@@ -4601,7 +4626,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>230</v>
       </c>
@@ -4729,7 +4754,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>239</v>
       </c>
@@ -4857,7 +4882,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>247</v>
       </c>
@@ -4979,7 +5004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>253</v>
       </c>
@@ -5103,7 +5128,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>254</v>
       </c>
@@ -5229,7 +5254,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>255</v>
       </c>
@@ -5357,7 +5382,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>256</v>
       </c>
@@ -5481,7 +5506,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>257</v>
       </c>
@@ -5607,7 +5632,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>258</v>
       </c>
@@ -5735,7 +5760,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>259</v>
       </c>
@@ -5861,7 +5886,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>260</v>
       </c>
@@ -5880,7 +5905,7 @@
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
@@ -5987,7 +6012,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>264</v>
       </c>
@@ -6113,7 +6138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>265</v>
       </c>
@@ -6241,7 +6266,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>266</v>
       </c>
@@ -6369,7 +6394,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>267</v>
       </c>
@@ -6493,7 +6518,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>273</v>
       </c>
@@ -6617,7 +6642,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>274</v>
       </c>
@@ -6743,7 +6768,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>275</v>
       </c>
@@ -6871,7 +6896,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>276</v>
       </c>
@@ -6995,7 +7020,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>277</v>
       </c>
@@ -7121,7 +7146,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>278</v>
       </c>
@@ -7249,7 +7274,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>279</v>
       </c>
@@ -7375,7 +7400,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>280</v>
       </c>
@@ -7394,7 +7419,7 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7501,7 +7526,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>283</v>
       </c>
@@ -7627,7 +7652,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>284</v>
       </c>
@@ -7755,7 +7780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>285</v>
       </c>
@@ -7883,7 +7908,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>286</v>
       </c>
@@ -7902,7 +7927,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
@@ -8005,7 +8030,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>293</v>
       </c>
@@ -8127,7 +8152,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>300</v>
       </c>
@@ -8251,7 +8276,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>301</v>
       </c>
@@ -8377,7 +8402,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>302</v>
       </c>
@@ -8505,7 +8530,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>303</v>
       </c>
@@ -8629,7 +8654,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>304</v>
       </c>
@@ -8755,7 +8780,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>305</v>
       </c>
@@ -8883,7 +8908,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>306</v>
       </c>
@@ -9009,7 +9034,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>307</v>
       </c>
@@ -9028,7 +9053,7 @@
         <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>79</v>
@@ -9135,7 +9160,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>311</v>
       </c>
@@ -9261,7 +9286,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>312</v>
       </c>
@@ -9389,7 +9414,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>313</v>
       </c>
@@ -9517,7 +9542,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>314</v>
       </c>
@@ -9536,7 +9561,7 @@
         <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
@@ -9641,7 +9666,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>323</v>
       </c>
@@ -9660,7 +9685,7 @@
         <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
@@ -9765,7 +9790,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>330</v>
       </c>
@@ -9891,7 +9916,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>339</v>
       </c>
@@ -10015,7 +10040,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>345</v>
       </c>
@@ -10139,7 +10164,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>353</v>
       </c>
@@ -10158,7 +10183,7 @@
         <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>79</v>
@@ -10263,7 +10288,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>365</v>
       </c>
@@ -10282,7 +10307,7 @@
         <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>79</v>
@@ -10387,7 +10412,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>374</v>
       </c>
@@ -10406,7 +10431,7 @@
         <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>79</v>
@@ -10502,21 +10527,21 @@
         <v>79</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10539,13 +10564,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10596,7 +10621,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10614,7 +10639,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10635,12 +10660,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10654,7 +10679,7 @@
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>79</v>
@@ -10663,16 +10688,16 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10722,7 +10747,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10737,13 +10762,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10752,21 +10777,21 @@
         <v>79</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10780,7 +10805,7 @@
         <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>79</v>
@@ -10792,13 +10817,13 @@
         <v>178</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10848,7 +10873,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10863,13 +10888,13 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10878,21 +10903,21 @@
         <v>344</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10918,10 +10943,10 @@
         <v>178</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10972,7 +10997,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10990,10 +11015,10 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
@@ -11011,16 +11036,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11039,13 +11064,13 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11096,7 +11121,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11111,10 +11136,10 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -11135,12 +11160,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11163,13 +11188,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11220,7 +11245,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11232,22 +11257,22 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11259,12 +11284,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11383,12 +11408,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11509,16 +11534,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11540,10 +11565,10 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>139</v>
@@ -11598,7 +11623,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11637,12 +11662,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11668,13 +11693,13 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11700,13 +11725,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11724,7 +11749,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11742,7 +11767,7 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>176</v>
@@ -11751,7 +11776,7 @@
         <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
@@ -11763,12 +11788,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11782,7 +11807,7 @@
         <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>79</v>
@@ -11791,13 +11816,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11848,7 +11873,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11866,19 +11891,19 @@
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>262</v>
@@ -11887,12 +11912,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11918,10 +11943,10 @@
         <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11951,10 +11976,10 @@
         <v>160</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11972,7 +11997,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11990,10 +12015,10 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
@@ -12011,12 +12036,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12042,10 +12067,10 @@
         <v>110</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12075,10 +12100,10 @@
         <v>160</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -12096,7 +12121,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12114,16 +12139,16 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>79</v>
@@ -12135,12 +12160,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12163,13 +12188,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12220,7 +12245,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12259,12 +12284,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12287,16 +12312,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12346,7 +12371,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12364,7 +12389,7 @@
         <v>357</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
@@ -12373,7 +12398,7 @@
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -12386,6 +12411,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AR84">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI83">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7927,7 +7927,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
@@ -9561,7 +9561,7 @@
         <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
@@ -9685,7 +9685,7 @@
         <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,7 +536,7 @@
     <t>SCH-25</t>
   </si>
   <si>
-    <t>748: transform using "waitlist" on SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
+    <t>748: transform using #waitlist on SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
   </si>
   <si>
     <t>Appt.Appointment.AppointmentStatus</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -827,64 +827,68 @@
     <t>749: source value from SD WAIT LIST - APPT STOP CODE (#409.3-13.4)</t>
   </si>
   <si>
+    <t>Appt.Appointment.LocationIEN
+Dim.Location.MedicalService</t>
+  </si>
+  <si>
+    <t>appointment.service</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.text</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType</t>
+  </si>
+  <si>
+    <t>The specific service that is to be performed during this appointment</t>
+  </si>
+  <si>
+    <t>The specific service that is to be performed during this appointment.</t>
+  </si>
+  <si>
+    <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+  </si>
+  <si>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.id</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.extension</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.code</t>
+  </si>
+  <si>
+    <t>738: source value from APPOINTMENT - CLINIC &gt; HOSPITAL LOCATION - CREDIT STOP CODE (#2.98-.01 &gt; 44-2503)</t>
+  </si>
+  <si>
     <t>Appt.Appointment.LocationIEN</t>
-  </si>
-  <si>
-    <t>appointment.service</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.text</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType</t>
-  </si>
-  <si>
-    <t>The specific service that is to be performed during this appointment</t>
-  </si>
-  <si>
-    <t>The specific service that is to be performed during this appointment.</t>
-  </si>
-  <si>
-    <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
-  </si>
-  <si>
-    <t>Request.code</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.code</t>
-  </si>
-  <si>
-    <t>738: source value from APPOINTMENT - CLINIC &gt; HOSPITAL LOCATION - CREDIT STOP CODE (#2.98-.01 &gt; 44-2503)</t>
   </si>
   <si>
     <t>appointment.clinStop</t>
@@ -1166,7 +1170,8 @@
     <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (#2.98-21 &gt; 409.68-.07)</t>
   </si>
   <si>
-    <t>Appt.Appointment.VisitIEN</t>
+    <t>Appt.Appointment.VisitIEN
+Outpat.Visit.COProcessCompleteDateTime,Outpat.Workload.COProcessCompleteDateTime</t>
   </si>
   <si>
     <t>Appointment.minutesDuration</t>
@@ -1191,8 +1196,7 @@
     <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
   </si>
   <si>
-    <t>Appt.Appointment.LengthOfAppointment
-Appt.AppointmentMultiple.LengthOfAppointment</t>
+    <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
     <t>Appointment.slot</t>
@@ -1852,7 +1856,7 @@
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="77.55859375" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="146.90625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="46.01171875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="84.28125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -7520,18 +7524,18 @@
         <v>281</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7654,10 +7658,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7782,10 +7786,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7910,10 +7914,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7939,10 +7943,10 @@
         <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7973,7 +7977,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7991,7 +7995,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8009,19 +8013,19 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>79</v>
@@ -8032,10 +8036,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8061,10 +8065,10 @@
         <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8095,7 +8099,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8113,7 +8117,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8131,16 +8135,16 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>79</v>
@@ -8154,10 +8158,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8278,10 +8282,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8404,10 +8408,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8532,10 +8536,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8656,10 +8660,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8782,10 +8786,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8910,10 +8914,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9036,10 +9040,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9151,21 +9155,21 @@
         <v>220</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9288,10 +9292,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9416,10 +9420,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9544,10 +9548,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9573,10 +9577,10 @@
         <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9606,10 +9610,10 @@
         <v>114</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9627,7 +9631,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9642,10 +9646,10 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9654,10 +9658,10 @@
         <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>79</v>
@@ -9668,10 +9672,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9694,13 +9698,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9751,7 +9755,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9766,10 +9770,10 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9781,7 +9785,7 @@
         <v>79</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>79</v>
@@ -9792,10 +9796,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9818,16 +9822,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9877,7 +9881,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9892,19 +9896,19 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -9918,10 +9922,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9947,10 +9951,10 @@
         <v>178</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10001,7 +10005,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10019,16 +10023,16 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10042,10 +10046,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10068,13 +10072,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10125,7 +10129,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10140,16 +10144,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10166,10 +10170,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10192,13 +10196,13 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10249,7 +10253,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10264,36 +10268,36 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10316,13 +10320,13 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10373,7 +10377,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10388,25 +10392,25 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>79</v>
@@ -10414,10 +10418,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10440,13 +10444,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10497,7 +10501,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10512,13 +10516,13 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10527,10 +10531,10 @@
         <v>79</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>79</v>
@@ -10538,10 +10542,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10564,13 +10568,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10621,7 +10625,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10639,7 +10643,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10662,10 +10666,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10688,16 +10692,16 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10747,7 +10751,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10762,13 +10766,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10777,10 +10781,10 @@
         <v>79</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>79</v>
@@ -10788,10 +10792,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10817,13 +10821,13 @@
         <v>178</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10873,7 +10877,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10888,25 +10892,25 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>79</v>
@@ -10914,10 +10918,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10943,10 +10947,10 @@
         <v>178</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10997,7 +11001,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11015,16 +11019,16 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>79</v>
@@ -11038,14 +11042,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11064,13 +11068,13 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11121,7 +11125,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11136,10 +11140,10 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -11162,10 +11166,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11188,13 +11192,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11245,7 +11249,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11257,22 +11261,22 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11286,10 +11290,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11410,10 +11414,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11536,14 +11540,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11565,10 +11569,10 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>139</v>
@@ -11623,7 +11627,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11664,10 +11668,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11693,13 +11697,13 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11725,13 +11729,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11749,7 +11753,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11767,7 +11771,7 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>176</v>
@@ -11776,7 +11780,7 @@
         <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
@@ -11790,10 +11794,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11816,13 +11820,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11873,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11891,22 +11895,22 @@
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>79</v>
@@ -11914,10 +11918,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11943,10 +11947,10 @@
         <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11976,10 +11980,10 @@
         <v>160</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11997,7 +12001,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12015,10 +12019,10 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
@@ -12038,10 +12042,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12067,10 +12071,10 @@
         <v>110</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12100,10 +12104,10 @@
         <v>160</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -12121,7 +12125,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12139,16 +12143,16 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>79</v>
@@ -12162,10 +12166,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12188,13 +12192,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12245,7 +12249,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12286,10 +12290,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12312,16 +12316,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12371,7 +12375,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12386,10 +12390,10 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>79</v>
@@ -12398,7 +12402,7 @@
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -244,15 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t/>
@@ -521,21 +521,6 @@
     <t>http://va.gov/fhir/ValueSet/VSVFAppointmentStatus</t>
   </si>
   <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>SCH-25</t>
-  </si>
-  <si>
     <t>748: transform using #waitlist on SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
   </si>
   <si>
@@ -546,6 +531,21 @@
 appointment.patientClass</t>
   </si>
   <si>
+    <t>Request.status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>SCH-25</t>
+  </si>
+  <si>
     <t>Appointment.cancelationReason</t>
   </si>
   <si>
@@ -697,16 +697,16 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>735: source value from APPOINTMENT - CANCELLATION REASON (#2.98-16)</t>
+  </si>
+  <si>
+    <t>Appt.Appointment.CancellationReasonIEN</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>735: source value from APPOINTMENT - CANCELLATION REASON (#2.98-16)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.CancellationReasonIEN</t>
   </si>
   <si>
     <t>Appointment.cancelationReason.coding.display</t>
@@ -915,15 +915,15 @@
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
   </si>
   <si>
+    <t>739: target not supported</t>
+  </si>
+  <si>
     <t>.performer.AssignedPerson.code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>739: target not supported</t>
-  </si>
-  <si>
     <t>Appointment.appointmentType</t>
   </si>
   <si>
@@ -1002,6 +1002,9 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
+    <t>741: target not supported</t>
+  </si>
+  <si>
     <t>Request.reasonCode</t>
   </si>
   <si>
@@ -1009,9 +1012,6 @@
   </si>
   <si>
     <t>AIS-3, SCH-7</t>
-  </si>
-  <si>
-    <t>741: target not supported</t>
   </si>
   <si>
     <t>Appointment.reasonReference</t>
@@ -1027,13 +1027,13 @@
     <t>Reason the appointment has been scheduled to take place, as specified using information from another resource. When the patient arrives and the encounter begins it may be used as the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
   </si>
   <si>
+    <t>742: target not supported</t>
+  </si>
+  <si>
     <t>Request.reasonReference</t>
   </si>
   <si>
     <t>.inboundRelationship[@typeCode = 'RSON'].observation</t>
-  </si>
-  <si>
-    <t>742: target not supported</t>
   </si>
   <si>
     <t>Appointment.priority</t>
@@ -1122,6 +1122,15 @@
     <t>Date/Time that the appointment is to take place.</t>
   </si>
   <si>
+    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (#409.3-22)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.AppointmentDesiredDate</t>
+  </si>
+  <si>
+    <t>appointment.dateTime</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -1137,15 +1146,6 @@
     <t>ARQ-11.1, SCH-11.4 / TQ1-7</t>
   </si>
   <si>
-    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (#409.3-22)</t>
-  </si>
-  <si>
-    <t>Appt.WaitList.AppointmentDesiredDate</t>
-  </si>
-  <si>
-    <t>appointment.dateTime</t>
-  </si>
-  <si>
     <t>Appointment.end</t>
   </si>
   <si>
@@ -1153,18 +1153,6 @@
   </si>
   <si>
     <t>Date/Time that the appointment is to conclude.</t>
-  </si>
-  <si>
-    <t>.effectiveTime.high</t>
-  </si>
-  <si>
-    <t>DTEND</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>SCH-11.5 / TQ1-8/ calculated based on the start and the duration which is in ARQ-9</t>
   </si>
   <si>
     <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (#2.98-21 &gt; 409.68-.07)</t>
@@ -1174,6 +1162,18 @@
 Outpat.Visit.COProcessCompleteDateTime,Outpat.Workload.COProcessCompleteDateTime</t>
   </si>
   <si>
+    <t>.effectiveTime.high</t>
+  </si>
+  <si>
+    <t>DTEND</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>SCH-11.5 / TQ1-8/ calculated based on the start and the duration which is in ARQ-9</t>
+  </si>
+  <si>
     <t>Appointment.minutesDuration</t>
   </si>
   <si>
@@ -1187,16 +1187,16 @@
     <t>Number of minutes that the appointment is to take. This can be less than the duration between the start and end times.  For example, where the actual time of appointment is only an estimate or if a 30 minute appointment is being requested, but any time would work.  Also, if there is, for example, a planned 15 minute break in the middle of a long appointment, the duration may be 15 minutes less than the difference between the start and end.</t>
   </si>
   <si>
+    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
+  </si>
+  <si>
+    <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
+  </si>
+  <si>
     <t>.activityTime[@xsi:type = ('SXPR_TS', 'PIVL_TS')].width</t>
   </si>
   <si>
     <t>DURATION (e.g. PT15M)</t>
-  </si>
-  <si>
-    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
     <t>Appointment.slot</t>
@@ -1231,6 +1231,12 @@
     <t>This property is required for many use cases where the age of an appointment is considered in processing workflows for scheduling and billing of appointments.</t>
   </si>
   <si>
+    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (#409.3-1)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.OriginatingDate</t>
+  </si>
+  <si>
     <t>Request.authoredOn</t>
   </si>
   <si>
@@ -1238,12 +1244,6 @@
   </si>
   <si>
     <t>CREATED</t>
-  </si>
-  <si>
-    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (#409.3-1)</t>
-  </si>
-  <si>
-    <t>Appt.WaitList.OriginatingDate</t>
   </si>
   <si>
     <t>Appointment.comment</t>
@@ -1260,6 +1260,12 @@
 Where this is a planned appointment and the start/end dates are not set then this field can be used to provide additional guidance on the details of the appointment request, including any restrictions on when to book it.</t>
   </si>
   <si>
+    <t>752: source value from SD WAIT LIST - COMMENTS (#409.3-25)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.WaitListComments</t>
+  </si>
+  <si>
     <t>Request.note</t>
   </si>
   <si>
@@ -1267,12 +1273,6 @@
   </si>
   <si>
     <t>DESCRIPTION (for internal use)</t>
-  </si>
-  <si>
-    <t>752: source value from SD WAIT LIST - COMMENTS (#409.3-25)</t>
-  </si>
-  <si>
-    <t>Appt.WaitList.WaitListComments</t>
   </si>
   <si>
     <t>Appointment.patientInstruction</t>
@@ -1406,6 +1406,9 @@
     <t>A Person, Location/HealthcareService or Device that is participating in the appointment.</t>
   </si>
   <si>
+    <t>754: reference from SD WAIT LIST - APPT CLINIC (#409.3-13.2)</t>
+  </si>
+  <si>
     <t>performer.person | reusableDevice.manufacturedDevice | subject.patient | location.serviceDeliveryLocation</t>
   </si>
   <si>
@@ -1416,9 +1419,6 @@
   </si>
   <si>
     <t>PID-3-Patient ID List | AIL-3 | AIG-3 | AIP-3</t>
-  </si>
-  <si>
-    <t>754: reference from SD WAIT LIST - APPT CLINIC (#409.3-13.2)</t>
   </si>
   <si>
     <t>Appointment.participant.required</t>
@@ -1850,14 +1850,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="34.3125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="110.08203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="155.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="77.55859375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="146.90625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="84.28125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="146.90625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.08203125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="155.20703125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="77.55859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2094,22 +2094,22 @@
         <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>79</v>
@@ -2725,16 +2725,16 @@
         <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>79</v>
@@ -2851,16 +2851,16 @@
         <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>79</v>
@@ -2977,16 +2977,16 @@
         <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>79</v>
@@ -3105,16 +3105,16 @@
         <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>79</v>
@@ -3226,28 +3226,28 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AR11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR11" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3475,16 +3475,16 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3599,16 +3599,16 @@
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>79</v>
@@ -3725,16 +3725,16 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3853,25 +3853,25 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -3977,16 +3977,16 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -4103,16 +4103,16 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4231,25 +4231,25 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR19" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -4357,25 +4357,25 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4480,10 +4480,10 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4492,16 +4492,16 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AQ21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4609,25 +4609,25 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4737,25 +4737,25 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4865,25 +4865,25 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4987,19 +4987,19 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>79</v>
@@ -5111,16 +5111,16 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5237,16 +5237,16 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5365,25 +5365,25 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5489,16 +5489,16 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5615,16 +5615,16 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5743,25 +5743,25 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5869,25 +5869,25 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5992,28 +5992,28 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>263</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6121,25 +6121,25 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6249,25 +6249,25 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6377,25 +6377,25 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6498,19 +6498,19 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6625,16 +6625,16 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6751,16 +6751,16 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6879,25 +6879,25 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7003,16 +7003,16 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7129,16 +7129,16 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7257,25 +7257,25 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7383,25 +7383,25 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7506,28 +7506,28 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>283</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7635,25 +7635,25 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7763,25 +7763,25 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -7891,25 +7891,25 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8010,25 +8010,25 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AP49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>79</v>
@@ -8135,25 +8135,25 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AN50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8259,16 +8259,16 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -8385,16 +8385,16 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8513,25 +8513,25 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR53" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8637,16 +8637,16 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -8763,16 +8763,16 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -8891,25 +8891,25 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9017,25 +9017,25 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR57" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9140,28 +9140,28 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>311</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9269,25 +9269,25 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR59" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9397,25 +9397,25 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9525,25 +9525,25 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9649,25 +9649,25 @@
         <v>320</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>322</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -9773,19 +9773,19 @@
         <v>328</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AO63" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>79</v>
@@ -9896,28 +9896,28 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN64" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AQ64" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -10023,25 +10023,25 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AP65" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AN65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO65" t="s" s="2">
+      <c r="AQ65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10144,25 +10144,25 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AP66" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AQ66" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>79</v>
@@ -10392,28 +10392,28 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AQ68" t="s" s="2">
+      <c r="AR68" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10516,25 +10516,25 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>79</v>
@@ -10643,16 +10643,16 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>79</v>
@@ -10772,19 +10772,19 @@
         <v>394</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AO71" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>397</v>
+        <v>79</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>79</v>
@@ -10898,22 +10898,22 @@
         <v>403</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AN72" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AO72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11019,25 +11019,25 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO73" t="s" s="2">
+      <c r="AQ73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR73" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11140,19 +11140,19 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>79</v>
@@ -11264,28 +11264,28 @@
         <v>422</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11391,16 +11391,16 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11517,16 +11517,16 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>79</v>
@@ -11645,16 +11645,16 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>79</v>
@@ -11771,25 +11771,25 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AQ79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR79" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="80" hidden="true">
@@ -11892,28 +11892,28 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>447</v>
+        <v>282</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AP80" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AO80" t="s" s="2">
+      <c r="AQ80" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AP80" t="s" s="2">
+      <c r="AR80" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AR80" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="81" hidden="true">
@@ -12019,19 +12019,19 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AP81" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>79</v>
@@ -12143,25 +12143,25 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AP82" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO82" t="s" s="2">
+      <c r="AQ82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR82" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -12267,16 +12267,16 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>79</v>
@@ -12390,28 +12390,28 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -521,7 +521,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFAppointmentStatus</t>
   </si>
   <si>
-    <t>748: transform using #waitlist on SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
+    <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
   </si>
   <si>
     <t>Appt.Appointment.AppointmentStatus</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file APPOINTMENT (#2.98) to Appointment</t>
+    <t>This StructureDefinition contains the maps for VistA file APPOINTMENT (2.98) to Appointment</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -521,7 +521,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFAppointmentStatus</t>
   </si>
   <si>
-    <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (#409.3-.01) case not null</t>
+    <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) case not null</t>
   </si>
   <si>
     <t>Appt.Appointment.AppointmentStatus</t>
@@ -697,7 +697,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>735: source value from APPOINTMENT - CANCELLATION REASON (#2.98-16)</t>
+    <t>735: source value from APPOINTMENT - CANCELLATION REASON (2.98-16)</t>
   </si>
   <si>
     <t>Appt.Appointment.CancellationReasonIEN</t>
@@ -824,7 +824,7 @@
     <t>Appointment.serviceCategory.coding.code</t>
   </si>
   <si>
-    <t>749: source value from SD WAIT LIST - APPT STOP CODE (#409.3-13.4)</t>
+    <t>749: source value from SD WAIT LIST - APPT STOP CODE (409.3-13.4)</t>
   </si>
   <si>
     <t>Appt.Appointment.LocationIEN
@@ -885,7 +885,7 @@
     <t>Appointment.serviceType.coding.code</t>
   </si>
   <si>
-    <t>738: source value from APPOINTMENT - CLINIC &gt; HOSPITAL LOCATION - CREDIT STOP CODE (#2.98-.01 &gt; 44-2503)</t>
+    <t>738: source value from APPOINTMENT - CLINIC &gt; HOSPITAL LOCATION - CREDIT STOP CODE (2.98-.01 &gt; 44-2503)</t>
   </si>
   <si>
     <t>Appt.Appointment.LocationIEN</t>
@@ -969,10 +969,11 @@
     <t>Appointment.appointmentType.coding.code</t>
   </si>
   <si>
-    <t>740: source value from APPOINTMENT - APPOINTMENT TYPE (#2.98-9.5)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.AppointmentTypeIEN</t>
+    <t>740: source value from APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01)</t>
+  </si>
+  <si>
+    <t>Appt.Appointment.AppointmentTypeIEN
+Dim.AppointmentType.AppointmentType</t>
   </si>
   <si>
     <t>appointment.type</t>
@@ -1122,7 +1123,7 @@
     <t>Date/Time that the appointment is to take place.</t>
   </si>
   <si>
-    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (#409.3-22)</t>
+    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (409.3-22)</t>
   </si>
   <si>
     <t>Appt.WaitList.AppointmentDesiredDate</t>
@@ -1155,7 +1156,7 @@
     <t>Date/Time that the appointment is to conclude.</t>
   </si>
   <si>
-    <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (#2.98-21 &gt; 409.68-.07)</t>
+    <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (2.98-21 &gt; 409.68-.07)</t>
   </si>
   <si>
     <t>Appt.Appointment.VisitIEN
@@ -1187,7 +1188,7 @@
     <t>Number of minutes that the appointment is to take. This can be less than the duration between the start and end times.  For example, where the actual time of appointment is only an estimate or if a 30 minute appointment is being requested, but any time would work.  Also, if there is, for example, a planned 15 minute break in the middle of a long appointment, the duration may be 15 minutes less than the difference between the start and end.</t>
   </si>
   <si>
-    <t>744: source value from PATIENT - LENGTH OF APP'T (#44.003-1)</t>
+    <t>744: source value from PATIENT - LENGTH OF APP'T (44.003-1)</t>
   </si>
   <si>
     <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
@@ -1231,7 +1232,7 @@
     <t>This property is required for many use cases where the age of an appointment is considered in processing workflows for scheduling and billing of appointments.</t>
   </si>
   <si>
-    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (#409.3-1)</t>
+    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (409.3-1)</t>
   </si>
   <si>
     <t>Appt.WaitList.OriginatingDate</t>
@@ -1260,7 +1261,7 @@
 Where this is a planned appointment and the start/end dates are not set then this field can be used to provide additional guidance on the details of the appointment request, including any restrictions on when to book it.</t>
   </si>
   <si>
-    <t>752: source value from SD WAIT LIST - COMMENTS (#409.3-25)</t>
+    <t>752: source value from SD WAIT LIST - COMMENTS (409.3-25)</t>
   </si>
   <si>
     <t>Appt.WaitList.WaitListComments</t>
@@ -1406,7 +1407,7 @@
     <t>A Person, Location/HealthcareService or Device that is participating in the appointment.</t>
   </si>
   <si>
-    <t>754: reference from SD WAIT LIST - APPT CLINIC (#409.3-13.2)</t>
+    <t>754: reference from SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
   </si>
   <si>
     <t>performer.person | reusableDevice.manufacturedDevice | subject.patient | location.serviceDeliveryLocation</t>
@@ -1850,7 +1851,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="146.90625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="145.37109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -524,7 +524,7 @@
     <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) case not null</t>
   </si>
   <si>
-    <t>Appt.Appointment.AppointmentStatus</t>
+    <t>Appt.WaitList.PatientIEN</t>
   </si>
   <si>
     <t>appointment.apptStatus
@@ -631,13 +631,185 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.coding.system</t>
+    <t>Appointment.cancelationReason.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>735: transform using VF_AppointmentCancellationReason on APPOINTMENT - CANCELLATION REASON (2.98-16)</t>
+  </si>
+  <si>
+    <t>Appt.Appointment.CancellationReasonIEN</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
+</t>
+  </si>
+  <si>
+    <t>Mapping from permitted to transmitted</t>
+  </si>
+  <si>
+    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
+  </si>
+  <si>
+    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension.extension</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.value[x]</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ConceptMap)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ConceptMap/CMVFAppointmentCancellationReason</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Appointment.cancelationReason.text.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory</t>
+  </si>
+  <si>
+    <t>A broad categorization of the service that is to be performed during this appointment</t>
+  </si>
+  <si>
+    <t>A broad categorization of the service that is to be performed during this appointment.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+  </si>
+  <si>
+    <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
+  </si>
+  <si>
+    <t>CATEGORIES</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.id</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.extension</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.coding</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.coding.system</t>
   </si>
   <si>
     <t>Identity of the terminology system</t>
@@ -661,7 +833,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.coding.version</t>
+    <t>Appointment.serviceCategory.coding.version</t>
   </si>
   <si>
     <t>Version of the system - if relevant</t>
@@ -682,7 +854,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.coding.code</t>
+    <t>Appointment.serviceCategory.coding.code</t>
   </si>
   <si>
     <t>Symbol in syntax defined by the system</t>
@@ -697,10 +869,13 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>735: source value from APPOINTMENT - CANCELLATION REASON (2.98-16)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.CancellationReasonIEN</t>
+    <t>749: source value from SD WAIT LIST - APPT STOP CODE (409.3-13.4)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.AppointmentPrimaryStopCodeIEN</t>
+  </si>
+  <si>
+    <t>appointment.service</t>
   </si>
   <si>
     <t>./code</t>
@@ -709,7 +884,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.coding.display</t>
+    <t>Appointment.serviceCategory.coding.display</t>
   </si>
   <si>
     <t>Representation defined by the system</t>
@@ -730,7 +905,7 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.coding.userSelected</t>
+    <t>Appointment.serviceCategory.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -758,137 +933,56 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory</t>
-  </si>
-  <si>
-    <t>A broad categorization of the service that is to be performed during this appointment</t>
-  </si>
-  <si>
-    <t>A broad categorization of the service that is to be performed during this appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
-  </si>
-  <si>
-    <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
-  </si>
-  <si>
-    <t>CATEGORIES</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.code</t>
-  </si>
-  <si>
-    <t>749: source value from SD WAIT LIST - APPT STOP CODE (409.3-13.4)</t>
+    <t>Appointment.serviceCategory.text</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType</t>
+  </si>
+  <si>
+    <t>The specific service that is to be performed during this appointment</t>
+  </si>
+  <si>
+    <t>The specific service that is to be performed during this appointment.</t>
+  </si>
+  <si>
+    <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+  </si>
+  <si>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.id</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.extension</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.serviceType.coding.code</t>
+  </si>
+  <si>
+    <t>738: source value from APPOINTMENT - CLINIC &gt; HOSPITAL LOCATION - CREDIT STOP CODE (2.98-.01 &gt; 44-2503)</t>
   </si>
   <si>
     <t>Appt.Appointment.LocationIEN
-Dim.Location.MedicalService</t>
-  </si>
-  <si>
-    <t>appointment.service</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.text</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType</t>
-  </si>
-  <si>
-    <t>The specific service that is to be performed during this appointment</t>
-  </si>
-  <si>
-    <t>The specific service that is to be performed during this appointment.</t>
-  </si>
-  <si>
-    <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
-  </si>
-  <si>
-    <t>Request.code</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.serviceType.coding.code</t>
-  </si>
-  <si>
-    <t>738: source value from APPOINTMENT - CLINIC &gt; HOSPITAL LOCATION - CREDIT STOP CODE (2.98-.01 &gt; 44-2503)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.LocationIEN</t>
+Dim.Location.SecondaryStopCodeIEN</t>
   </si>
   <si>
     <t>appointment.clinStop</t>
@@ -954,19 +1048,7 @@
     <t>Appointment.appointmentType.coding</t>
   </si>
   <si>
-    <t>Appointment.appointmentType.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.coding.code</t>
+    <t>Appointment.appointmentType.text</t>
   </si>
   <si>
     <t>740: source value from APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01)</t>
@@ -977,15 +1059,6 @@
   </si>
   <si>
     <t>appointment.type</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.appointmentType.text</t>
   </si>
   <si>
     <t>Appointment.reasonCode</t>
@@ -1408,6 +1481,9 @@
   </si>
   <si>
     <t>754: reference from SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.AppointmentLocationIEN</t>
   </si>
   <si>
     <t>performer.person | reusableDevice.manufacturedDevice | subject.patient | location.serviceDeliveryLocation</t>
@@ -1813,12 +1889,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR84"/>
+  <dimension ref="A1:AR78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.09375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.09375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="88.0859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="54.19140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3894,25 +3970,29 @@
         <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3960,7 +4040,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3972,13 +4052,13 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3987,7 +4067,7 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3996,26 +4076,26 @@
         <v>79</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -4027,17 +4107,15 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -4074,31 +4152,31 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
@@ -4113,7 +4191,7 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4127,10 +4205,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4141,7 +4219,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4150,23 +4228,19 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4202,31 +4276,29 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -4241,7 +4313,7 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4250,17 +4322,19 @@
         <v>79</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4278,19 +4352,19 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4340,19 +4414,19 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
@@ -4367,7 +4441,7 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>212</v>
+        <v>133</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4376,15 +4450,15 @@
         <v>79</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>213</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4398,27 +4472,25 @@
         <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4466,7 +4538,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4475,16 +4547,16 @@
         <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4493,7 +4565,7 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4502,12 +4574,12 @@
         <v>79</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>223</v>
@@ -4521,7 +4593,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4530,21 +4602,19 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4580,31 +4650,31 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
@@ -4619,7 +4689,7 @@
         <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4628,15 +4698,15 @@
         <v>79</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4644,7 +4714,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4656,29 +4726,27 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4720,10 +4788,10 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4732,7 +4800,7 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
@@ -4747,7 +4815,7 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>237</v>
+        <v>133</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4756,15 +4824,15 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4772,7 +4840,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4784,23 +4852,19 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4809,7 +4873,7 @@
         <v>79</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>79</v>
@@ -4848,7 +4912,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4857,7 +4921,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4875,7 +4939,7 @@
         <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>245</v>
+        <v>133</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -4884,15 +4948,15 @@
         <v>79</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>246</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4903,7 +4967,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4912,16 +4976,16 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4945,14 +5009,16 @@
         <v>79</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4970,19 +5036,19 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4997,10 +5063,10 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>79</v>
@@ -5011,10 +5077,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5025,7 +5091,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -5034,16 +5100,16 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5070,13 +5136,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -5094,19 +5158,19 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -5121,10 +5185,10 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>79</v>
@@ -5135,21 +5199,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5161,17 +5225,15 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5208,31 +5270,31 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -5261,14 +5323,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5284,23 +5346,21 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5336,19 +5396,19 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5360,7 +5420,7 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5375,7 +5435,7 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5384,15 +5444,15 @@
         <v>79</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5403,7 +5463,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -5412,19 +5472,23 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5472,19 +5536,19 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
@@ -5499,7 +5563,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5508,26 +5572,26 @@
         <v>79</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5539,17 +5603,15 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5586,31 +5648,31 @@
         <v>79</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
@@ -5639,21 +5701,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5662,23 +5724,21 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5714,31 +5774,31 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5753,7 +5813,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5762,15 +5822,15 @@
         <v>79</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5793,18 +5853,20 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5852,7 +5914,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5879,7 +5941,7 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5888,15 +5950,15 @@
         <v>79</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>213</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5910,7 +5972,7 @@
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
@@ -5919,18 +5981,18 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5978,7 +6040,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5993,19 +6055,19 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -6014,15 +6076,15 @@
         <v>79</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>222</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6036,7 +6098,7 @@
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -6045,17 +6107,17 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6104,7 +6166,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6119,19 +6181,19 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -6140,15 +6202,15 @@
         <v>79</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>229</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6171,19 +6233,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6232,7 +6292,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6259,7 +6319,7 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6268,15 +6328,15 @@
         <v>79</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>238</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6299,19 +6359,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>178</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6360,7 +6420,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>244</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6387,7 +6447,7 @@
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6396,15 +6456,15 @@
         <v>79</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>246</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6415,7 +6475,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6427,18 +6487,20 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6462,11 +6524,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6484,13 +6548,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -6508,10 +6572,10 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6520,15 +6584,15 @@
         <v>79</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6539,7 +6603,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6548,18 +6612,20 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>179</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6584,13 +6650,11 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6608,19 +6672,19 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
@@ -6632,10 +6696,10 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6649,21 +6713,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6675,17 +6739,15 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6722,31 +6784,31 @@
         <v>79</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -6775,14 +6837,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6798,23 +6860,21 @@
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6850,19 +6910,19 @@
         <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6874,7 +6934,7 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
@@ -6889,7 +6949,7 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -6898,15 +6958,15 @@
         <v>79</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6917,7 +6977,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6926,19 +6986,23 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6986,19 +7050,19 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -7013,7 +7077,7 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7022,26 +7086,26 @@
         <v>79</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -7053,17 +7117,15 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7100,31 +7162,31 @@
         <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -7153,21 +7215,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -7176,23 +7238,21 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -7228,31 +7288,31 @@
         <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -7267,7 +7327,7 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7276,15 +7336,15 @@
         <v>79</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7307,18 +7367,20 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7366,7 +7428,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7393,7 +7455,7 @@
         <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7402,15 +7464,15 @@
         <v>79</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>213</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7424,7 +7486,7 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7433,18 +7495,18 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7492,7 +7554,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7507,19 +7569,19 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7528,15 +7590,15 @@
         <v>79</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>222</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7550,7 +7612,7 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
@@ -7559,17 +7621,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7618,7 +7680,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7633,19 +7695,19 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7654,15 +7716,15 @@
         <v>79</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>229</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7685,19 +7747,17 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7746,7 +7806,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7773,7 +7833,7 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7782,15 +7842,15 @@
         <v>79</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>238</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7813,19 +7873,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>178</v>
+        <v>288</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7874,7 +7934,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>244</v>
+        <v>293</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7901,7 +7961,7 @@
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -7910,15 +7970,15 @@
         <v>79</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>246</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7929,7 +7989,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7941,16 +8001,20 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>288</v>
+        <v>198</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7974,11 +8038,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7996,13 +8062,13 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
@@ -8011,7 +8077,7 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
@@ -8023,24 +8089,24 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8051,7 +8117,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -8066,10 +8132,10 @@
         <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8100,7 +8166,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8118,13 +8184,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -8133,7 +8199,7 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>79</v>
@@ -8145,24 +8211,24 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8182,16 +8248,16 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>179</v>
+        <v>325</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>180</v>
+        <v>326</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8218,13 +8284,11 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8242,7 +8306,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8254,7 +8318,7 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8269,35 +8333,35 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>176</v>
+        <v>328</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8309,17 +8373,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8356,31 +8418,31 @@
         <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8409,14 +8471,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8432,23 +8494,21 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8484,19 +8544,19 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8508,7 +8568,7 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8523,7 +8583,7 @@
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -8532,15 +8592,15 @@
         <v>79</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8551,7 +8611,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8560,19 +8620,23 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8620,19 +8684,19 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8647,7 +8711,7 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -8656,49 +8720,51 @@
         <v>79</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8734,46 +8800,46 @@
         <v>79</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -8782,15 +8848,15 @@
         <v>79</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8801,7 +8867,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8813,20 +8879,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8850,13 +8912,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8874,13 +8936,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8889,7 +8951,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
@@ -8898,10 +8960,10 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>205</v>
+        <v>345</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8910,15 +8972,15 @@
         <v>79</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>206</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8929,7 +8991,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8938,20 +9000,18 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>178</v>
+        <v>348</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>349</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -9000,13 +9060,13 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>211</v>
+        <v>347</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
@@ -9015,7 +9075,7 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
@@ -9024,10 +9084,10 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -9036,15 +9096,15 @@
         <v>79</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9058,27 +9118,27 @@
         <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>110</v>
+        <v>355</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -9126,7 +9186,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9141,36 +9201,36 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>221</v>
+        <v>360</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>222</v>
+        <v>362</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9190,21 +9250,19 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>224</v>
+        <v>364</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>225</v>
+        <v>365</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9252,7 +9310,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>227</v>
+        <v>363</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9279,24 +9337,24 @@
         <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>228</v>
+        <v>366</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>229</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>313</v>
+        <v>369</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>313</v>
+        <v>369</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9307,7 +9365,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9316,23 +9374,19 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -9380,13 +9434,13 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>236</v>
+        <v>369</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
@@ -9404,27 +9458,27 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>237</v>
+        <v>374</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9438,7 +9492,7 @@
         <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>79</v>
@@ -9447,20 +9501,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>240</v>
+        <v>379</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9508,7 +9558,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>244</v>
+        <v>377</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9523,36 +9573,36 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>245</v>
+        <v>385</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>246</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,10 +9613,10 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
@@ -9575,13 +9625,13 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>171</v>
+        <v>378</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>316</v>
+        <v>390</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9608,13 +9658,13 @@
         <v>79</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9632,13 +9682,13 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
@@ -9647,36 +9697,36 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>320</v>
+        <v>392</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>322</v>
+        <v>394</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>323</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9687,10 +9737,10 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
@@ -9699,13 +9749,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>325</v>
+        <v>399</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>326</v>
+        <v>400</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>327</v>
+        <v>401</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9756,13 +9806,13 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
@@ -9771,22 +9821,22 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>330</v>
+        <v>404</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>79</v>
@@ -9797,10 +9847,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9811,7 +9861,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9823,17 +9873,15 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>332</v>
+        <v>407</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9882,13 +9930,13 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
@@ -9906,27 +9954,27 @@
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>337</v>
+        <v>410</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>338</v>
+        <v>79</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9940,7 +9988,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9949,15 +9997,17 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>178</v>
+        <v>412</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>341</v>
+        <v>413</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -10006,7 +10056,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10021,36 +10071,36 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>79</v>
+        <v>417</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>343</v>
+        <v>419</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>344</v>
+        <v>420</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>346</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>346</v>
+        <v>421</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10061,10 +10111,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -10073,15 +10123,17 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>347</v>
+        <v>178</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>348</v>
+        <v>422</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10130,13 +10182,13 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>346</v>
+        <v>421</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
@@ -10145,36 +10197,36 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>350</v>
+        <v>427</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>351</v>
+        <v>428</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>352</v>
+        <v>429</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>354</v>
+        <v>430</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>354</v>
+        <v>430</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10188,22 +10240,22 @@
         <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>355</v>
+        <v>178</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>356</v>
+        <v>431</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>357</v>
+        <v>432</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10254,7 +10306,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>354</v>
+        <v>430</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10269,65 +10321,65 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>362</v>
+        <v>428</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>355</v>
+        <v>436</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>367</v>
+        <v>437</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10378,13 +10430,13 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
@@ -10393,36 +10445,36 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>361</v>
+        <v>439</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>375</v>
+        <v>441</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>375</v>
+        <v>441</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10430,13 +10482,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>79</v>
@@ -10445,13 +10497,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>377</v>
+        <v>443</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10502,51 +10554,51 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>375</v>
+        <v>441</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>445</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>361</v>
+        <v>446</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>382</v>
+        <v>448</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>79</v>
+        <v>449</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>383</v>
+        <v>450</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>383</v>
+        <v>450</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10557,7 +10609,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10569,13 +10621,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>384</v>
+        <v>178</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>385</v>
+        <v>179</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>386</v>
+        <v>180</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10626,19 +10678,19 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>383</v>
+        <v>181</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10653,7 +10705,7 @@
         <v>79</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>387</v>
+        <v>176</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>79</v>
@@ -10667,24 +10719,24 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>79</v>
@@ -10693,16 +10745,16 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>389</v>
+        <v>136</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>390</v>
+        <v>137</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>391</v>
+        <v>183</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>392</v>
+        <v>139</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10752,37 +10804,37 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>388</v>
+        <v>187</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>396</v>
+        <v>176</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>397</v>
+        <v>79</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>79</v>
@@ -10793,44 +10845,46 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I72" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I72" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J72" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>400</v>
+        <v>455</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10878,51 +10932,51 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>398</v>
+        <v>456</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>405</v>
+        <v>133</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10933,7 +10987,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10942,18 +10996,20 @@
         <v>79</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10978,13 +11034,13 @@
         <v>79</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>79</v>
+        <v>461</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>79</v>
+        <v>462</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>79</v>
@@ -11002,13 +11058,13 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
@@ -11029,53 +11085,53 @@
         <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>405</v>
+        <v>464</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>410</v>
+        <v>176</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>345</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>413</v>
+        <v>467</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>415</v>
+        <v>469</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11126,13 +11182,13 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
@@ -11141,36 +11197,36 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>79</v>
+        <v>470</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>79</v>
+        <v>471</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11178,11 +11234,11 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11190,16 +11246,16 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>419</v>
+        <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11226,13 +11282,13 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>79</v>
+        <v>479</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>79</v>
+        <v>480</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -11250,19 +11306,19 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>422</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
@@ -11274,27 +11330,27 @@
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>423</v>
+        <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>425</v>
+        <v>482</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>427</v>
+        <v>483</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>427</v>
+        <v>483</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11302,7 +11358,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>90</v>
@@ -11314,16 +11370,16 @@
         <v>79</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>179</v>
+        <v>484</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>180</v>
+        <v>485</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11350,13 +11406,13 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>79</v>
+        <v>486</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -11374,10 +11430,10 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>181</v>
+        <v>483</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>90</v>
@@ -11386,7 +11442,7 @@
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
@@ -11401,35 +11457,35 @@
         <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>176</v>
+        <v>488</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>79</v>
+        <v>489</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>79</v>
+        <v>490</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>79</v>
@@ -11441,17 +11497,15 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>136</v>
+        <v>492</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>137</v>
+        <v>493</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11500,19 +11554,19 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>187</v>
+        <v>491</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
@@ -11541,14 +11595,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11561,26 +11615,24 @@
         <v>79</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>136</v>
+        <v>492</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>431</v>
+        <v>496</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>432</v>
+        <v>497</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
@@ -11628,7 +11680,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>433</v>
+        <v>495</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11640,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
@@ -11652,10 +11704,10 @@
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>133</v>
+        <v>499</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>79</v>
@@ -11664,759 +11716,11 @@
         <v>79</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AR80" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR81" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR83" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>476</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR84">
+  <autoFilter ref="A1:AR78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12426,7 +11730,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3134" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="460">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,16 +559,40 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFAppointmentCancellationReason</t>
+  </si>
+  <si>
+    <t>735: terminologyMaps using VF_AppointmentCancellationReason on APPOINTMENT - CANCELLATION REASON (2.98-16)</t>
+  </si>
+  <si>
+    <t>Appt.Appointment.CancellationReasonIEN</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory</t>
+  </si>
+  <si>
+    <t>A broad categorization of the service that is to be performed during this appointment</t>
+  </si>
+  <si>
+    <t>A broad categorization of the service that is to be performed during this appointment.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.id</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+  </si>
+  <si>
+    <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
+  </si>
+  <si>
+    <t>CATEGORIES</t>
+  </si>
+  <si>
+    <t>Appointment.serviceCategory.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -584,7 +608,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.extension</t>
+    <t>Appointment.serviceCategory.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -603,7 +627,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.coding</t>
+    <t>Appointment.serviceCategory.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -631,178 +655,6 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Appointment.cancelationReason.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>735: transform using VF_AppointmentCancellationReason on APPOINTMENT - CANCELLATION REASON (2.98-16)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.CancellationReasonIEN</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
-</t>
-  </si>
-  <si>
-    <t>Mapping from permitted to transmitted</t>
-  </si>
-  <si>
-    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
-  </si>
-  <si>
-    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension.extension</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(ConceptMap)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFAppointmentCancellationReason</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>Appointment.cancelationReason.text.value</t>
-  </si>
-  <si>
-    <t>Primitive value for string</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>1048576</t>
-  </si>
-  <si>
-    <t>string.value</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory</t>
-  </si>
-  <si>
-    <t>A broad categorization of the service that is to be performed during this appointment</t>
-  </si>
-  <si>
-    <t>A broad categorization of the service that is to be performed during this appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
-  </si>
-  <si>
-    <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
-  </si>
-  <si>
-    <t>CATEGORIES</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.id</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.extension</t>
-  </si>
-  <si>
-    <t>Appointment.serviceCategory.coding</t>
-  </si>
-  <si>
     <t>Appointment.serviceCategory.coding.id</t>
   </si>
   <si>
@@ -934,6 +786,27 @@
   </si>
   <si>
     <t>Appointment.serviceCategory.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Appointment.serviceType</t>
@@ -1889,12 +1762,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR78"/>
+  <dimension ref="A1:AR66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="88.0859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.19140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="47.6953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.6953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1917,7 +1790,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="50.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3470,7 +3343,7 @@
         <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>79</v>
@@ -3512,11 +3385,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3549,10 +3422,10 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>79</v>
@@ -3561,7 +3434,7 @@
         <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3575,10 +3448,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3589,7 +3462,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3598,10 +3471,10 @@
         <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>179</v>
@@ -3634,13 +3507,11 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3658,19 +3529,19 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
@@ -3685,10 +3556,10 @@
         <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>79</v>
@@ -3699,21 +3570,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3725,17 +3596,15 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3772,31 +3641,31 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
@@ -3811,7 +3680,7 @@
         <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3825,14 +3694,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3848,23 +3717,21 @@
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3900,19 +3767,19 @@
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3924,7 +3791,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
@@ -3939,7 +3806,7 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -3948,15 +3815,15 @@
         <v>79</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3967,10 +3834,10 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
@@ -3979,7 +3846,7 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>198</v>
@@ -4046,7 +3913,7 @@
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
@@ -4055,36 +3922,36 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4107,13 +3974,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4164,7 +4031,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4191,7 +4058,7 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4205,14 +4072,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4234,12 +4101,14 @@
         <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4276,17 +4145,19 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AC19" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4313,7 +4184,7 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4327,14 +4198,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4352,21 +4221,23 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4414,19 +4285,19 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
@@ -4441,7 +4312,7 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4450,15 +4321,15 @@
         <v>79</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>133</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4478,18 +4349,20 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4538,7 +4411,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4547,34 +4420,34 @@
         <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4582,7 +4455,7 @@
         <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4593,28 +4466,30 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4650,46 +4525,46 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>230</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4698,15 +4573,15 @@
         <v>79</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4714,7 +4589,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4726,27 +4601,27 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4788,10 +4663,10 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4800,7 +4675,7 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
@@ -4815,7 +4690,7 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4824,15 +4699,15 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4840,7 +4715,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4852,19 +4727,23 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4873,7 +4752,7 @@
         <v>79</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>79</v>
@@ -4912,7 +4791,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4921,7 +4800,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4939,7 +4818,7 @@
         <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -4948,15 +4827,15 @@
         <v>79</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4976,19 +4855,23 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -5009,7 +4892,7 @@
         <v>79</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
         <v>79</v>
@@ -5036,7 +4919,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5048,7 +4931,7 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -5063,7 +4946,7 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -5072,15 +4955,15 @@
         <v>79</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5106,12 +4989,14 @@
         <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5136,11 +5021,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -5158,7 +5043,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5182,13 +5067,13 @@
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>248</v>
+        <v>183</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>79</v>
@@ -5199,10 +5084,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5225,13 +5110,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5282,7 +5167,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5309,7 +5194,7 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5323,10 +5208,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5355,7 +5240,7 @@
         <v>137</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>139</v>
@@ -5396,19 +5281,19 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5435,7 +5320,7 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5449,10 +5334,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5475,19 +5360,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5536,7 +5421,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5563,7 +5448,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5572,15 +5457,15 @@
         <v>79</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5603,13 +5488,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5660,7 +5545,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5687,7 +5572,7 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5701,10 +5586,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5733,7 +5618,7 @@
         <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -5774,19 +5659,19 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5813,7 +5698,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5827,10 +5712,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5856,16 +5741,16 @@
         <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5914,7 +5799,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5941,7 +5826,7 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5950,15 +5835,15 @@
         <v>79</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>262</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5981,16 +5866,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6040,7 +5925,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6067,7 +5952,7 @@
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -6076,15 +5961,15 @@
         <v>79</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>269</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6110,14 +5995,14 @@
         <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6166,7 +6051,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6181,19 +6066,19 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -6202,15 +6087,15 @@
         <v>79</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>279</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6233,17 +6118,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6292,7 +6177,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6319,7 +6204,7 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6328,15 +6213,15 @@
         <v>79</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>286</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6359,19 +6244,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6420,7 +6305,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6447,7 +6332,7 @@
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6456,15 +6341,15 @@
         <v>79</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>295</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6487,19 +6372,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6548,7 +6433,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6575,7 +6460,7 @@
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6584,15 +6469,15 @@
         <v>79</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>206</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6618,14 +6503,12 @@
         <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6650,11 +6533,11 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6672,7 +6555,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6687,7 +6570,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -6696,16 +6579,16 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>79</v>
@@ -6713,10 +6596,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6736,16 +6619,16 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6772,13 +6655,11 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6796,7 +6677,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6808,7 +6689,7 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -6823,35 +6704,35 @@
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6863,17 +6744,15 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6910,31 +6789,31 @@
         <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
@@ -6949,7 +6828,7 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -6963,14 +6842,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6986,23 +6865,21 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>191</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -7038,19 +6915,19 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7062,7 +6939,7 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -7077,7 +6954,7 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7086,15 +6963,15 @@
         <v>79</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7105,7 +6982,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -7114,19 +6991,23 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -7174,19 +7055,19 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -7201,7 +7082,7 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7210,49 +7091,51 @@
         <v>79</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -7288,46 +7171,46 @@
         <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7336,15 +7219,15 @@
         <v>79</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7355,7 +7238,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7367,20 +7250,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7404,13 +7283,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7428,13 +7307,13 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -7443,7 +7322,7 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
@@ -7452,10 +7331,10 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7464,15 +7343,15 @@
         <v>79</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>262</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7483,7 +7362,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7492,20 +7371,18 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>178</v>
+        <v>307</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7554,13 +7431,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7569,7 +7446,7 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>79</v>
@@ -7578,10 +7455,10 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7590,15 +7467,15 @@
         <v>79</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7612,27 +7489,27 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>110</v>
+        <v>314</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7680,7 +7557,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7695,36 +7572,36 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>279</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7744,21 +7621,19 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7806,7 +7681,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7833,24 +7708,24 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>286</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7861,7 +7736,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -7870,23 +7745,19 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7934,13 +7805,13 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
@@ -7958,27 +7829,27 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7992,7 +7863,7 @@
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
@@ -8001,20 +7872,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>178</v>
+        <v>337</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>198</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -8062,7 +7929,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>202</v>
+        <v>336</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8077,36 +7944,36 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>205</v>
+        <v>344</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>206</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8117,10 +7984,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>79</v>
@@ -8129,13 +7996,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>171</v>
+        <v>337</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8162,11 +8029,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -8184,13 +8053,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -8199,36 +8068,36 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8242,22 +8111,22 @@
         <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>171</v>
+        <v>358</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8284,11 +8153,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>327</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8306,7 +8177,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8321,36 +8192,36 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8361,7 +8232,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8373,13 +8244,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>178</v>
+        <v>366</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>179</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>180</v>
+        <v>368</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8430,19 +8301,19 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>181</v>
+        <v>365</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8457,7 +8328,7 @@
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>176</v>
+        <v>369</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8471,24 +8342,24 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>79</v>
@@ -8497,16 +8368,16 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>136</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>183</v>
+        <v>373</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>139</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8544,49 +8415,49 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>187</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>176</v>
+        <v>378</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>79</v>
@@ -8597,10 +8468,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8611,32 +8482,30 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>190</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>191</v>
+        <v>382</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8684,13 +8553,13 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
@@ -8699,36 +8568,36 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>195</v>
+        <v>387</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>196</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8742,29 +8611,25 @@
         <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>198</v>
+        <v>390</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8812,7 +8677,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>202</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8827,40 +8692,40 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>205</v>
+        <v>387</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>206</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8876,16 +8741,16 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>171</v>
+        <v>395</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8912,13 +8777,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8936,7 +8801,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8951,7 +8816,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>343</v>
+        <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
@@ -8960,10 +8825,10 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8972,15 +8837,15 @@
         <v>79</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8988,7 +8853,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>81</v>
@@ -9003,13 +8868,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9060,10 +8925,10 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>81</v>
@@ -9072,10 +8937,10 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>404</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
@@ -9084,27 +8949,27 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9127,17 +8992,15 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>355</v>
+        <v>186</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>356</v>
+        <v>187</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9186,7 +9049,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>354</v>
+        <v>189</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9198,7 +9061,7 @@
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -9210,38 +9073,38 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>360</v>
+        <v>177</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9253,15 +9116,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>364</v>
+        <v>137</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9310,19 +9175,19 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>363</v>
+        <v>195</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
@@ -9337,28 +9202,28 @@
         <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>366</v>
+        <v>177</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9371,22 +9236,26 @@
         <v>79</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>370</v>
+        <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -9434,7 +9303,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>369</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9446,7 +9315,7 @@
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
@@ -9458,16 +9327,16 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>374</v>
+        <v>133</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>79</v>
@@ -9475,10 +9344,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9489,10 +9358,10 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>79</v>
@@ -9501,15 +9370,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>378</v>
+        <v>171</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9534,13 +9405,13 @@
         <v>79</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9558,13 +9429,13 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
@@ -9573,36 +9444,36 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>386</v>
+        <v>177</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>388</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9625,13 +9496,13 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9682,7 +9553,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9697,36 +9568,36 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>397</v>
+        <v>434</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9740,22 +9611,22 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>399</v>
+        <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9782,13 +9653,13 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>79</v>
+        <v>439</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9806,7 +9677,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9821,22 +9692,22 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>79</v>
@@ -9847,10 +9718,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9858,10 +9729,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9870,16 +9741,16 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9906,13 +9777,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>79</v>
+        <v>445</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9930,13 +9801,13 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
@@ -9957,24 +9828,24 @@
         <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>79</v>
+        <v>448</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>79</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9988,7 +9859,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>79</v>
@@ -9997,17 +9868,15 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -10056,7 +9925,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10071,22 +9940,22 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>419</v>
+        <v>177</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>79</v>
@@ -10097,10 +9966,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10111,10 +9980,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -10123,16 +9992,16 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>178</v>
+        <v>451</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>423</v>
+        <v>456</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>424</v>
+        <v>457</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10182,13 +10051,13 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
@@ -10197,1530 +10066,32 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M73" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AR74" t="s" s="2">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR78">
+  <autoFilter ref="A1:AR66">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11730,7 +10101,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1698,7 +1698,7 @@
     <t>Appointment.participant:va-clinic.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
@@ -1780,7 +1780,7 @@
     <t>Appointment.participant:va-patient.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file APPOINTMENT (2.98) to Appointment</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to Appointment</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1605,6 +1605,121 @@
     <t>Participation period of the actor.</t>
   </si>
   <si>
+    <t>Appointment.participant:va-patient</t>
+  </si>
+  <si>
+    <t>va-patient</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.code</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.code</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>1722-1: fixed value = #PART</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.actor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+</t>
+  </si>
+  <si>
+    <t>1722: reference from PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.required</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.status</t>
+  </si>
+  <si>
+    <t>accepted</t>
+  </si>
+  <si>
+    <t>1722-2: fixed value = #accepted</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.period</t>
+  </si>
+  <si>
     <t>Appointment.participant:va-clinic</t>
   </si>
   <si>
@@ -1626,73 +1741,37 @@
     <t>Appointment.participant:va-clinic.type.id</t>
   </si>
   <si>
-    <t>Appointment.participant.type.id</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.extension</t>
   </si>
   <si>
-    <t>Appointment.participant.type.extension</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding.id</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.id</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding.extension</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.extension</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding.system</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.system</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding.version</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.version</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding.code</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.code</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
     <t>746-1: fixed value = #PART</t>
   </si>
   <si>
     <t>Appointment.participant:va-clinic.type.coding.display</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.display</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.coding.userSelected</t>
   </si>
   <si>
-    <t>Appointment.participant.type.coding.userSelected</t>
-  </si>
-  <si>
     <t>Appointment.participant:va-clinic.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.text</t>
   </si>
   <si>
     <t>Appointment.participant:va-clinic.actor</t>
@@ -1714,89 +1793,10 @@
     <t>Appointment.participant:va-clinic.status</t>
   </si>
   <si>
-    <t>accepted</t>
-  </si>
-  <si>
     <t>746-2: fixed value = #accepted</t>
   </si>
   <si>
     <t>Appointment.participant:va-clinic.period</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient</t>
-  </si>
-  <si>
-    <t>va-patient</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.code</t>
-  </si>
-  <si>
-    <t>1722-1: fixed value = #PART</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.actor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
-</t>
-  </si>
-  <si>
-    <t>1722: reference from PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.required</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.status</t>
-  </si>
-  <si>
-    <t>1722-2: fixed value = #accepted</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.period</t>
   </si>
   <si>
     <t>Appointment.participant:va-appt-clinic</t>
@@ -15487,7 +15487,7 @@
         <v>544</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -15507,7 +15507,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>493</v>
@@ -15628,7 +15628,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>500</v>
@@ -15672,7 +15672,7 @@
         <v>78</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>78</v>
@@ -15726,7 +15726,7 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>78</v>
@@ -15749,7 +15749,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>508</v>
@@ -15870,13 +15870,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>460</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>78</v>
@@ -15993,7 +15993,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>469</v>
@@ -16114,7 +16114,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>470</v>
@@ -16237,7 +16237,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>471</v>
@@ -16362,7 +16362,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>476</v>
@@ -16485,7 +16485,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>519</v>
@@ -16606,7 +16606,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>521</v>
@@ -16729,7 +16729,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>523</v>
@@ -16854,7 +16854,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>525</v>
@@ -16975,7 +16975,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>527</v>
@@ -17098,7 +17098,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>529</v>
@@ -17223,7 +17223,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>531</v>
@@ -17346,7 +17346,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>533</v>
@@ -17446,7 +17446,7 @@
         <v>101</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>78</v>
@@ -17469,7 +17469,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>537</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>539</v>
@@ -17717,7 +17717,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>541</v>
@@ -17842,7 +17842,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>485</v>
@@ -17868,7 +17868,7 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>487</v>
@@ -17940,10 +17940,10 @@
         <v>101</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AL128" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>78</v>
@@ -18128,7 +18128,7 @@
         <v>78</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>78</v>
@@ -20324,7 +20324,7 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="L148" t="s" s="2">
         <v>487</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,10 +527,6 @@
     <t>Appt.WaitList.PatientIEN</t>
   </si>
   <si>
-    <t>appointment.apptStatus
-appointment.patientClass</t>
-  </si>
-  <si>
     <t>Request.status</t>
   </si>
   <si>
@@ -768,7 +764,8 @@
 Dim.Location.MedicalService,Dim.Location.MedicalService</t>
   </si>
   <si>
-    <t>appointment.service</t>
+    <t>Dim.Location.MedicalService
+Dim.Location.MedicalService</t>
   </si>
   <si>
     <t>./code</t>
@@ -992,7 +989,7 @@
 Dim.Location.PrimaryStopCodeIEN</t>
   </si>
   <si>
-    <t>appointment.clinStop</t>
+    <t>Dim.Location.PrimaryStopCodeIEN</t>
   </si>
   <si>
     <t>Appointment.serviceType:va-stop-code.coding.display</t>
@@ -1056,6 +1053,9 @@
 Dim.Location.SecondaryStopCodeIEN</t>
   </si>
   <si>
+    <t>Dim.Location.SecondaryStopCodeIEN</t>
+  </si>
+  <si>
     <t>Appointment.serviceType:va-credit-stop-code.coding.display</t>
   </si>
   <si>
@@ -1126,7 +1126,7 @@
 Dim.AppointmentType.AppointmentType</t>
   </si>
   <si>
-    <t>appointment.type</t>
+    <t>Dim.AppointmentType.AppointmentType</t>
   </si>
   <si>
     <t>Appointment.reasonCode</t>
@@ -1276,9 +1276,6 @@
     <t>Appt.Appointment.AppointmentDateTime</t>
   </si>
   <si>
-    <t>appointment.dateTime</t>
-  </si>
-  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -1308,6 +1305,10 @@
   <si>
     <t>Appt.Appointment.VisitIEN
 Outpat.Visit.COProcessCompleteDateTime,Outpat.Workload.COProcessCompleteDateTime</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.COProcessCompleteDateTime
+Outpat.Workload.COProcessCompleteDateTime</t>
   </si>
   <si>
     <t>.effectiveTime.high</t>
@@ -2269,7 +2270,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="145.37109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="44.71875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="110.08203125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="155.20703125" customWidth="true" bestFit="true"/>
@@ -3773,30 +3774,30 @@
         <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AP12" t="s" s="2">
+      <c r="AQ12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AQ12" t="s" s="2">
+      <c r="AR12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AR12" t="s" s="2">
-        <v>169</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3819,13 +3820,13 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3856,7 +3857,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3874,7 +3875,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3889,19 +3890,19 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3915,10 +3916,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3941,13 +3942,13 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3974,27 +3975,27 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4021,10 +4022,10 @@
         <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>79</v>
@@ -4035,13 +4036,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>79</v>
@@ -4063,13 +4064,13 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4096,11 +4097,11 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -4118,7 +4119,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4145,10 +4146,10 @@
         <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>79</v>
@@ -4159,10 +4160,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4185,13 +4186,13 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4242,7 +4243,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4269,7 +4270,7 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -4283,10 +4284,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4315,7 +4316,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>139</v>
@@ -4356,19 +4357,19 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC17" t="s" s="2">
+      <c r="AD17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4395,7 +4396,7 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -4409,10 +4410,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4435,19 +4436,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -4496,7 +4497,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4523,24 +4524,24 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR18" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4563,13 +4564,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4620,7 +4621,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4647,7 +4648,7 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4661,10 +4662,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4693,7 +4694,7 @@
         <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>139</v>
@@ -4734,19 +4735,19 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC20" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC20" t="s" s="2">
+      <c r="AD20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4773,7 +4774,7 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4787,10 +4788,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4816,16 +4817,16 @@
         <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4835,46 +4836,46 @@
         <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4889,36 +4890,36 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4941,16 +4942,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5000,7 +5001,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5027,24 +5028,24 @@
         <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5070,14 +5071,14 @@
         <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -5126,7 +5127,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5141,36 +5142,36 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5193,17 +5194,17 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5252,7 +5253,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5279,24 +5280,24 @@
         <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5319,19 +5320,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5380,7 +5381,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5407,24 +5408,24 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5447,19 +5448,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5508,7 +5509,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5535,27 +5536,27 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
@@ -5577,13 +5578,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5610,11 +5611,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -5632,7 +5633,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5659,10 +5660,10 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>79</v>
@@ -5673,10 +5674,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5699,13 +5700,13 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5756,7 +5757,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5783,7 +5784,7 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5797,10 +5798,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5829,7 +5830,7 @@
         <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>139</v>
@@ -5870,19 +5871,19 @@
         <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5909,7 +5910,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5923,10 +5924,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5949,19 +5950,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -6010,7 +6011,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6037,24 +6038,24 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6077,13 +6078,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6134,7 +6135,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6161,7 +6162,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -6175,10 +6176,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6207,7 +6208,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -6248,19 +6249,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC32" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC32" t="s" s="2">
+      <c r="AD32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6287,7 +6288,7 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -6301,10 +6302,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6330,16 +6331,16 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -6349,7 +6350,7 @@
         <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>79</v>
@@ -6388,7 +6389,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6403,7 +6404,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -6415,24 +6416,24 @@
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6455,16 +6456,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6514,7 +6515,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6541,24 +6542,24 @@
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6584,14 +6585,14 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6640,7 +6641,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6655,11 +6656,11 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
       </c>
@@ -6667,24 +6668,24 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6707,17 +6708,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6766,7 +6767,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6793,24 +6794,24 @@
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6833,19 +6834,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6894,7 +6895,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6921,24 +6922,24 @@
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6961,19 +6962,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7022,7 +7023,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7049,24 +7050,24 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7089,16 +7090,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7124,27 +7125,27 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7168,10 +7169,10 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -7185,13 +7186,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>79</v>
@@ -7213,16 +7214,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7248,11 +7249,11 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -7270,7 +7271,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7294,10 +7295,10 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -7311,10 +7312,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7337,13 +7338,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7394,7 +7395,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7421,7 +7422,7 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7435,10 +7436,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7467,7 +7468,7 @@
         <v>137</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -7508,19 +7509,19 @@
         <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC42" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC42" t="s" s="2">
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7547,7 +7548,7 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7561,10 +7562,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7587,19 +7588,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7648,7 +7649,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7675,24 +7676,24 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7715,13 +7716,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7772,7 +7773,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7799,7 +7800,7 @@
         <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7813,10 +7814,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7845,7 +7846,7 @@
         <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>139</v>
@@ -7886,19 +7887,19 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC45" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC45" t="s" s="2">
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7925,7 +7926,7 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7939,10 +7940,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7968,16 +7969,16 @@
         <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7987,7 +7988,7 @@
         <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>79</v>
@@ -8026,7 +8027,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8041,7 +8042,7 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
@@ -8053,24 +8054,24 @@
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8093,16 +8094,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8152,7 +8153,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8179,24 +8180,24 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8222,14 +8223,14 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8278,7 +8279,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8293,36 +8294,36 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8345,17 +8346,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -8404,7 +8405,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8431,24 +8432,24 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8471,19 +8472,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8532,7 +8533,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8559,24 +8560,24 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8599,19 +8600,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8660,7 +8661,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8687,27 +8688,27 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>79</v>
@@ -8729,16 +8730,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8764,11 +8765,11 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -8786,7 +8787,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8810,10 +8811,10 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8827,10 +8828,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8853,13 +8854,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8910,7 +8911,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8937,7 +8938,7 @@
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -8951,10 +8952,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8983,7 +8984,7 @@
         <v>137</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -9024,19 +9025,19 @@
         <v>79</v>
       </c>
       <c r="AB54" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC54" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC54" t="s" s="2">
+      <c r="AD54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9063,7 +9064,7 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -9077,10 +9078,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9103,19 +9104,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9164,7 +9165,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9191,24 +9192,24 @@
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR55" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9231,13 +9232,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9288,7 +9289,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9315,7 +9316,7 @@
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -9329,10 +9330,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9361,7 +9362,7 @@
         <v>137</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>139</v>
@@ -9402,19 +9403,19 @@
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC57" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC57" t="s" s="2">
+      <c r="AD57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9441,7 +9442,7 @@
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -9455,10 +9456,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9484,16 +9485,16 @@
         <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9503,7 +9504,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9542,7 +9543,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9557,7 +9558,7 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>79</v>
@@ -9569,24 +9570,24 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR58" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR58" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9609,16 +9610,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9668,7 +9669,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9695,24 +9696,24 @@
         <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR59" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9738,14 +9739,14 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9794,7 +9795,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9809,28 +9810,28 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9838,7 +9839,7 @@
         <v>337</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9861,17 +9862,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9920,7 +9921,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9947,16 +9948,16 @@
         <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9964,7 +9965,7 @@
         <v>338</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9987,19 +9988,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10048,7 +10049,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10075,16 +10076,16 @@
         <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -10092,7 +10093,7 @@
         <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10115,19 +10116,19 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10176,7 +10177,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10203,16 +10204,16 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -10243,7 +10244,7 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>341</v>
@@ -10365,7 +10366,7 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>348</v>
@@ -10487,13 +10488,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10544,7 +10545,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10571,7 +10572,7 @@
         <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10617,7 +10618,7 @@
         <v>137</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>139</v>
@@ -10658,19 +10659,19 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC67" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC67" t="s" s="2">
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10697,7 +10698,7 @@
         <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -10737,19 +10738,19 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10798,7 +10799,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10825,16 +10826,16 @@
         <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10865,19 +10866,19 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10926,7 +10927,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10953,16 +10954,16 @@
         <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -10993,7 +10994,7 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>362</v>
@@ -11367,7 +11368,7 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>387</v>
@@ -11693,30 +11694,30 @@
         <v>407</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AO75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AQ75" t="s" s="2">
+      <c r="AR75" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11742,10 +11743,10 @@
         <v>403</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11796,7 +11797,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11811,16 +11812,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AN76" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>419</v>
@@ -11944,7 +11945,7 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>429</v>
@@ -12237,7 +12238,7 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>447</v>
@@ -12363,7 +12364,7 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>456</v>
@@ -12656,14 +12657,14 @@
         <v>79</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>466</v>
@@ -12733,13 +12734,13 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12790,7 +12791,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12817,7 +12818,7 @@
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -12863,7 +12864,7 @@
         <v>137</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>139</v>
@@ -12916,7 +12917,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12943,7 +12944,7 @@
         <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13111,7 +13112,7 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>483</v>
@@ -13200,7 +13201,7 @@
         <v>489</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>79</v>
@@ -13693,7 +13694,7 @@
         <v>79</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>79</v>
@@ -13859,13 +13860,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13916,7 +13917,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13943,7 +13944,7 @@
         <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -13989,7 +13990,7 @@
         <v>137</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>139</v>
@@ -14042,7 +14043,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14069,7 +14070,7 @@
         <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14237,7 +14238,7 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>483</v>
@@ -14326,7 +14327,7 @@
         <v>489</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>79</v>
@@ -14363,13 +14364,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14420,7 +14421,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14447,7 +14448,7 @@
         <v>79</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>79</v>
@@ -14493,7 +14494,7 @@
         <v>137</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>139</v>
@@ -14534,19 +14535,19 @@
         <v>79</v>
       </c>
       <c r="AB98" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC98" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC98" t="s" s="2">
+      <c r="AD98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14573,7 +14574,7 @@
         <v>79</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>79</v>
@@ -14613,19 +14614,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -14674,7 +14675,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14701,16 +14702,16 @@
         <v>79</v>
       </c>
       <c r="AO99" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="100" hidden="true">
@@ -14741,13 +14742,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14798,7 +14799,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14825,7 +14826,7 @@
         <v>79</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>79</v>
@@ -14871,7 +14872,7 @@
         <v>137</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>139</v>
@@ -14912,19 +14913,19 @@
         <v>79</v>
       </c>
       <c r="AB101" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC101" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC101" t="s" s="2">
+      <c r="AD101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14951,7 +14952,7 @@
         <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>79</v>
@@ -14994,16 +14995,16 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15052,7 +15053,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15079,16 +15080,16 @@
         <v>79</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR102" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -15119,16 +15120,16 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15178,7 +15179,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15205,16 +15206,16 @@
         <v>79</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR103" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR103" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -15248,14 +15249,14 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -15304,7 +15305,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15331,16 +15332,16 @@
         <v>79</v>
       </c>
       <c r="AO104" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR104" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR104" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="105" hidden="true">
@@ -15371,17 +15372,17 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -15430,7 +15431,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15457,16 +15458,16 @@
         <v>79</v>
       </c>
       <c r="AO105" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR105" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR105" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -15497,19 +15498,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -15558,7 +15559,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15585,16 +15586,16 @@
         <v>79</v>
       </c>
       <c r="AO106" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR106" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR106" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="107" hidden="true">
@@ -15625,19 +15626,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15686,7 +15687,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15713,16 +15714,16 @@
         <v>79</v>
       </c>
       <c r="AO107" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR107" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR107" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="108" hidden="true">
@@ -16209,7 +16210,7 @@
         <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>79</v>
@@ -16375,13 +16376,13 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16432,7 +16433,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16459,7 +16460,7 @@
         <v>79</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>79</v>
@@ -16505,7 +16506,7 @@
         <v>137</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>139</v>
@@ -16558,7 +16559,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16585,7 +16586,7 @@
         <v>79</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>79</v>
@@ -16753,7 +16754,7 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>483</v>
@@ -16842,7 +16843,7 @@
         <v>489</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>79</v>
@@ -16879,13 +16880,13 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16936,7 +16937,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16963,7 +16964,7 @@
         <v>79</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>79</v>
@@ -17009,7 +17010,7 @@
         <v>137</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>139</v>
@@ -17050,19 +17051,19 @@
         <v>79</v>
       </c>
       <c r="AB118" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC118" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC118" t="s" s="2">
+      <c r="AD118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17089,7 +17090,7 @@
         <v>79</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>79</v>
@@ -17129,19 +17130,19 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17190,7 +17191,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17217,16 +17218,16 @@
         <v>79</v>
       </c>
       <c r="AO119" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR119" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR119" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="120" hidden="true">
@@ -17257,13 +17258,13 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L120" t="s" s="2">
+      <c r="M120" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17314,7 +17315,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17341,7 +17342,7 @@
         <v>79</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>79</v>
@@ -17387,7 +17388,7 @@
         <v>137</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>139</v>
@@ -17428,19 +17429,19 @@
         <v>79</v>
       </c>
       <c r="AB121" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC121" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC121" t="s" s="2">
+      <c r="AD121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17467,7 +17468,7 @@
         <v>79</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>79</v>
@@ -17510,16 +17511,16 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17568,7 +17569,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17595,16 +17596,16 @@
         <v>79</v>
       </c>
       <c r="AO122" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR122" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR122" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="123" hidden="true">
@@ -17635,16 +17636,16 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17694,7 +17695,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17721,16 +17722,16 @@
         <v>79</v>
       </c>
       <c r="AO123" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR123" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR123" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="124" hidden="true">
@@ -17764,14 +17765,14 @@
         <v>110</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17820,7 +17821,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17847,16 +17848,16 @@
         <v>79</v>
       </c>
       <c r="AO124" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR124" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR124" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="125" hidden="true">
@@ -17887,17 +17888,17 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17946,7 +17947,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17973,16 +17974,16 @@
         <v>79</v>
       </c>
       <c r="AO125" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR125" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR125" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -18013,19 +18014,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
@@ -18074,7 +18075,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -18101,16 +18102,16 @@
         <v>79</v>
       </c>
       <c r="AO126" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR126" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR126" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="127" hidden="true">
@@ -18141,19 +18142,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -18202,7 +18203,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18229,16 +18230,16 @@
         <v>79</v>
       </c>
       <c r="AO127" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR127" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR127" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="128" hidden="true">
@@ -18725,7 +18726,7 @@
         <v>79</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>79</v>
@@ -18891,13 +18892,13 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18948,7 +18949,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18975,7 +18976,7 @@
         <v>79</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>79</v>
@@ -19021,7 +19022,7 @@
         <v>137</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>139</v>
@@ -19074,7 +19075,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19101,7 +19102,7 @@
         <v>79</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>79</v>
@@ -19269,7 +19270,7 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>483</v>
@@ -19358,7 +19359,7 @@
         <v>489</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>79</v>
@@ -19395,13 +19396,13 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19452,7 +19453,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19479,7 +19480,7 @@
         <v>79</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>79</v>
@@ -19525,7 +19526,7 @@
         <v>137</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>139</v>
@@ -19566,19 +19567,19 @@
         <v>79</v>
       </c>
       <c r="AB138" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC138" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC138" t="s" s="2">
+      <c r="AD138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF138" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19605,7 +19606,7 @@
         <v>79</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>79</v>
@@ -19645,19 +19646,19 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
@@ -19706,7 +19707,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19733,16 +19734,16 @@
         <v>79</v>
       </c>
       <c r="AO139" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR139" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR139" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="140" hidden="true">
@@ -19773,13 +19774,13 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19830,7 +19831,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19857,7 +19858,7 @@
         <v>79</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>79</v>
@@ -19903,7 +19904,7 @@
         <v>137</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>139</v>
@@ -19944,19 +19945,19 @@
         <v>79</v>
       </c>
       <c r="AB141" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC141" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AC141" t="s" s="2">
+      <c r="AD141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF141" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19983,7 +19984,7 @@
         <v>79</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>79</v>
@@ -20026,16 +20027,16 @@
         <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>79</v>
@@ -20084,7 +20085,7 @@
         <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20111,16 +20112,16 @@
         <v>79</v>
       </c>
       <c r="AO142" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR142" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR142" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -20151,16 +20152,16 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -20210,7 +20211,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20237,16 +20238,16 @@
         <v>79</v>
       </c>
       <c r="AO143" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR143" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR143" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="144" hidden="true">
@@ -20280,14 +20281,14 @@
         <v>110</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -20336,7 +20337,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20363,16 +20364,16 @@
         <v>79</v>
       </c>
       <c r="AO144" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AP144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR144" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AP144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR144" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="145" hidden="true">
@@ -20403,17 +20404,17 @@
         <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20462,7 +20463,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20489,16 +20490,16 @@
         <v>79</v>
       </c>
       <c r="AO145" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR145" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR145" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="146" hidden="true">
@@ -20529,19 +20530,19 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20590,7 +20591,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20617,16 +20618,16 @@
         <v>79</v>
       </c>
       <c r="AO146" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR146" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR146" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="147" hidden="true">
@@ -20657,19 +20658,19 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20718,7 +20719,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20745,16 +20746,16 @@
         <v>79</v>
       </c>
       <c r="AO147" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR147" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR147" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="148" hidden="true">
@@ -21241,7 +21242,7 @@
         <v>79</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>79</v>
@@ -21364,7 +21365,7 @@
         <v>79</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>612</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,6 +527,10 @@
     <t>Appt.WaitList.PatientIEN</t>
   </si>
   <si>
+    <t>appointment.apptStatus
+appointment.patientClass</t>
+  </si>
+  <si>
     <t>Request.status</t>
   </si>
   <si>
@@ -764,8 +768,7 @@
 Dim.Location.MedicalService,Dim.Location.MedicalService</t>
   </si>
   <si>
-    <t>Dim.Location.MedicalService
-Dim.Location.MedicalService</t>
+    <t>appointment.service</t>
   </si>
   <si>
     <t>./code</t>
@@ -989,7 +992,7 @@
 Dim.Location.PrimaryStopCodeIEN</t>
   </si>
   <si>
-    <t>Dim.Location.PrimaryStopCodeIEN</t>
+    <t>appointment.clinStop</t>
   </si>
   <si>
     <t>Appointment.serviceType:va-stop-code.coding.display</t>
@@ -1053,9 +1056,6 @@
 Dim.Location.SecondaryStopCodeIEN</t>
   </si>
   <si>
-    <t>Dim.Location.SecondaryStopCodeIEN</t>
-  </si>
-  <si>
     <t>Appointment.serviceType:va-credit-stop-code.coding.display</t>
   </si>
   <si>
@@ -1126,7 +1126,7 @@
 Dim.AppointmentType.AppointmentType</t>
   </si>
   <si>
-    <t>Dim.AppointmentType.AppointmentType</t>
+    <t>appointment.type</t>
   </si>
   <si>
     <t>Appointment.reasonCode</t>
@@ -1276,6 +1276,9 @@
     <t>Appt.Appointment.AppointmentDateTime</t>
   </si>
   <si>
+    <t>appointment.dateTime</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -1305,10 +1308,6 @@
   <si>
     <t>Appt.Appointment.VisitIEN
 Outpat.Visit.COProcessCompleteDateTime,Outpat.Workload.COProcessCompleteDateTime</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.COProcessCompleteDateTime
-Outpat.Workload.COProcessCompleteDateTime</t>
   </si>
   <si>
     <t>.effectiveTime.high</t>
@@ -2270,7 +2269,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="145.37109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="44.71875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="110.08203125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="155.20703125" customWidth="true" bestFit="true"/>
@@ -3774,30 +3773,30 @@
         <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3820,13 +3819,13 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3857,7 +3856,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3875,7 +3874,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3890,10 +3889,10 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>79</v>
@@ -3902,7 +3901,7 @@
         <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3916,10 +3915,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3942,13 +3941,13 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3975,27 +3974,27 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4022,10 +4021,10 @@
         <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>79</v>
@@ -4036,13 +4035,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>79</v>
@@ -4064,13 +4063,13 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4097,11 +4096,11 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -4119,7 +4118,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4146,10 +4145,10 @@
         <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>79</v>
@@ -4160,10 +4159,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4186,13 +4185,13 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4243,7 +4242,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4270,7 +4269,7 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -4284,10 +4283,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4316,7 +4315,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>139</v>
@@ -4357,19 +4356,19 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4396,7 +4395,7 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -4410,10 +4409,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4436,19 +4435,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -4497,7 +4496,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4524,7 +4523,7 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4533,15 +4532,15 @@
         <v>79</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4564,13 +4563,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4621,7 +4620,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4648,7 +4647,7 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4662,10 +4661,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4694,7 +4693,7 @@
         <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>139</v>
@@ -4735,19 +4734,19 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4774,7 +4773,7 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4788,10 +4787,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4817,16 +4816,16 @@
         <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4836,7 +4835,7 @@
         <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>79</v>
@@ -4875,7 +4874,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4890,7 +4889,7 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
@@ -4902,7 +4901,7 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4911,15 +4910,15 @@
         <v>79</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4942,16 +4941,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5001,7 +5000,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5028,7 +5027,7 @@
         <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -5037,15 +5036,15 @@
         <v>79</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5071,14 +5070,14 @@
         <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -5127,7 +5126,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5142,19 +5141,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -5163,15 +5162,15 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5194,17 +5193,17 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5253,7 +5252,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5280,7 +5279,7 @@
         <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -5289,15 +5288,15 @@
         <v>79</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5320,19 +5319,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5381,7 +5380,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5408,7 +5407,7 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -5417,15 +5416,15 @@
         <v>79</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5448,19 +5447,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5509,7 +5508,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5536,7 +5535,7 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5545,18 +5544,18 @@
         <v>79</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
@@ -5578,13 +5577,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5611,11 +5610,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -5633,7 +5632,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5660,10 +5659,10 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>79</v>
@@ -5674,10 +5673,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5700,13 +5699,13 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5757,7 +5756,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5784,7 +5783,7 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5798,10 +5797,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5830,7 +5829,7 @@
         <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>139</v>
@@ -5871,19 +5870,19 @@
         <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5910,7 +5909,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5924,10 +5923,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5950,19 +5949,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -6011,7 +6010,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6038,7 +6037,7 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -6047,15 +6046,15 @@
         <v>79</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6078,13 +6077,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6135,7 +6134,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6162,7 +6161,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -6176,10 +6175,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6208,7 +6207,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -6249,19 +6248,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6288,7 +6287,7 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -6302,10 +6301,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6331,16 +6330,16 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -6350,7 +6349,7 @@
         <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>79</v>
@@ -6389,7 +6388,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6404,7 +6403,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -6416,7 +6415,7 @@
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -6425,15 +6424,15 @@
         <v>79</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6456,16 +6455,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6515,7 +6514,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6542,7 +6541,7 @@
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -6551,15 +6550,15 @@
         <v>79</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6585,14 +6584,14 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6641,7 +6640,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6656,10 +6655,10 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -6668,7 +6667,7 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6677,15 +6676,15 @@
         <v>79</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6708,17 +6707,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6767,7 +6766,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6794,7 +6793,7 @@
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6803,15 +6802,15 @@
         <v>79</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6834,19 +6833,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6895,7 +6894,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6922,7 +6921,7 @@
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6931,15 +6930,15 @@
         <v>79</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6962,19 +6961,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7023,7 +7022,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7050,7 +7049,7 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -7059,15 +7058,15 @@
         <v>79</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7090,16 +7089,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7125,27 +7124,27 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7169,10 +7168,10 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -7186,13 +7185,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>79</v>
@@ -7214,16 +7213,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7249,11 +7248,11 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -7271,7 +7270,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7295,10 +7294,10 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -7312,10 +7311,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7338,13 +7337,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7395,7 +7394,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7422,7 +7421,7 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7436,10 +7435,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7468,7 +7467,7 @@
         <v>137</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -7509,19 +7508,19 @@
         <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7548,7 +7547,7 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7562,10 +7561,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7588,19 +7587,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7649,7 +7648,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7676,7 +7675,7 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7685,15 +7684,15 @@
         <v>79</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7716,13 +7715,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7773,7 +7772,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7800,7 +7799,7 @@
         <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7814,10 +7813,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7846,7 +7845,7 @@
         <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>139</v>
@@ -7887,19 +7886,19 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7926,7 +7925,7 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7940,10 +7939,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7969,16 +7968,16 @@
         <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7988,7 +7987,7 @@
         <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>79</v>
@@ -8027,7 +8026,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8042,7 +8041,7 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
@@ -8054,7 +8053,7 @@
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8063,15 +8062,15 @@
         <v>79</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8094,16 +8093,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8153,7 +8152,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8180,7 +8179,7 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8189,15 +8188,15 @@
         <v>79</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8223,14 +8222,14 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8279,7 +8278,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8294,19 +8293,19 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -8315,15 +8314,15 @@
         <v>79</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8346,17 +8345,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -8405,7 +8404,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8432,7 +8431,7 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
@@ -8441,15 +8440,15 @@
         <v>79</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8472,19 +8471,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8533,7 +8532,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8560,7 +8559,7 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>79</v>
@@ -8569,15 +8568,15 @@
         <v>79</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8600,19 +8599,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8661,7 +8660,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8688,7 +8687,7 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -8697,18 +8696,18 @@
         <v>79</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>79</v>
@@ -8730,16 +8729,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8765,11 +8764,11 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -8787,7 +8786,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8811,10 +8810,10 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8828,10 +8827,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8854,13 +8853,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8911,7 +8910,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8938,7 +8937,7 @@
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -8952,10 +8951,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8984,7 +8983,7 @@
         <v>137</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -9025,19 +9024,19 @@
         <v>79</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9064,7 +9063,7 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -9078,10 +9077,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9104,19 +9103,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9165,7 +9164,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9192,7 +9191,7 @@
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -9201,15 +9200,15 @@
         <v>79</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9232,13 +9231,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9289,7 +9288,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9316,7 +9315,7 @@
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -9330,10 +9329,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9362,7 +9361,7 @@
         <v>137</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>139</v>
@@ -9403,19 +9402,19 @@
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9442,7 +9441,7 @@
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -9456,10 +9455,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9485,16 +9484,16 @@
         <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9504,7 +9503,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9543,7 +9542,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9558,7 +9557,7 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>79</v>
@@ -9570,7 +9569,7 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -9579,15 +9578,15 @@
         <v>79</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9610,16 +9609,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9669,7 +9668,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9696,7 +9695,7 @@
         <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>79</v>
@@ -9705,15 +9704,15 @@
         <v>79</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9739,14 +9738,14 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9795,7 +9794,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9810,19 +9809,19 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9831,7 +9830,7 @@
         <v>79</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9839,7 +9838,7 @@
         <v>337</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9862,17 +9861,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9921,7 +9920,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9948,7 +9947,7 @@
         <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>79</v>
@@ -9957,7 +9956,7 @@
         <v>79</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9965,7 +9964,7 @@
         <v>338</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9988,19 +9987,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10049,7 +10048,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10076,7 +10075,7 @@
         <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>79</v>
@@ -10085,7 +10084,7 @@
         <v>79</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -10093,7 +10092,7 @@
         <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10116,19 +10115,19 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10177,7 +10176,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10204,7 +10203,7 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>79</v>
@@ -10213,7 +10212,7 @@
         <v>79</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -10244,7 +10243,7 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>341</v>
@@ -10366,7 +10365,7 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>348</v>
@@ -10488,13 +10487,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10545,7 +10544,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10572,7 +10571,7 @@
         <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10618,7 +10617,7 @@
         <v>137</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>139</v>
@@ -10659,19 +10658,19 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10698,7 +10697,7 @@
         <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -10738,19 +10737,19 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10799,7 +10798,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10826,7 +10825,7 @@
         <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -10835,7 +10834,7 @@
         <v>79</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10866,19 +10865,19 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10927,7 +10926,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10954,7 +10953,7 @@
         <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>79</v>
@@ -10963,7 +10962,7 @@
         <v>79</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -10994,7 +10993,7 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>362</v>
@@ -11368,7 +11367,7 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>387</v>
@@ -11694,30 +11693,30 @@
         <v>407</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11743,10 +11742,10 @@
         <v>403</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11797,7 +11796,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11812,16 +11811,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>419</v>
@@ -11945,7 +11944,7 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>429</v>
@@ -12238,7 +12237,7 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>447</v>
@@ -12364,7 +12363,7 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>456</v>
@@ -12657,14 +12656,14 @@
         <v>79</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>466</v>
@@ -12734,13 +12733,13 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12791,7 +12790,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12818,7 +12817,7 @@
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -12864,7 +12863,7 @@
         <v>137</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>139</v>
@@ -12917,7 +12916,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12944,7 +12943,7 @@
         <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13112,7 +13111,7 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>483</v>
@@ -13201,7 +13200,7 @@
         <v>489</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>79</v>
@@ -13694,7 +13693,7 @@
         <v>79</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>79</v>
@@ -13860,13 +13859,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13917,7 +13916,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13944,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -13990,7 +13989,7 @@
         <v>137</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>139</v>
@@ -14043,7 +14042,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14070,7 +14069,7 @@
         <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14238,7 +14237,7 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>483</v>
@@ -14327,7 +14326,7 @@
         <v>489</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>79</v>
@@ -14364,13 +14363,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14421,7 +14420,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14448,7 +14447,7 @@
         <v>79</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>79</v>
@@ -14494,7 +14493,7 @@
         <v>137</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>139</v>
@@ -14535,19 +14534,19 @@
         <v>79</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14574,7 +14573,7 @@
         <v>79</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>79</v>
@@ -14614,19 +14613,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -14675,7 +14674,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14702,7 +14701,7 @@
         <v>79</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>79</v>
@@ -14711,7 +14710,7 @@
         <v>79</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" hidden="true">
@@ -14742,13 +14741,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14799,7 +14798,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14826,7 +14825,7 @@
         <v>79</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>79</v>
@@ -14872,7 +14871,7 @@
         <v>137</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>139</v>
@@ -14913,19 +14912,19 @@
         <v>79</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14952,7 +14951,7 @@
         <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>79</v>
@@ -14995,16 +14994,16 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15053,7 +15052,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15080,7 +15079,7 @@
         <v>79</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15089,7 +15088,7 @@
         <v>79</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -15120,16 +15119,16 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15179,7 +15178,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15206,7 +15205,7 @@
         <v>79</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15215,7 +15214,7 @@
         <v>79</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -15249,14 +15248,14 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -15305,7 +15304,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15332,7 +15331,7 @@
         <v>79</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15341,7 +15340,7 @@
         <v>79</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" hidden="true">
@@ -15372,17 +15371,17 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -15431,7 +15430,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15458,7 +15457,7 @@
         <v>79</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15467,7 +15466,7 @@
         <v>79</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -15498,19 +15497,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -15559,7 +15558,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15586,7 +15585,7 @@
         <v>79</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>79</v>
@@ -15595,7 +15594,7 @@
         <v>79</v>
       </c>
       <c r="AR106" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="107" hidden="true">
@@ -15626,19 +15625,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15687,7 +15686,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15714,7 +15713,7 @@
         <v>79</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>79</v>
@@ -15723,7 +15722,7 @@
         <v>79</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108" hidden="true">
@@ -16210,7 +16209,7 @@
         <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>79</v>
@@ -16376,13 +16375,13 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16433,7 +16432,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16460,7 +16459,7 @@
         <v>79</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>79</v>
@@ -16506,7 +16505,7 @@
         <v>137</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>139</v>
@@ -16559,7 +16558,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16586,7 +16585,7 @@
         <v>79</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>79</v>
@@ -16754,7 +16753,7 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>483</v>
@@ -16843,7 +16842,7 @@
         <v>489</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>79</v>
@@ -16880,13 +16879,13 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16937,7 +16936,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16964,7 +16963,7 @@
         <v>79</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>79</v>
@@ -17010,7 +17009,7 @@
         <v>137</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>139</v>
@@ -17051,19 +17050,19 @@
         <v>79</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17090,7 +17089,7 @@
         <v>79</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>79</v>
@@ -17130,19 +17129,19 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17191,7 +17190,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17218,7 +17217,7 @@
         <v>79</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>79</v>
@@ -17227,7 +17226,7 @@
         <v>79</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" hidden="true">
@@ -17258,13 +17257,13 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17315,7 +17314,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17342,7 +17341,7 @@
         <v>79</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>79</v>
@@ -17388,7 +17387,7 @@
         <v>137</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>139</v>
@@ -17429,19 +17428,19 @@
         <v>79</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17468,7 +17467,7 @@
         <v>79</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>79</v>
@@ -17511,16 +17510,16 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17569,7 +17568,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17596,7 +17595,7 @@
         <v>79</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>79</v>
@@ -17605,7 +17604,7 @@
         <v>79</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="123" hidden="true">
@@ -17636,16 +17635,16 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17695,7 +17694,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17722,7 +17721,7 @@
         <v>79</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>79</v>
@@ -17731,7 +17730,7 @@
         <v>79</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="124" hidden="true">
@@ -17765,14 +17764,14 @@
         <v>110</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17821,7 +17820,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17848,7 +17847,7 @@
         <v>79</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>79</v>
@@ -17857,7 +17856,7 @@
         <v>79</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" hidden="true">
@@ -17888,17 +17887,17 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17947,7 +17946,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17974,7 +17973,7 @@
         <v>79</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>79</v>
@@ -17983,7 +17982,7 @@
         <v>79</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -18014,19 +18013,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
@@ -18075,7 +18074,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -18102,7 +18101,7 @@
         <v>79</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>79</v>
@@ -18111,7 +18110,7 @@
         <v>79</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="127" hidden="true">
@@ -18142,19 +18141,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -18203,7 +18202,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18230,7 +18229,7 @@
         <v>79</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>79</v>
@@ -18239,7 +18238,7 @@
         <v>79</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" hidden="true">
@@ -18726,7 +18725,7 @@
         <v>79</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>79</v>
@@ -18892,13 +18891,13 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18949,7 +18948,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18976,7 +18975,7 @@
         <v>79</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>79</v>
@@ -19022,7 +19021,7 @@
         <v>137</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>139</v>
@@ -19075,7 +19074,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19102,7 +19101,7 @@
         <v>79</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>79</v>
@@ -19270,7 +19269,7 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>483</v>
@@ -19359,7 +19358,7 @@
         <v>489</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>79</v>
@@ -19396,13 +19395,13 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19453,7 +19452,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19480,7 +19479,7 @@
         <v>79</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>79</v>
@@ -19526,7 +19525,7 @@
         <v>137</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>139</v>
@@ -19567,19 +19566,19 @@
         <v>79</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19606,7 +19605,7 @@
         <v>79</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>79</v>
@@ -19646,19 +19645,19 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
@@ -19707,7 +19706,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19734,7 +19733,7 @@
         <v>79</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>79</v>
@@ -19743,7 +19742,7 @@
         <v>79</v>
       </c>
       <c r="AR139" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="140" hidden="true">
@@ -19774,13 +19773,13 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19831,7 +19830,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19858,7 +19857,7 @@
         <v>79</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>79</v>
@@ -19904,7 +19903,7 @@
         <v>137</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>139</v>
@@ -19945,19 +19944,19 @@
         <v>79</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19984,7 +19983,7 @@
         <v>79</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>79</v>
@@ -20027,16 +20026,16 @@
         <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>79</v>
@@ -20085,7 +20084,7 @@
         <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20112,7 +20111,7 @@
         <v>79</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>79</v>
@@ -20121,7 +20120,7 @@
         <v>79</v>
       </c>
       <c r="AR142" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -20152,16 +20151,16 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -20211,7 +20210,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20238,7 +20237,7 @@
         <v>79</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>79</v>
@@ -20247,7 +20246,7 @@
         <v>79</v>
       </c>
       <c r="AR143" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="144" hidden="true">
@@ -20281,14 +20280,14 @@
         <v>110</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -20337,7 +20336,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20364,7 +20363,7 @@
         <v>79</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP144" t="s" s="2">
         <v>79</v>
@@ -20373,7 +20372,7 @@
         <v>79</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="145" hidden="true">
@@ -20404,17 +20403,17 @@
         <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20463,7 +20462,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20490,7 +20489,7 @@
         <v>79</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP145" t="s" s="2">
         <v>79</v>
@@ -20499,7 +20498,7 @@
         <v>79</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" hidden="true">
@@ -20530,19 +20529,19 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20591,7 +20590,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20618,7 +20617,7 @@
         <v>79</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP146" t="s" s="2">
         <v>79</v>
@@ -20627,7 +20626,7 @@
         <v>79</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="147" hidden="true">
@@ -20658,19 +20657,19 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20719,7 +20718,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20746,7 +20745,7 @@
         <v>79</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>79</v>
@@ -20755,7 +20754,7 @@
         <v>79</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="148" hidden="true">
@@ -21242,7 +21241,7 @@
         <v>79</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>79</v>
@@ -21365,7 +21364,7 @@
         <v>79</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>612</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,10 +1270,10 @@
     <t>Date/Time that the appointment is to take place.</t>
   </si>
   <si>
-    <t>743: source value from APPOINTMENT - APPOINTMENT DATE/TIME (2.98-.001)</t>
-  </si>
-  <si>
-    <t>Appt.Appointment.AppointmentDateTime</t>
+    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (409.3-22)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.AppointmentDesiredDate</t>
   </si>
   <si>
     <t>appointment.dateTime</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -518,7 +518,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFAppointmentStatus</t>
+    <t>http://va.gov/fhir/ValueSet/AppointmentStatus</t>
   </si>
   <si>
     <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) case not null</t>
@@ -559,7 +559,7 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFAppointmentCancellationReason</t>
+    <t>http://va.gov/fhir/ValueSet/AppointmentCancellationReason</t>
   </si>
   <si>
     <t>735: terminologyMaps using VF_AppointmentCancellationReason on APPOINTMENT - CANCELLATION REASON (2.98-16)</t>
@@ -2257,7 +2257,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="50.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.94140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,7 +556,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-Appointment-2033:if SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}Appointment-2034:if Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
+a-11-2033:2.98-9.5 &gt; 409.1-.01: if SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}a-11-2034:2.98-9.5 &gt; 409.1-.01: if Not SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
   </si>
   <si>
     <t>2034: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01) case Not SERVICE CONNECTED</t>
@@ -634,7 +634,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-Appointment-732:if I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #booked {null}Appointment-733:if I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #arrived {null}Appointment-734:if I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then fixed value #fulfilled {null}Appointment-748:if not null then fixed value #waitlist {null}</t>
+a-11-732:2.98-3: if I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then #booked {null}a-11-733:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then #arrived {null}a-11-734:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then #fulfilled {null}a-11-748:409.3-.01: if not null then #waitlist {null}</t>
   </si>
   <si>
     <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) case not null</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6286" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6286" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -566,6 +566,9 @@
 Dim.AppointmentType.AppointmentType</t>
   </si>
   <si>
+    <t>appointment.type</t>
+  </si>
+  <si>
     <t>Appointment.modifierExtension</t>
   </si>
   <si>
@@ -634,7 +637,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-732:2.98-3: if I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then #booked {null}a-11-733:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then #arrived {null}a-11-734:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then #fulfilled {null}a-11-748:409.3-.01: if not null then #waitlist {null}</t>
+a-11-732:2.98-3: if I, NT, Null AND check-in date (44.003-309)=NULL AND check-out date (44.003-303)=NULL then #booked {null}a-11-733:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then #arrived {null}a-11-734:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then #fulfilled {null}a-11-748:409.3-.01: if not null then #waitlist {null}</t>
   </si>
   <si>
     <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) case not null</t>
@@ -643,8 +646,7 @@
     <t>Appt.WaitList.PatientIEN</t>
   </si>
   <si>
-    <t>appointment.apptStatus
-appointment.patientClass</t>
+    <t>appointment.apptStatus,appointment.patientClass,appointment.serviceCategory</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -854,7 +856,7 @@
 Dim.Location.MedicalService,Dim.Location.MedicalService</t>
   </si>
   <si>
-    <t>appointment.service</t>
+    <t>appointment.clinicStop,appointment.facility,appointment.id,appointment.location,appointment.provider,appointment.service,appointment.visitString</t>
   </si>
   <si>
     <t>./code</t>
@@ -981,7 +983,7 @@
     <t>Appointment.serviceCategory:va-stop-code.coding.code</t>
   </si>
   <si>
-    <t>749: source value from SD WAIT LIST - APPT STOP CODE (409.3-13.4)</t>
+    <t>749: source value from null (409.3-13.4)</t>
   </si>
   <si>
     <t>Appt.WaitList.AppointmentPrimaryStopCodeIEN</t>
@@ -1078,9 +1080,6 @@
 Dim.Location.PrimaryStopCodeIEN</t>
   </si>
   <si>
-    <t>appointment.clinStop</t>
-  </si>
-  <si>
     <t>Appointment.serviceType:va-stop-code.coding.display</t>
   </si>
   <si>
@@ -1206,9 +1205,6 @@
   </si>
   <si>
     <t>740: source value from APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01)</t>
-  </si>
-  <si>
-    <t>appointment.type</t>
   </si>
   <si>
     <t>Appointment.reasonCode</t>
@@ -2351,7 +2347,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="205.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="138.34765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="110.08203125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="155.20703125" customWidth="true" bestFit="true"/>
@@ -4097,7 +4093,7 @@
         <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>79</v>
@@ -4117,14 +4113,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4146,16 +4142,16 @@
         <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -4204,7 +4200,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4245,10 +4241,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4271,13 +4267,13 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4328,7 +4324,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4352,27 +4348,27 @@
         <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4398,13 +4394,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4434,7 +4430,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -4452,7 +4448,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4464,39 +4460,39 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4519,13 +4515,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4556,7 +4552,7 @@
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4574,7 +4570,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4589,10 +4585,10 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -4615,10 +4611,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4641,13 +4637,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4674,17 +4670,17 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
@@ -4694,7 +4690,7 @@
         <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4721,10 +4717,10 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>79</v>
@@ -4735,13 +4731,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
@@ -4763,13 +4759,13 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4796,11 +4792,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4818,7 +4814,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4845,10 +4841,10 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>79</v>
@@ -4859,10 +4855,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4983,14 +4979,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5012,13 +5008,13 @@
         <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5109,10 +5105,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5138,16 +5134,16 @@
         <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -5196,7 +5192,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5223,7 +5219,7 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -5232,15 +5228,15 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5361,14 +5357,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5390,13 +5386,13 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5487,10 +5483,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5516,16 +5512,16 @@
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5535,7 +5531,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5574,7 +5570,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5589,7 +5585,7 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>79</v>
@@ -5601,7 +5597,7 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5610,15 +5606,15 @@
         <v>79</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5644,13 +5640,13 @@
         <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5700,7 +5696,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5727,7 +5723,7 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5736,15 +5732,15 @@
         <v>79</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5770,14 +5766,14 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5826,7 +5822,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5841,19 +5837,19 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5862,15 +5858,15 @@
         <v>79</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5896,14 +5892,14 @@
         <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5952,7 +5948,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5979,7 +5975,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5988,15 +5984,15 @@
         <v>79</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6019,19 +6015,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -6080,7 +6076,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6107,7 +6103,7 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -6116,15 +6112,15 @@
         <v>79</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6150,16 +6146,16 @@
         <v>149</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -6208,7 +6204,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6235,7 +6231,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -6244,18 +6240,18 @@
         <v>79</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6277,13 +6273,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6310,11 +6306,11 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -6332,7 +6328,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6359,10 +6355,10 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>79</v>
@@ -6373,10 +6369,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6497,14 +6493,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6526,13 +6522,13 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6623,10 +6619,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6652,16 +6648,16 @@
         <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6710,7 +6706,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6737,7 +6733,7 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6746,15 +6742,15 @@
         <v>79</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6875,14 +6871,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6904,13 +6900,13 @@
         <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -7001,10 +6997,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7030,16 +7026,16 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7049,7 +7045,7 @@
         <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>79</v>
@@ -7088,7 +7084,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7103,7 +7099,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -7115,7 +7111,7 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -7124,15 +7120,15 @@
         <v>79</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7158,13 +7154,13 @@
         <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7214,7 +7210,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7241,7 +7237,7 @@
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -7250,15 +7246,15 @@
         <v>79</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7284,14 +7280,14 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -7340,7 +7336,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7355,10 +7351,10 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -7367,7 +7363,7 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -7376,15 +7372,15 @@
         <v>79</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7410,14 +7406,14 @@
         <v>149</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -7466,7 +7462,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7493,7 +7489,7 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7502,15 +7498,15 @@
         <v>79</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7533,19 +7529,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7594,7 +7590,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7621,7 +7617,7 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7630,15 +7626,15 @@
         <v>79</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7664,16 +7660,16 @@
         <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7722,7 +7718,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7749,7 +7745,7 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7758,15 +7754,15 @@
         <v>79</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7789,16 +7785,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7824,17 +7820,17 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7844,7 +7840,7 @@
         <v>139</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7868,10 +7864,10 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7885,13 +7881,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>79</v>
@@ -7913,16 +7909,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7948,11 +7944,11 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7970,7 +7966,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7994,10 +7990,10 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8011,10 +8007,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8135,14 +8131,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8164,13 +8160,13 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8261,10 +8257,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8290,16 +8286,16 @@
         <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8348,7 +8344,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8375,7 +8371,7 @@
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -8384,15 +8380,15 @@
         <v>79</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8513,14 +8509,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8542,13 +8538,13 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8639,10 +8635,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8668,16 +8664,16 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8687,7 +8683,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8726,7 +8722,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8741,7 +8737,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -8753,7 +8749,7 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -8762,15 +8758,15 @@
         <v>79</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8796,13 +8792,13 @@
         <v>149</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8852,7 +8848,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8879,7 +8875,7 @@
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8888,15 +8884,15 @@
         <v>79</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8922,14 +8918,14 @@
         <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8978,7 +8974,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8993,19 +8989,19 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -9014,7 +9010,7 @@
         <v>79</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -9048,14 +9044,14 @@
         <v>149</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -9104,7 +9100,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9131,7 +9127,7 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -9140,7 +9136,7 @@
         <v>79</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -9171,19 +9167,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9232,7 +9228,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9259,7 +9255,7 @@
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -9268,7 +9264,7 @@
         <v>79</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -9302,16 +9298,16 @@
         <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -9360,7 +9356,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9387,7 +9383,7 @@
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -9396,7 +9392,7 @@
         <v>79</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9404,7 +9400,7 @@
         <v>350</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>351</v>
@@ -9429,16 +9425,16 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9464,11 +9460,11 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -9486,7 +9482,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9510,10 +9506,10 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -9530,7 +9526,7 @@
         <v>352</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9654,11 +9650,11 @@
         <v>353</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9680,13 +9676,13 @@
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9780,7 +9776,7 @@
         <v>354</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9806,16 +9802,16 @@
         <v>167</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9864,7 +9860,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9891,7 +9887,7 @@
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9900,7 +9896,7 @@
         <v>79</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9908,7 +9904,7 @@
         <v>355</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10032,11 +10028,11 @@
         <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -10058,13 +10054,13 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10158,7 +10154,7 @@
         <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10184,16 +10180,16 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10242,7 +10238,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10269,7 +10265,7 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>79</v>
@@ -10278,7 +10274,7 @@
         <v>79</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -10286,7 +10282,7 @@
         <v>360</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10312,13 +10308,13 @@
         <v>149</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10368,7 +10364,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10395,7 +10391,7 @@
         <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10404,7 +10400,7 @@
         <v>79</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -10412,7 +10408,7 @@
         <v>361</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10438,14 +10434,14 @@
         <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -10494,7 +10490,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10515,13 +10511,13 @@
         <v>363</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10530,7 +10526,7 @@
         <v>79</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10564,14 +10560,14 @@
         <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10620,7 +10616,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10647,7 +10643,7 @@
         <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10656,7 +10652,7 @@
         <v>79</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -10687,19 +10683,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10748,7 +10744,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10775,7 +10771,7 @@
         <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -10784,7 +10780,7 @@
         <v>79</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -10818,16 +10814,16 @@
         <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10876,7 +10872,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10903,7 +10899,7 @@
         <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -10912,7 +10908,7 @@
         <v>79</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10943,7 +10939,7 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>368</v>
@@ -11065,7 +11061,7 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>375</v>
@@ -11292,7 +11288,7 @@
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11314,13 +11310,13 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11440,16 +11436,16 @@
         <v>167</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -11498,7 +11494,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11525,7 +11521,7 @@
         <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>79</v>
@@ -11534,7 +11530,7 @@
         <v>79</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11568,16 +11564,16 @@
         <v>149</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11626,7 +11622,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11647,13 +11643,13 @@
         <v>175</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>386</v>
+        <v>176</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>79</v>
@@ -11662,15 +11658,15 @@
         <v>79</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11693,13 +11689,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11729,11 +11725,11 @@
         <v>114</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
       </c>
@@ -11750,7 +11746,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11765,36 +11761,36 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AO75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11817,13 +11813,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11874,7 +11870,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11889,19 +11885,19 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11915,10 +11911,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11941,16 +11937,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12000,7 +11996,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12024,27 +12020,27 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>373</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12070,10 +12066,10 @@
         <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12124,7 +12120,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12139,36 +12135,36 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AL78" t="s" s="2">
+      <c r="AM78" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AP78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12191,13 +12187,13 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12248,7 +12244,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12272,16 +12268,16 @@
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AP79" t="s" s="2">
+      <c r="AQ79" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>79</v>
@@ -12289,10 +12285,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12315,13 +12311,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12372,7 +12368,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12387,36 +12383,36 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AO80" t="s" s="2">
+      <c r="AP80" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AP80" t="s" s="2">
+      <c r="AQ80" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AQ80" t="s" s="2">
+      <c r="AR80" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AR80" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12439,13 +12435,13 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12496,7 +12492,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12511,36 +12507,36 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AM81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AO81" t="s" s="2">
+      <c r="AP81" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AP81" t="s" s="2">
+      <c r="AQ81" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AQ81" t="s" s="2">
+      <c r="AR81" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AR81" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12563,13 +12559,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12620,7 +12616,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12635,22 +12631,22 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AM82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AM82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AO82" t="s" s="2">
+      <c r="AP82" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>79</v>
@@ -12661,10 +12657,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12687,13 +12683,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12744,7 +12740,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12771,7 +12767,7 @@
         <v>79</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>79</v>
@@ -12785,10 +12781,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12811,16 +12807,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12870,7 +12866,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12885,22 +12881,22 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AM84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>79</v>
@@ -12911,10 +12907,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12940,13 +12936,13 @@
         <v>149</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12996,7 +12992,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13011,36 +13007,36 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AM85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AO85" t="s" s="2">
+      <c r="AP85" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AP85" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="AQ85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13066,10 +13062,10 @@
         <v>149</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13120,7 +13116,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13147,28 +13143,28 @@
         <v>79</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13187,13 +13183,13 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13244,7 +13240,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13268,10 +13264,10 @@
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13285,10 +13281,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13311,13 +13307,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13356,7 +13352,7 @@
         <v>79</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
@@ -13366,7 +13362,7 @@
         <v>139</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>90</v>
@@ -13378,39 +13374,39 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AO88" t="s" s="2">
+      <c r="AP88" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AP88" t="s" s="2">
+      <c r="AQ88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13531,14 +13527,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13560,13 +13556,13 @@
         <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13657,14 +13653,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13686,16 +13682,16 @@
         <v>135</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="N91" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13744,7 +13740,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13785,10 +13781,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13811,16 +13807,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13846,14 +13842,14 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Y92" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Y92" t="s" s="2">
+      <c r="Z92" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
       </c>
@@ -13870,7 +13866,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13897,7 +13893,7 @@
         <v>79</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>153</v>
@@ -13906,15 +13902,15 @@
         <v>79</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13937,13 +13933,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13994,7 +13990,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14021,24 +14017,24 @@
         <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AP93" t="s" s="2">
+      <c r="AQ93" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AQ93" t="s" s="2">
+      <c r="AR93" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14064,10 +14060,10 @@
         <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14097,11 +14093,11 @@
         <v>170</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>79</v>
       </c>
@@ -14118,7 +14114,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14145,10 +14141,10 @@
         <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>79</v>
@@ -14159,10 +14155,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14188,10 +14184,10 @@
         <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14221,11 +14217,11 @@
         <v>170</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>79</v>
       </c>
@@ -14242,7 +14238,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>90</v>
@@ -14269,24 +14265,24 @@
         <v>79</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AP95" t="s" s="2">
+      <c r="AQ95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14309,13 +14305,13 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14366,7 +14362,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14407,13 +14403,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14435,13 +14431,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14492,7 +14488,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>90</v>
@@ -14504,39 +14500,39 @@
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AO97" t="s" s="2">
+      <c r="AP97" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AP97" t="s" s="2">
+      <c r="AQ97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR97" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14657,14 +14653,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14686,13 +14682,13 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14783,14 +14779,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14812,16 +14808,16 @@
         <v>135</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14870,7 +14866,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14911,10 +14907,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14937,16 +14933,16 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14972,14 +14968,14 @@
         <v>79</v>
       </c>
       <c r="X101" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Y101" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Y101" t="s" s="2">
+      <c r="Z101" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
       </c>
@@ -14996,7 +14992,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15023,7 +15019,7 @@
         <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>153</v>
@@ -15032,15 +15028,15 @@
         <v>79</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15161,14 +15157,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -15190,13 +15186,13 @@
         <v>135</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15287,10 +15283,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15316,16 +15312,16 @@
         <v>167</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -15374,7 +15370,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15401,7 +15397,7 @@
         <v>79</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15410,15 +15406,15 @@
         <v>79</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15539,14 +15535,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15568,13 +15564,13 @@
         <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15665,10 +15661,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15694,16 +15690,16 @@
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15752,7 +15748,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15779,7 +15775,7 @@
         <v>79</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>79</v>
@@ -15788,15 +15784,15 @@
         <v>79</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15822,13 +15818,13 @@
         <v>149</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15878,7 +15874,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15905,7 +15901,7 @@
         <v>79</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>79</v>
@@ -15914,15 +15910,15 @@
         <v>79</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15948,14 +15944,14 @@
         <v>110</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15965,7 +15961,7 @@
         <v>79</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>79</v>
@@ -16004,7 +16000,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -16019,7 +16015,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>79</v>
@@ -16031,7 +16027,7 @@
         <v>79</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>79</v>
@@ -16040,15 +16036,15 @@
         <v>79</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16074,14 +16070,14 @@
         <v>149</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -16130,7 +16126,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16157,7 +16153,7 @@
         <v>79</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>79</v>
@@ -16166,15 +16162,15 @@
         <v>79</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16197,19 +16193,19 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -16258,7 +16254,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16285,7 +16281,7 @@
         <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>79</v>
@@ -16294,15 +16290,15 @@
         <v>79</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16328,16 +16324,16 @@
         <v>149</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -16386,7 +16382,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16413,7 +16409,7 @@
         <v>79</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>79</v>
@@ -16422,15 +16418,15 @@
         <v>79</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16453,13 +16449,13 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16510,7 +16506,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16525,36 +16521,36 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AL113" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AL113" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="AM113" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO113" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AP113" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AP113" t="s" s="2">
+      <c r="AQ113" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AQ113" t="s" s="2">
+      <c r="AR113" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AR113" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16580,10 +16576,10 @@
         <v>110</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16613,11 +16609,11 @@
         <v>170</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z114" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>79</v>
       </c>
@@ -16634,7 +16630,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16661,10 +16657,10 @@
         <v>79</v>
       </c>
       <c r="AO114" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>79</v>
@@ -16675,10 +16671,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16704,10 +16700,10 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16719,7 +16715,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16737,11 +16733,11 @@
         <v>170</v>
       </c>
       <c r="Y115" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z115" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z115" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA115" t="s" s="2">
         <v>79</v>
       </c>
@@ -16758,7 +16754,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>90</v>
@@ -16773,7 +16769,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>79</v>
@@ -16785,24 +16781,24 @@
         <v>79</v>
       </c>
       <c r="AO115" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AP115" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AP115" t="s" s="2">
+      <c r="AQ115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR115" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR115" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16825,13 +16821,13 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16882,7 +16878,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16923,13 +16919,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>79</v>
@@ -16951,13 +16947,13 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17008,7 +17004,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>90</v>
@@ -17020,39 +17016,39 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN117" t="s" s="2">
+      <c r="AO117" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AO117" t="s" s="2">
+      <c r="AP117" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AP117" t="s" s="2">
+      <c r="AQ117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR117" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AQ117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR117" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17173,14 +17169,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17202,13 +17198,13 @@
         <v>135</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17299,14 +17295,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17328,16 +17324,16 @@
         <v>135</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M120" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="N120" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>79</v>
@@ -17386,7 +17382,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17427,10 +17423,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17453,16 +17449,16 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17488,14 +17484,14 @@
         <v>79</v>
       </c>
       <c r="X121" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Y121" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Y121" t="s" s="2">
+      <c r="Z121" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z121" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AA121" t="s" s="2">
         <v>79</v>
       </c>
@@ -17512,7 +17508,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17539,7 +17535,7 @@
         <v>79</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>153</v>
@@ -17548,15 +17544,15 @@
         <v>79</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17677,14 +17673,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17706,13 +17702,13 @@
         <v>135</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17803,10 +17799,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17832,16 +17828,16 @@
         <v>167</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17890,7 +17886,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17917,7 +17913,7 @@
         <v>79</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>79</v>
@@ -17926,15 +17922,15 @@
         <v>79</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18055,14 +18051,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -18084,13 +18080,13 @@
         <v>135</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -18181,10 +18177,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18210,16 +18206,16 @@
         <v>104</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -18268,7 +18264,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18295,7 +18291,7 @@
         <v>79</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>79</v>
@@ -18304,15 +18300,15 @@
         <v>79</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18338,13 +18334,13 @@
         <v>149</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18394,7 +18390,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18421,7 +18417,7 @@
         <v>79</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>79</v>
@@ -18430,15 +18426,15 @@
         <v>79</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18464,14 +18460,14 @@
         <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -18481,7 +18477,7 @@
         <v>79</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>79</v>
@@ -18520,7 +18516,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18535,7 +18531,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>79</v>
@@ -18547,7 +18543,7 @@
         <v>79</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>79</v>
@@ -18556,15 +18552,15 @@
         <v>79</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18590,14 +18586,14 @@
         <v>149</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -18646,7 +18642,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18673,7 +18669,7 @@
         <v>79</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>79</v>
@@ -18682,15 +18678,15 @@
         <v>79</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18713,19 +18709,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18774,7 +18770,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18801,7 +18797,7 @@
         <v>79</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>79</v>
@@ -18810,15 +18806,15 @@
         <v>79</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18844,16 +18840,16 @@
         <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
@@ -18902,7 +18898,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18929,7 +18925,7 @@
         <v>79</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>79</v>
@@ -18938,15 +18934,15 @@
         <v>79</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18969,13 +18965,13 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19026,7 +19022,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -19041,7 +19037,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>79</v>
@@ -19053,24 +19049,24 @@
         <v>79</v>
       </c>
       <c r="AO133" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AP133" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AP133" t="s" s="2">
+      <c r="AQ133" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AQ133" t="s" s="2">
+      <c r="AR133" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AR133" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19096,10 +19092,10 @@
         <v>110</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -19129,11 +19125,11 @@
         <v>170</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z134" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA134" t="s" s="2">
         <v>79</v>
       </c>
@@ -19150,7 +19146,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19177,10 +19173,10 @@
         <v>79</v>
       </c>
       <c r="AO134" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP134" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>79</v>
@@ -19191,10 +19187,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19220,10 +19216,10 @@
         <v>110</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19235,7 +19231,7 @@
         <v>79</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>79</v>
@@ -19253,11 +19249,11 @@
         <v>170</v>
       </c>
       <c r="Y135" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z135" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z135" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA135" t="s" s="2">
         <v>79</v>
       </c>
@@ -19274,7 +19270,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>90</v>
@@ -19289,7 +19285,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>79</v>
@@ -19301,24 +19297,24 @@
         <v>79</v>
       </c>
       <c r="AO135" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AP135" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AP135" t="s" s="2">
+      <c r="AQ135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR135" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AQ135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR135" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19341,13 +19337,13 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -19398,7 +19394,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19439,13 +19435,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C137" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>79</v>
@@ -19467,13 +19463,13 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19524,7 +19520,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>90</v>
@@ -19536,39 +19532,39 @@
         <v>79</v>
       </c>
       <c r="AJ137" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN137" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN137" t="s" s="2">
+      <c r="AO137" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AO137" t="s" s="2">
+      <c r="AP137" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AP137" t="s" s="2">
+      <c r="AQ137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR137" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AQ137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR137" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19689,14 +19685,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19718,13 +19714,13 @@
         <v>135</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19815,14 +19811,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19844,16 +19840,16 @@
         <v>135</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M140" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="N140" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19902,7 +19898,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19943,10 +19939,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19969,16 +19965,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20004,14 +20000,14 @@
         <v>79</v>
       </c>
       <c r="X141" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Y141" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Y141" t="s" s="2">
+      <c r="Z141" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
       </c>
@@ -20028,7 +20024,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20055,7 +20051,7 @@
         <v>79</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>153</v>
@@ -20064,15 +20060,15 @@
         <v>79</v>
       </c>
       <c r="AR141" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20193,14 +20189,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -20222,13 +20218,13 @@
         <v>135</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -20319,10 +20315,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20348,16 +20344,16 @@
         <v>167</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -20406,7 +20402,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20433,7 +20429,7 @@
         <v>79</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AP144" t="s" s="2">
         <v>79</v>
@@ -20442,15 +20438,15 @@
         <v>79</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20571,14 +20567,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20600,13 +20596,13 @@
         <v>135</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -20697,10 +20693,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20726,16 +20722,16 @@
         <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20784,7 +20780,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20811,7 +20807,7 @@
         <v>79</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>79</v>
@@ -20820,15 +20816,15 @@
         <v>79</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20854,13 +20850,13 @@
         <v>149</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20910,7 +20906,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20937,7 +20933,7 @@
         <v>79</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP148" t="s" s="2">
         <v>79</v>
@@ -20946,15 +20942,15 @@
         <v>79</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20980,14 +20976,14 @@
         <v>110</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20997,7 +20993,7 @@
         <v>79</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>79</v>
@@ -21036,7 +21032,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21051,7 +21047,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -21063,7 +21059,7 @@
         <v>79</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>79</v>
@@ -21072,15 +21068,15 @@
         <v>79</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21106,14 +21102,14 @@
         <v>149</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>79</v>
@@ -21162,7 +21158,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21189,7 +21185,7 @@
         <v>79</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>79</v>
@@ -21198,15 +21194,15 @@
         <v>79</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21229,19 +21225,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>79</v>
@@ -21290,7 +21286,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21317,7 +21313,7 @@
         <v>79</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>79</v>
@@ -21326,15 +21322,15 @@
         <v>79</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21360,16 +21356,16 @@
         <v>149</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -21418,7 +21414,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21445,7 +21441,7 @@
         <v>79</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>79</v>
@@ -21454,15 +21450,15 @@
         <v>79</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21485,13 +21481,13 @@
         <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21542,7 +21538,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21557,11 +21553,11 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AL153" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AL153" t="s" s="2">
-        <v>628</v>
-      </c>
       <c r="AM153" t="s" s="2">
         <v>79</v>
       </c>
@@ -21569,24 +21565,24 @@
         <v>79</v>
       </c>
       <c r="AO153" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AP153" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AP153" t="s" s="2">
+      <c r="AQ153" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AQ153" t="s" s="2">
+      <c r="AR153" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AR153" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21612,10 +21608,10 @@
         <v>110</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -21645,11 +21641,11 @@
         <v>170</v>
       </c>
       <c r="Y154" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z154" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z154" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA154" t="s" s="2">
         <v>79</v>
       </c>
@@ -21666,7 +21662,7 @@
         <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21693,10 +21689,10 @@
         <v>79</v>
       </c>
       <c r="AO154" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP154" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AP154" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>79</v>
@@ -21707,10 +21703,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21736,10 +21732,10 @@
         <v>110</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21751,7 +21747,7 @@
         <v>79</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>79</v>
@@ -21769,11 +21765,11 @@
         <v>170</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z155" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA155" t="s" s="2">
         <v>79</v>
       </c>
@@ -21790,7 +21786,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>90</v>
@@ -21805,7 +21801,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>79</v>
@@ -21817,24 +21813,24 @@
         <v>79</v>
       </c>
       <c r="AO155" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AP155" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AP155" t="s" s="2">
+      <c r="AQ155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR155" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AQ155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR155" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21857,13 +21853,13 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21914,7 +21910,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21955,10 +21951,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21981,16 +21977,16 @@
         <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -22040,7 +22036,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -22064,19 +22060,19 @@
         <v>79</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AO157" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AP157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AQ157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AR157" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AP157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AQ157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AR157" t="s" s="2">
-        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1354,7 +1354,7 @@
     <t>Appt.WaitList.AppointmentDesiredDate</t>
   </si>
   <si>
-    <t>appointment.dateTime</t>
+    <t>appointment.dateTime,appointment.id,appointment.visitString</t>
   </si>
   <si>
     <t>Request.occurrence[x]</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6286" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6286" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -566,7 +566,7 @@
 Dim.AppointmentType.AppointmentType</t>
   </si>
   <si>
-    <t>appointment.type</t>
+    <t>Appointment.Type</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>
@@ -646,7 +646,7 @@
     <t>Appt.WaitList.PatientIEN</t>
   </si>
   <si>
-    <t>appointment.apptStatus,appointment.patientClass,appointment.serviceCategory</t>
+    <t>Appointment.NoShow,Appointment.AppointmentExtension.PatientStatus,Appointment.AppointmentExtension.ServiceStatus</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -686,6 +686,9 @@
     <t>Appt.Appointment.CancellationReasonIEN</t>
   </si>
   <si>
+    <t>Appointment.AppointmentExtension.CancelReason</t>
+  </si>
+  <si>
     <t>Appointment.serviceCategory</t>
   </si>
   <si>
@@ -856,7 +859,7 @@
 Dim.Location.MedicalService,Dim.Location.MedicalService</t>
   </si>
   <si>
-    <t>appointment.clinicStop,appointment.facility,appointment.id,appointment.location,appointment.provider,appointment.service,appointment.visitString</t>
+    <t>Appointment.CareProvider,Appointment.EnteredAt,Appointment.Location,Appointment.PlacerApptId,Appointment.Type</t>
   </si>
   <si>
     <t>./code</t>
@@ -1354,9 +1357,6 @@
     <t>Appt.WaitList.AppointmentDesiredDate</t>
   </si>
   <si>
-    <t>appointment.dateTime,appointment.id,appointment.visitString</t>
-  </si>
-  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -1388,6 +1388,9 @@
 Outpat.Visit.COProcessCompleteDateTime,Outpat.Workload.COProcessCompleteDateTime</t>
   </si>
   <si>
+    <t>Appointment.CareProvider,Appointment.EncounterNumber,Appointment.AppointmentExtension.AssociatedEncounterNumber</t>
+  </si>
+  <si>
     <t>.effectiveTime.high</t>
   </si>
   <si>
@@ -1419,6 +1422,9 @@
     <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
+    <t>Appointment.AppointmentExtension.Length</t>
+  </si>
+  <si>
     <t>.activityTime[@xsi:type = ('SXPR_TS', 'PIVL_TS')].width</t>
   </si>
   <si>
@@ -1461,6 +1467,9 @@
   </si>
   <si>
     <t>Appt.WaitList.OriginatingDate</t>
+  </si>
+  <si>
+    <t>Appointment.EnteredOn</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -2347,7 +2356,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="205.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="138.34765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="116.4140625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="110.08203125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="155.20703125" customWidth="true" bestFit="true"/>
@@ -4591,7 +4600,7 @@
         <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4611,10 +4620,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4640,10 +4649,10 @@
         <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4670,17 +4679,17 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
@@ -4690,7 +4699,7 @@
         <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4717,10 +4726,10 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>79</v>
@@ -4731,13 +4740,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
@@ -4762,10 +4771,10 @@
         <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4792,11 +4801,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4814,7 +4823,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4841,10 +4850,10 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>79</v>
@@ -4855,10 +4864,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4979,10 +4988,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5008,10 +5017,10 @@
         <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>181</v>
@@ -5105,10 +5114,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5134,16 +5143,16 @@
         <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -5192,7 +5201,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5219,7 +5228,7 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -5228,15 +5237,15 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5357,10 +5366,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5386,10 +5395,10 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>181</v>
@@ -5483,10 +5492,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5512,16 +5521,16 @@
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5531,7 +5540,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5570,7 +5579,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5585,7 +5594,7 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>79</v>
@@ -5597,7 +5606,7 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5606,15 +5615,15 @@
         <v>79</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5640,13 +5649,13 @@
         <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5696,7 +5705,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5723,7 +5732,7 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5732,15 +5741,15 @@
         <v>79</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5766,14 +5775,14 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5822,7 +5831,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5837,19 +5846,19 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5858,15 +5867,15 @@
         <v>79</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5892,14 +5901,14 @@
         <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5948,7 +5957,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5975,7 +5984,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5984,15 +5993,15 @@
         <v>79</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6015,19 +6024,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -6076,7 +6085,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6103,7 +6112,7 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -6112,15 +6121,15 @@
         <v>79</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6146,16 +6155,16 @@
         <v>149</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -6204,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6231,7 +6240,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -6240,18 +6249,18 @@
         <v>79</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6276,10 +6285,10 @@
         <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6306,11 +6315,11 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -6328,7 +6337,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6355,10 +6364,10 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>79</v>
@@ -6369,10 +6378,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6493,10 +6502,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6522,10 +6531,10 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>181</v>
@@ -6619,10 +6628,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6648,16 +6657,16 @@
         <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6706,7 +6715,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6733,7 +6742,7 @@
         <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6742,15 +6751,15 @@
         <v>79</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6871,10 +6880,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6900,10 +6909,10 @@
         <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>181</v>
@@ -6997,10 +7006,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7026,16 +7035,16 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7045,7 +7054,7 @@
         <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>79</v>
@@ -7084,7 +7093,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7099,7 +7108,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -7111,7 +7120,7 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -7120,15 +7129,15 @@
         <v>79</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7154,13 +7163,13 @@
         <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7210,7 +7219,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7237,7 +7246,7 @@
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -7246,15 +7255,15 @@
         <v>79</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7280,14 +7289,14 @@
         <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -7336,7 +7345,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7351,10 +7360,10 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -7363,7 +7372,7 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -7372,15 +7381,15 @@
         <v>79</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7406,14 +7415,14 @@
         <v>149</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -7462,7 +7471,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7489,7 +7498,7 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -7498,15 +7507,15 @@
         <v>79</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7529,19 +7538,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7590,7 +7599,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7617,7 +7626,7 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -7626,15 +7635,15 @@
         <v>79</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7660,16 +7669,16 @@
         <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7718,7 +7727,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7745,7 +7754,7 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7754,15 +7763,15 @@
         <v>79</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7788,13 +7797,13 @@
         <v>208</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7820,17 +7829,17 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7840,7 +7849,7 @@
         <v>139</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7864,10 +7873,10 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7881,13 +7890,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>79</v>
@@ -7912,13 +7921,13 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7944,11 +7953,11 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7966,7 +7975,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7990,10 +7999,10 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8007,10 +8016,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8131,10 +8140,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8160,10 +8169,10 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>181</v>
@@ -8257,10 +8266,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8286,16 +8295,16 @@
         <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8344,7 +8353,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8371,7 +8380,7 @@
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -8380,15 +8389,15 @@
         <v>79</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8509,10 +8518,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8538,10 +8547,10 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>181</v>
@@ -8635,10 +8644,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8664,16 +8673,16 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8683,7 +8692,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8722,7 +8731,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8737,7 +8746,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -8749,7 +8758,7 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -8758,15 +8767,15 @@
         <v>79</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8792,13 +8801,13 @@
         <v>149</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8848,7 +8857,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8875,7 +8884,7 @@
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8884,15 +8893,15 @@
         <v>79</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8918,14 +8927,14 @@
         <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8974,7 +8983,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8989,19 +8998,19 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -9010,15 +9019,15 @@
         <v>79</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9044,14 +9053,14 @@
         <v>149</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -9100,7 +9109,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9127,7 +9136,7 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -9136,15 +9145,15 @@
         <v>79</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9167,19 +9176,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9228,7 +9237,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9255,7 +9264,7 @@
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -9264,15 +9273,15 @@
         <v>79</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9298,16 +9307,16 @@
         <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -9356,7 +9365,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9383,7 +9392,7 @@
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -9392,18 +9401,18 @@
         <v>79</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>79</v>
@@ -9428,13 +9437,13 @@
         <v>208</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9460,11 +9469,11 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -9482,7 +9491,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9506,10 +9515,10 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -9523,10 +9532,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9647,10 +9656,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9676,10 +9685,10 @@
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>181</v>
@@ -9773,10 +9782,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9802,16 +9811,16 @@
         <v>167</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9860,7 +9869,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9887,7 +9896,7 @@
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9896,15 +9905,15 @@
         <v>79</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10025,10 +10034,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10054,10 +10063,10 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>181</v>
@@ -10151,10 +10160,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10180,16 +10189,16 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10199,7 +10208,7 @@
         <v>79</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>79</v>
@@ -10238,7 +10247,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10253,7 +10262,7 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>79</v>
@@ -10265,7 +10274,7 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>79</v>
@@ -10274,15 +10283,15 @@
         <v>79</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10308,13 +10317,13 @@
         <v>149</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10364,7 +10373,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10391,7 +10400,7 @@
         <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10400,15 +10409,15 @@
         <v>79</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10434,14 +10443,14 @@
         <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -10490,7 +10499,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10505,19 +10514,19 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10526,15 +10535,15 @@
         <v>79</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10560,14 +10569,14 @@
         <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10616,7 +10625,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10643,7 +10652,7 @@
         <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10652,15 +10661,15 @@
         <v>79</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10683,19 +10692,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10744,7 +10753,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10771,7 +10780,7 @@
         <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -10780,15 +10789,15 @@
         <v>79</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10814,16 +10823,16 @@
         <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10872,7 +10881,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10899,7 +10908,7 @@
         <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -10908,15 +10917,15 @@
         <v>79</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10942,10 +10951,10 @@
         <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10976,7 +10985,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10994,7 +11003,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11009,7 +11018,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>79</v>
@@ -11021,13 +11030,13 @@
         <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>79</v>
@@ -11035,10 +11044,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11064,10 +11073,10 @@
         <v>208</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11098,7 +11107,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -11116,7 +11125,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11143,24 +11152,24 @@
         <v>79</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11281,10 +11290,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11310,10 +11319,10 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>181</v>
@@ -11407,10 +11416,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11436,16 +11445,16 @@
         <v>167</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -11494,7 +11503,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11521,7 +11530,7 @@
         <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>79</v>
@@ -11530,15 +11539,15 @@
         <v>79</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11564,16 +11573,16 @@
         <v>149</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11622,7 +11631,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11637,7 +11646,7 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>175</v>
@@ -11649,7 +11658,7 @@
         <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>79</v>
@@ -11658,15 +11667,15 @@
         <v>79</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11692,10 +11701,10 @@
         <v>208</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11725,10 +11734,10 @@
         <v>114</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -11746,7 +11755,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11761,7 +11770,7 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>79</v>
@@ -11770,10 +11779,10 @@
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11782,15 +11791,15 @@
         <v>79</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11813,13 +11822,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11870,7 +11879,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11885,7 +11894,7 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>79</v>
@@ -11894,10 +11903,10 @@
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11911,10 +11920,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11937,16 +11946,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11996,7 +12005,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12020,27 +12029,27 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12066,10 +12075,10 @@
         <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12120,7 +12129,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12135,10 +12144,10 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>176</v>
@@ -12147,24 +12156,24 @@
         <v>79</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12187,13 +12196,13 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12244,7 +12253,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12268,16 +12277,16 @@
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>79</v>
@@ -12285,10 +12294,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12311,13 +12320,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12368,7 +12377,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12383,13 +12392,13 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>434</v>
@@ -12435,7 +12444,7 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>440</v>
@@ -12513,30 +12522,30 @@
         <v>443</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>434</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12559,13 +12568,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12616,7 +12625,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12631,22 +12640,22 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>79</v>
+        <v>455</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>434</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>79</v>
@@ -12657,10 +12666,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12683,13 +12692,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12740,7 +12749,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12767,7 +12776,7 @@
         <v>79</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>79</v>
@@ -12781,10 +12790,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12807,16 +12816,16 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12866,7 +12875,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12881,22 +12890,22 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>79</v>
+        <v>470</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>79</v>
@@ -12907,10 +12916,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12936,13 +12945,13 @@
         <v>149</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12992,7 +13001,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13007,36 +13016,36 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13062,10 +13071,10 @@
         <v>149</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13116,7 +13125,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13143,28 +13152,28 @@
         <v>79</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13183,13 +13192,13 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13240,7 +13249,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13264,10 +13273,10 @@
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13281,10 +13290,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13307,13 +13316,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13352,7 +13361,7 @@
         <v>79</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
@@ -13362,7 +13371,7 @@
         <v>139</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>90</v>
@@ -13374,7 +13383,7 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
@@ -13386,27 +13395,27 @@
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13527,10 +13536,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13556,10 +13565,10 @@
         <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>181</v>
@@ -13653,14 +13662,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13682,10 +13691,10 @@
         <v>135</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>181</v>
@@ -13740,7 +13749,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13781,10 +13790,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13810,13 +13819,13 @@
         <v>208</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13842,13 +13851,13 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13866,7 +13875,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13893,7 +13902,7 @@
         <v>79</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>153</v>
@@ -13902,15 +13911,15 @@
         <v>79</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13933,13 +13942,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13990,7 +13999,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14017,24 +14026,24 @@
         <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14060,10 +14069,10 @@
         <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14093,28 +14102,28 @@
         <v>170</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14141,10 +14150,10 @@
         <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>79</v>
@@ -14155,10 +14164,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14184,10 +14193,10 @@
         <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14217,28 +14226,28 @@
         <v>170</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>90</v>
@@ -14265,24 +14274,24 @@
         <v>79</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14305,13 +14314,13 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14362,7 +14371,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14403,13 +14412,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14431,13 +14440,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14488,7 +14497,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>90</v>
@@ -14500,7 +14509,7 @@
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
@@ -14512,27 +14521,27 @@
         <v>79</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14653,10 +14662,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14682,10 +14691,10 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>181</v>
@@ -14779,14 +14788,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14808,10 +14817,10 @@
         <v>135</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>181</v>
@@ -14866,7 +14875,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14907,10 +14916,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14936,13 +14945,13 @@
         <v>208</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14968,13 +14977,13 @@
         <v>79</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -14992,7 +15001,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15019,7 +15028,7 @@
         <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>153</v>
@@ -15028,15 +15037,15 @@
         <v>79</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15157,10 +15166,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15186,10 +15195,10 @@
         <v>135</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>181</v>
@@ -15283,10 +15292,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15312,16 +15321,16 @@
         <v>167</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -15370,7 +15379,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15397,7 +15406,7 @@
         <v>79</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15406,15 +15415,15 @@
         <v>79</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15535,10 +15544,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15564,10 +15573,10 @@
         <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>181</v>
@@ -15661,10 +15670,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15690,16 +15699,16 @@
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15748,7 +15757,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15775,7 +15784,7 @@
         <v>79</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>79</v>
@@ -15784,15 +15793,15 @@
         <v>79</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15818,13 +15827,13 @@
         <v>149</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15874,7 +15883,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15901,7 +15910,7 @@
         <v>79</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>79</v>
@@ -15910,15 +15919,15 @@
         <v>79</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15944,14 +15953,14 @@
         <v>110</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15961,7 +15970,7 @@
         <v>79</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>79</v>
@@ -16000,7 +16009,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -16015,7 +16024,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>79</v>
@@ -16027,7 +16036,7 @@
         <v>79</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>79</v>
@@ -16036,15 +16045,15 @@
         <v>79</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16070,14 +16079,14 @@
         <v>149</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -16126,7 +16135,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16153,7 +16162,7 @@
         <v>79</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>79</v>
@@ -16162,15 +16171,15 @@
         <v>79</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16193,19 +16202,19 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -16254,7 +16263,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16281,7 +16290,7 @@
         <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>79</v>
@@ -16290,15 +16299,15 @@
         <v>79</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16324,16 +16333,16 @@
         <v>149</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -16382,7 +16391,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16409,7 +16418,7 @@
         <v>79</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>79</v>
@@ -16418,15 +16427,15 @@
         <v>79</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16449,13 +16458,13 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16506,7 +16515,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16521,36 +16530,36 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16576,10 +16585,10 @@
         <v>110</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16609,28 +16618,28 @@
         <v>170</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF114" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16657,10 +16666,10 @@
         <v>79</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>79</v>
@@ -16671,10 +16680,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16700,10 +16709,10 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16715,7 +16724,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16733,28 +16742,28 @@
         <v>170</v>
       </c>
       <c r="Y115" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF115" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>90</v>
@@ -16769,7 +16778,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>79</v>
@@ -16781,24 +16790,24 @@
         <v>79</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR115" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16821,13 +16830,13 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16878,7 +16887,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16919,13 +16928,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>79</v>
@@ -16947,13 +16956,13 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17004,7 +17013,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>90</v>
@@ -17016,7 +17025,7 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -17028,27 +17037,27 @@
         <v>79</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17169,10 +17178,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17198,10 +17207,10 @@
         <v>135</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>181</v>
@@ -17295,14 +17304,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17324,10 +17333,10 @@
         <v>135</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>181</v>
@@ -17382,7 +17391,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17423,10 +17432,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17452,13 +17461,13 @@
         <v>208</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17484,13 +17493,13 @@
         <v>79</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>79</v>
@@ -17508,7 +17517,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17535,7 +17544,7 @@
         <v>79</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>153</v>
@@ -17544,15 +17553,15 @@
         <v>79</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17673,10 +17682,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17702,10 +17711,10 @@
         <v>135</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>181</v>
@@ -17799,10 +17808,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17828,16 +17837,16 @@
         <v>167</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17886,7 +17895,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17913,7 +17922,7 @@
         <v>79</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>79</v>
@@ -17922,15 +17931,15 @@
         <v>79</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18051,10 +18060,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18080,10 +18089,10 @@
         <v>135</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>181</v>
@@ -18177,10 +18186,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18206,16 +18215,16 @@
         <v>104</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -18264,7 +18273,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18291,7 +18300,7 @@
         <v>79</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>79</v>
@@ -18300,15 +18309,15 @@
         <v>79</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18334,13 +18343,13 @@
         <v>149</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18390,7 +18399,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18417,7 +18426,7 @@
         <v>79</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>79</v>
@@ -18426,15 +18435,15 @@
         <v>79</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18460,14 +18469,14 @@
         <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -18477,7 +18486,7 @@
         <v>79</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>79</v>
@@ -18516,7 +18525,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18531,7 +18540,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>79</v>
@@ -18543,7 +18552,7 @@
         <v>79</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>79</v>
@@ -18552,15 +18561,15 @@
         <v>79</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18586,14 +18595,14 @@
         <v>149</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -18642,7 +18651,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18669,7 +18678,7 @@
         <v>79</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>79</v>
@@ -18678,15 +18687,15 @@
         <v>79</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18709,19 +18718,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18770,7 +18779,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18797,7 +18806,7 @@
         <v>79</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>79</v>
@@ -18806,15 +18815,15 @@
         <v>79</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18840,16 +18849,16 @@
         <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
@@ -18898,7 +18907,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18925,7 +18934,7 @@
         <v>79</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>79</v>
@@ -18934,15 +18943,15 @@
         <v>79</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18965,13 +18974,13 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19022,7 +19031,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -19037,7 +19046,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>79</v>
@@ -19049,24 +19058,24 @@
         <v>79</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19092,10 +19101,10 @@
         <v>110</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -19125,28 +19134,28 @@
         <v>170</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF134" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19173,10 +19182,10 @@
         <v>79</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>79</v>
@@ -19187,10 +19196,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19216,10 +19225,10 @@
         <v>110</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19231,7 +19240,7 @@
         <v>79</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>79</v>
@@ -19249,28 +19258,28 @@
         <v>170</v>
       </c>
       <c r="Y135" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF135" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>90</v>
@@ -19285,7 +19294,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>79</v>
@@ -19297,24 +19306,24 @@
         <v>79</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19337,13 +19346,13 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -19394,7 +19403,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19435,13 +19444,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>79</v>
@@ -19463,13 +19472,13 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19520,7 +19529,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>90</v>
@@ -19532,7 +19541,7 @@
         <v>79</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>79</v>
@@ -19544,27 +19553,27 @@
         <v>79</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR137" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19685,10 +19694,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19714,10 +19723,10 @@
         <v>135</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>181</v>
@@ -19811,14 +19820,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19840,10 +19849,10 @@
         <v>135</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>181</v>
@@ -19898,7 +19907,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19939,10 +19948,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19968,13 +19977,13 @@
         <v>208</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20000,13 +20009,13 @@
         <v>79</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
@@ -20024,7 +20033,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20051,7 +20060,7 @@
         <v>79</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>153</v>
@@ -20060,15 +20069,15 @@
         <v>79</v>
       </c>
       <c r="AR141" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20189,10 +20198,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20218,10 +20227,10 @@
         <v>135</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>181</v>
@@ -20315,10 +20324,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20344,16 +20353,16 @@
         <v>167</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -20402,7 +20411,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20429,7 +20438,7 @@
         <v>79</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP144" t="s" s="2">
         <v>79</v>
@@ -20438,15 +20447,15 @@
         <v>79</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20567,10 +20576,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20596,10 +20605,10 @@
         <v>135</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>181</v>
@@ -20693,10 +20702,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20722,16 +20731,16 @@
         <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20780,7 +20789,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20807,7 +20816,7 @@
         <v>79</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>79</v>
@@ -20816,15 +20825,15 @@
         <v>79</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20850,13 +20859,13 @@
         <v>149</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20906,7 +20915,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20933,7 +20942,7 @@
         <v>79</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP148" t="s" s="2">
         <v>79</v>
@@ -20942,15 +20951,15 @@
         <v>79</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20976,14 +20985,14 @@
         <v>110</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20993,7 +21002,7 @@
         <v>79</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>79</v>
@@ -21032,7 +21041,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21047,7 +21056,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -21059,7 +21068,7 @@
         <v>79</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>79</v>
@@ -21068,15 +21077,15 @@
         <v>79</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21102,14 +21111,14 @@
         <v>149</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>79</v>
@@ -21158,7 +21167,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21185,7 +21194,7 @@
         <v>79</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>79</v>
@@ -21194,15 +21203,15 @@
         <v>79</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21225,19 +21234,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>79</v>
@@ -21286,7 +21295,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21313,7 +21322,7 @@
         <v>79</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>79</v>
@@ -21322,15 +21331,15 @@
         <v>79</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21356,16 +21365,16 @@
         <v>149</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -21414,7 +21423,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21441,7 +21450,7 @@
         <v>79</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>79</v>
@@ -21450,15 +21459,15 @@
         <v>79</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21481,13 +21490,13 @@
         <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21538,7 +21547,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21553,10 +21562,10 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>79</v>
@@ -21565,24 +21574,24 @@
         <v>79</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AR153" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21608,10 +21617,10 @@
         <v>110</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -21641,28 +21650,28 @@
         <v>170</v>
       </c>
       <c r="Y154" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF154" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21689,10 +21698,10 @@
         <v>79</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>79</v>
@@ -21703,10 +21712,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21732,10 +21741,10 @@
         <v>110</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21747,7 +21756,7 @@
         <v>79</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>79</v>
@@ -21765,28 +21774,28 @@
         <v>170</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF155" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>90</v>
@@ -21801,7 +21810,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>79</v>
@@ -21813,24 +21822,24 @@
         <v>79</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21853,13 +21862,13 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21910,7 +21919,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21951,10 +21960,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21977,16 +21986,16 @@
         <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -22036,7 +22045,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -22063,7 +22072,7 @@
         <v>434</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AP157" t="s" s="2">
         <v>79</v>
@@ -22072,7 +22081,7 @@
         <v>79</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -646,7 +646,7 @@
     <t>Appt.WaitList.PatientIEN</t>
   </si>
   <si>
-    <t>Appointment.NoShow,Appointment.AppointmentExtension.PatientStatus,Appointment.AppointmentExtension.ServiceStatus</t>
+    <t>Appointment.NoShow,Appointment.Extension[AppointmentExtension].PatientStatus,Appointment.Extension[AppointmentExtension].ServiceStatus</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -686,7 +686,7 @@
     <t>Appt.Appointment.CancellationReasonIEN</t>
   </si>
   <si>
-    <t>Appointment.AppointmentExtension.CancelReason</t>
+    <t>Appointment.Extension[AppointmentExtension].CancelReason</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -1388,7 +1388,7 @@
 Outpat.Visit.COProcessCompleteDateTime,Outpat.Workload.COProcessCompleteDateTime</t>
   </si>
   <si>
-    <t>Appointment.CareProvider,Appointment.EncounterNumber,Appointment.AppointmentExtension.AssociatedEncounterNumber</t>
+    <t>Appointment.CareProvider,Appointment.EncounterNumber,Appointment.Extension[AppointmentExtension].AssociatedEncounterNumber</t>
   </si>
   <si>
     <t>.effectiveTime.high</t>
@@ -1422,7 +1422,7 @@
     <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
   </si>
   <si>
-    <t>Appointment.AppointmentExtension.Length</t>
+    <t>Appointment.Extension[AppointmentExtension].Length</t>
   </si>
   <si>
     <t>.activityTime[@xsi:type = ('SXPR_TS', 'PIVL_TS')].width</t>
@@ -2356,7 +2356,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="205.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="116.4140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="135.7890625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="110.08203125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="155.20703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file APPOINTMENT (2.98) to Appointment</t>
+    <t>This StructureDefinition contains the maps for VistA file APPOINTMENT (2.98) to Appointment.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1905,61 +1905,61 @@
     <t>Appointment.participant:va-patient.period</t>
   </si>
   <si>
-    <t>Appointment.participant:va-appt-clinic</t>
-  </si>
-  <si>
-    <t>va-appt-clinic</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.modifierExtension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.code</t>
+    <t>Appointment.participant:va-apptclinic</t>
+  </si>
+  <si>
+    <t>va-apptclinic</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.modifierExtension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.code</t>
   </si>
   <si>
     <t>754-1: fixed value = #PART</t>
   </si>
   <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.actor</t>
+    <t>Appointment.participant:va-apptclinic.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.actor</t>
   </si>
   <si>
     <t>754: reference from SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
@@ -1968,10 +1968,10 @@
     <t>Appt.WaitList.AppointmentLocationIEN</t>
   </si>
   <si>
-    <t>Appointment.participant:va-appt-clinic.required</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-appt-clinic.status</t>
+    <t>Appointment.participant:va-apptclinic.required</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.status</t>
   </si>
   <si>
     <t>tentative</t>
@@ -1980,7 +1980,7 @@
     <t>754-2: fixed value = #tentative</t>
   </si>
   <si>
-    <t>Appointment.participant:va-appt-clinic.period</t>
+    <t>Appointment.participant:va-apptclinic.period</t>
   </si>
   <si>
     <t>Appointment.requestedPeriod</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,10 +556,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-2033:2.98-9.5 &gt; 409.1-.01: if SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}a-11-2034:2.98-9.5 &gt; 409.1-.01: if Not SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
-  </si>
-  <si>
-    <t>2034: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01) case Not SERVICE CONNECTED</t>
+a-11-2033:If (2.98-9.5 &gt; 409.1-.01) is SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}a-11-2034:If (2.98-9.5 &gt; 409.1-.01) is Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
+  </si>
+  <si>
+    <t>2034: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01) if Not SERVICE CONNECTED</t>
   </si>
   <si>
     <t>Appt.Appointment.AppointmentTypeIEN
@@ -637,10 +637,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-732:2.98-3: if I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then #booked {null}a-11-733:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then #arrived {null}a-11-734:2.98-3: if I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then #fulfilled {null}a-11-748:409.3-.01: if not null then #waitlist {null}</t>
-  </si>
-  <si>
-    <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) case not null</t>
+a-11-732:If (2.98-3) is I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #booked {null}a-11-733:If (2.98-3) is I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #arrived {null}a-11-734:If (2.98-3) is I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then fixed value #fulfilled {null}a-11-748:If (409.3-.01) is not null then fixed value #waitlist {null}</t>
+  </si>
+  <si>
+    <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) if not null</t>
   </si>
   <si>
     <t>Appt.WaitList.PatientIEN</t>
@@ -852,7 +852,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>749: source value from null (409.3-13.4)</t>
+    <t>749: source value based on null (409.3-13.4)</t>
   </si>
   <si>
     <t>Appt.WaitList.AppointmentPrimaryStopCodeIEN</t>
@@ -1018,7 +1018,7 @@
     <t>Appointment.appointmentType.text</t>
   </si>
   <si>
-    <t>740: source value from APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01)</t>
+    <t>740: source value based on APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01)</t>
   </si>
   <si>
     <t>Appointment.reasonCode</t>
@@ -1109,7 +1109,7 @@
     <t>The brief description of the appointment as would be shown on a subject line in a meeting request, or appointment list. Detailed or expanded information should be put in the comment field.</t>
   </si>
   <si>
-    <t>1791: source value from APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - DESCRIPTION (2.98-9.5 &gt; 409.1-10)</t>
+    <t>1791: source value based on APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - DESCRIPTION (2.98-9.5 &gt; 409.1-10)</t>
   </si>
   <si>
     <t>Appt.Appointment.AppointmentTypeIEN</t>
@@ -1162,7 +1162,7 @@
     <t>Date/Time that the appointment is to take place.</t>
   </si>
   <si>
-    <t>750: source value from SD WAIT LIST - DESIRED DATE OF APPOINTMENT (409.3-22)</t>
+    <t>750: source value based on SD WAIT LIST - DESIRED DATE OF APPOINTMENT (409.3-22)</t>
   </si>
   <si>
     <t>Appt.WaitList.AppointmentDesiredDate</t>
@@ -1192,7 +1192,7 @@
     <t>Date/Time that the appointment is to conclude.</t>
   </si>
   <si>
-    <t>1612: source value from APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (2.98-21 &gt; 409.68-.07)</t>
+    <t>1612: source value based on APPOINTMENT - OUTPATIENT ENCOUNTER &gt; OUTPATIENT ENCOUNTER - CHECK OUT PROCESS COMPLETION (2.98-21 &gt; 409.68-.07)</t>
   </si>
   <si>
     <t>Appt.Appointment.VisitIEN
@@ -1227,7 +1227,7 @@
     <t>Number of minutes that the appointment is to take. This can be less than the duration between the start and end times.  For example, where the actual time of appointment is only an estimate or if a 30 minute appointment is being requested, but any time would work.  Also, if there is, for example, a planned 15 minute break in the middle of a long appointment, the duration may be 15 minutes less than the difference between the start and end.</t>
   </si>
   <si>
-    <t>744: source value from PATIENT - LENGTH OF APP'T (44.003-1)</t>
+    <t>744: source value based on PATIENT - LENGTH OF APP'T (44.003-1)</t>
   </si>
   <si>
     <t>Appt.Appointment.LengthOfAppointment,Appt.AppointmentMultiple.LengthOfAppointment</t>
@@ -1274,7 +1274,7 @@
     <t>This property is required for many use cases where the age of an appointment is considered in processing workflows for scheduling and billing of appointments.</t>
   </si>
   <si>
-    <t>751: source value from SD WAIT LIST - ORIGINATING DATE (409.3-1)</t>
+    <t>751: source value based on SD WAIT LIST - ORIGINATING DATE (409.3-1)</t>
   </si>
   <si>
     <t>Appt.WaitList.OriginatingDate</t>
@@ -1306,7 +1306,7 @@
 Where this is a planned appointment and the start/end dates are not set then this field can be used to provide additional guidance on the details of the appointment request, including any restrictions on when to book it.</t>
   </si>
   <si>
-    <t>752: source value from SD WAIT LIST - COMMENTS (409.3-25)</t>
+    <t>752: source value based on SD WAIT LIST - COMMENTS (409.3-25)</t>
   </si>
   <si>
     <t>Appt.WaitList.WaitListComments</t>
@@ -1452,7 +1452,7 @@
     <t>A Person, Location/HealthcareService or Device that is participating in the appointment.</t>
   </si>
   <si>
-    <t>2038: reference from APPOINTMENT - CLINIC (2.98-.01)</t>
+    <t>2038: reference based on APPOINTMENT - CLINIC (2.98-.01)</t>
   </si>
   <si>
     <t>Appt.Appointment.LocationIEN</t>
@@ -1630,7 +1630,7 @@
     <t>Appointment.participant:va-clinic.actor</t>
   </si>
   <si>
-    <t>746: reference from APPOINTMENT - CLINIC (2.98-.01)</t>
+    <t>746: reference based on APPOINTMENT - CLINIC (2.98-.01)</t>
   </si>
   <si>
     <t>Appointment.participant:va-clinic.required</t>
@@ -1705,7 +1705,7 @@
     <t>Appointment.participant:va-patient.actor</t>
   </si>
   <si>
-    <t>1722: reference from PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
+    <t>1722: reference based on PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.required</t>
@@ -1777,7 +1777,7 @@
     <t>Appointment.participant:va-apptclinic.actor</t>
   </si>
   <si>
-    <t>754: reference from SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
+    <t>754: reference based on SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
   </si>
   <si>
     <t>Appt.WaitList.AppointmentLocationIEN</t>
@@ -2166,7 +2166,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="205.51953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="202.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="84.28125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="135.7890625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="34.3125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4844" uniqueCount="583">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -633,6 +633,9 @@
 This element is labeled as a modifier because the status contains the code entered-in-error that mark the Appointment as not currently valid.</t>
   </si>
   <si>
+    <t>see mapping [VF_AppointmentStatus](ConceptMap-VF-AppointmentStatus.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/AppointmentStatus</t>
   </si>
   <si>
@@ -677,6 +680,9 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
+    <t>see mapping [VF_AppointmentCancellationReason](ConceptMap-VF-AppointmentCancellationReason.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/AppointmentCancellationReason</t>
   </si>
   <si>
@@ -852,7 +858,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>749: source value based on null (409.3-13.4)</t>
+    <t>749: source value based on SD WAIT LIST - APPT STOP CODE (409.3-13.4)</t>
   </si>
   <si>
     <t>Appt.WaitList.AppointmentPrimaryStopCodeIEN</t>
@@ -2155,7 +2161,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="50.4921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="99.4375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.94140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -4249,9 +4255,11 @@
       <c r="X17" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Y17" s="2"/>
+      <c r="Y17" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -4281,39 +4289,39 @@
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4336,13 +4344,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4371,9 +4379,11 @@
       <c r="X18" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Y18" s="2"/>
+      <c r="Y18" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4391,7 +4401,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4406,13 +4416,13 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4432,10 +4442,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4458,13 +4468,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4491,17 +4501,17 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
@@ -4511,7 +4521,7 @@
         <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4538,10 +4548,10 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>79</v>
@@ -4552,13 +4562,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
@@ -4580,13 +4590,13 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4613,11 +4623,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4635,7 +4645,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4662,10 +4672,10 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>79</v>
@@ -4676,10 +4686,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4800,10 +4810,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4829,10 +4839,10 @@
         <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>181</v>
@@ -4926,10 +4936,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4955,16 +4965,16 @@
         <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -5013,7 +5023,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5040,7 +5050,7 @@
         <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -5049,15 +5059,15 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5178,10 +5188,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5207,10 +5217,10 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>181</v>
@@ -5304,10 +5314,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5333,16 +5343,16 @@
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5352,7 +5362,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5391,7 +5401,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5406,7 +5416,7 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>79</v>
@@ -5418,7 +5428,7 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5427,15 +5437,15 @@
         <v>79</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5461,13 +5471,13 @@
         <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5517,7 +5527,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5544,7 +5554,7 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5553,15 +5563,15 @@
         <v>79</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5587,14 +5597,14 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5643,7 +5653,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5658,10 +5668,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5670,7 +5680,7 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5679,15 +5689,15 @@
         <v>79</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5713,14 +5723,14 @@
         <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5769,7 +5779,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5796,7 +5806,7 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5805,15 +5815,15 @@
         <v>79</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5836,19 +5846,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5897,7 +5907,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5924,7 +5934,7 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5933,15 +5943,15 @@
         <v>79</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5967,16 +5977,16 @@
         <v>149</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -6025,7 +6035,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6052,7 +6062,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -6061,15 +6071,15 @@
         <v>79</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6092,16 +6102,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6127,11 +6137,11 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -6149,7 +6159,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6173,10 +6183,10 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -6190,10 +6200,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6216,13 +6226,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6253,7 +6263,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -6271,7 +6281,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6286,7 +6296,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -6298,13 +6308,13 @@
         <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>79</v>
@@ -6312,10 +6322,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6338,13 +6348,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6375,7 +6385,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -6393,7 +6403,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6420,24 +6430,24 @@
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6558,10 +6568,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6587,10 +6597,10 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>181</v>
@@ -6684,10 +6694,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6713,16 +6723,16 @@
         <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6771,7 +6781,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6798,7 +6808,7 @@
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6807,15 +6817,15 @@
         <v>79</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6841,16 +6851,16 @@
         <v>149</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6899,7 +6909,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6914,7 +6924,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>175</v>
@@ -6926,7 +6936,7 @@
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6935,15 +6945,15 @@
         <v>79</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6966,13 +6976,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7002,10 +7012,10 @@
         <v>114</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -7023,7 +7033,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7038,7 +7048,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -7047,10 +7057,10 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -7059,15 +7069,15 @@
         <v>79</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7090,13 +7100,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7147,7 +7157,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7162,7 +7172,7 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
@@ -7171,10 +7181,10 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -7188,10 +7198,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7214,16 +7224,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7273,7 +7283,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7297,27 +7307,27 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7343,10 +7353,10 @@
         <v>149</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7397,7 +7407,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7412,10 +7422,10 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>176</v>
@@ -7424,24 +7434,24 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7464,13 +7474,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7521,7 +7531,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7545,16 +7555,16 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>79</v>
@@ -7562,10 +7572,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7588,13 +7598,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7645,7 +7655,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7660,36 +7670,36 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7712,13 +7722,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7769,7 +7779,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7784,36 +7794,36 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7836,13 +7846,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7893,7 +7903,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7908,22 +7918,22 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>79</v>
@@ -7934,10 +7944,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7960,13 +7970,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8017,7 +8027,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8044,7 +8054,7 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8058,10 +8068,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8084,16 +8094,16 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8143,7 +8153,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8158,22 +8168,22 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>79</v>
@@ -8184,10 +8194,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8213,13 +8223,13 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8269,7 +8279,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8284,36 +8294,36 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8339,10 +8349,10 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8393,7 +8403,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8420,28 +8430,28 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8460,13 +8470,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8517,7 +8527,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8541,10 +8551,10 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -8558,10 +8568,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8584,13 +8594,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8629,7 +8639,7 @@
         <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8639,7 +8649,7 @@
         <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>90</v>
@@ -8651,7 +8661,7 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8663,27 +8673,27 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8804,10 +8814,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8833,10 +8843,10 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>181</v>
@@ -8930,14 +8940,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8959,10 +8969,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>181</v>
@@ -9017,7 +9027,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9058,10 +9068,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9084,16 +9094,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9119,13 +9129,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -9143,7 +9153,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9170,7 +9180,7 @@
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>153</v>
@@ -9179,15 +9189,15 @@
         <v>79</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9210,13 +9220,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9267,7 +9277,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9282,36 +9292,36 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9337,10 +9347,10 @@
         <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9370,10 +9380,10 @@
         <v>170</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -9391,7 +9401,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9418,10 +9428,10 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>79</v>
@@ -9432,10 +9442,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9461,10 +9471,10 @@
         <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9476,7 +9486,7 @@
         <v>79</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>79</v>
@@ -9494,10 +9504,10 @@
         <v>170</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9515,7 +9525,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>90</v>
@@ -9530,7 +9540,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>79</v>
@@ -9542,24 +9552,24 @@
         <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9582,13 +9592,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9639,7 +9649,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9680,13 +9690,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9708,13 +9718,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9765,7 +9775,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>90</v>
@@ -9777,7 +9787,7 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9789,27 +9799,27 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9930,10 +9940,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9959,10 +9969,10 @@
         <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>181</v>
@@ -10056,14 +10066,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10085,10 +10095,10 @@
         <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>181</v>
@@ -10143,7 +10153,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10184,10 +10194,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10210,16 +10220,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10245,13 +10255,13 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -10269,7 +10279,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10296,7 +10306,7 @@
         <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>153</v>
@@ -10305,15 +10315,15 @@
         <v>79</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10434,10 +10444,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10463,10 +10473,10 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>181</v>
@@ -10560,10 +10570,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10589,16 +10599,16 @@
         <v>167</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10647,7 +10657,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10674,7 +10684,7 @@
         <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -10683,15 +10693,15 @@
         <v>79</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10812,10 +10822,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10841,10 +10851,10 @@
         <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>181</v>
@@ -10938,10 +10948,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10967,16 +10977,16 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11025,7 +11035,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11052,7 +11062,7 @@
         <v>79</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>79</v>
@@ -11061,15 +11071,15 @@
         <v>79</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11095,13 +11105,13 @@
         <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11151,7 +11161,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11178,7 +11188,7 @@
         <v>79</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>79</v>
@@ -11187,15 +11197,15 @@
         <v>79</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11221,14 +11231,14 @@
         <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -11238,7 +11248,7 @@
         <v>79</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>79</v>
@@ -11277,7 +11287,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11292,7 +11302,7 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>79</v>
@@ -11304,7 +11314,7 @@
         <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>79</v>
@@ -11313,15 +11323,15 @@
         <v>79</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11347,14 +11357,14 @@
         <v>149</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11403,7 +11413,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11430,7 +11440,7 @@
         <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>79</v>
@@ -11439,15 +11449,15 @@
         <v>79</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11470,19 +11480,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11531,7 +11541,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11558,7 +11568,7 @@
         <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11567,15 +11577,15 @@
         <v>79</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11601,16 +11611,16 @@
         <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11659,7 +11669,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11686,7 +11696,7 @@
         <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11695,15 +11705,15 @@
         <v>79</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11726,13 +11736,13 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11783,7 +11793,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11798,36 +11808,36 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11853,10 +11863,10 @@
         <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11886,10 +11896,10 @@
         <v>170</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -11907,7 +11917,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11934,10 +11944,10 @@
         <v>79</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>79</v>
@@ -11948,10 +11958,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11977,10 +11987,10 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11992,7 +12002,7 @@
         <v>79</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>79</v>
@@ -12010,10 +12020,10 @@
         <v>170</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -12031,7 +12041,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>90</v>
@@ -12046,7 +12056,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>79</v>
@@ -12058,24 +12068,24 @@
         <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12098,13 +12108,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12155,7 +12165,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12196,13 +12206,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>79</v>
@@ -12224,13 +12234,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12281,7 +12291,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>90</v>
@@ -12293,7 +12303,7 @@
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -12305,27 +12315,27 @@
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12446,10 +12456,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12475,10 +12485,10 @@
         <v>135</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>181</v>
@@ -12572,14 +12582,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12601,10 +12611,10 @@
         <v>135</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>181</v>
@@ -12659,7 +12669,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12700,10 +12710,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12726,16 +12736,16 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12761,13 +12771,13 @@
         <v>79</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12785,7 +12795,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12812,7 +12822,7 @@
         <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>153</v>
@@ -12821,15 +12831,15 @@
         <v>79</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12950,10 +12960,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12979,10 +12989,10 @@
         <v>135</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>181</v>
@@ -13076,10 +13086,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13105,16 +13115,16 @@
         <v>167</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13163,7 +13173,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13190,7 +13200,7 @@
         <v>79</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>79</v>
@@ -13199,15 +13209,15 @@
         <v>79</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13328,10 +13338,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13357,10 +13367,10 @@
         <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>181</v>
@@ -13454,10 +13464,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13483,16 +13493,16 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13541,7 +13551,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13568,7 +13578,7 @@
         <v>79</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>79</v>
@@ -13577,15 +13587,15 @@
         <v>79</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13611,13 +13621,13 @@
         <v>149</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13667,7 +13677,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13694,7 +13704,7 @@
         <v>79</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>79</v>
@@ -13703,15 +13713,15 @@
         <v>79</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13737,14 +13747,14 @@
         <v>110</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13754,7 +13764,7 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>79</v>
@@ -13793,7 +13803,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13808,7 +13818,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>79</v>
@@ -13820,7 +13830,7 @@
         <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -13829,15 +13839,15 @@
         <v>79</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13863,14 +13873,14 @@
         <v>149</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13919,7 +13929,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13946,7 +13956,7 @@
         <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -13955,15 +13965,15 @@
         <v>79</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13986,19 +13996,19 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -14047,7 +14057,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14074,7 +14084,7 @@
         <v>79</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14083,15 +14093,15 @@
         <v>79</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14117,16 +14127,16 @@
         <v>149</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
@@ -14175,7 +14185,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14202,7 +14212,7 @@
         <v>79</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14211,15 +14221,15 @@
         <v>79</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14242,13 +14252,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14299,7 +14309,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14314,7 +14324,7 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>79</v>
@@ -14326,24 +14336,24 @@
         <v>79</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14369,10 +14379,10 @@
         <v>110</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14402,10 +14412,10 @@
         <v>170</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>79</v>
@@ -14423,7 +14433,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14450,10 +14460,10 @@
         <v>79</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>79</v>
@@ -14464,10 +14474,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14493,10 +14503,10 @@
         <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14508,7 +14518,7 @@
         <v>79</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>79</v>
@@ -14526,10 +14536,10 @@
         <v>170</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -14547,7 +14557,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>90</v>
@@ -14562,7 +14572,7 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
@@ -14574,24 +14584,24 @@
         <v>79</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14614,13 +14624,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14671,7 +14681,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14712,13 +14722,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>79</v>
@@ -14740,13 +14750,13 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14797,7 +14807,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>90</v>
@@ -14809,7 +14819,7 @@
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
@@ -14821,27 +14831,27 @@
         <v>79</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14962,10 +14972,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14991,10 +15001,10 @@
         <v>135</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>181</v>
@@ -15088,14 +15098,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15117,10 +15127,10 @@
         <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>181</v>
@@ -15175,7 +15185,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15216,10 +15226,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15242,16 +15252,16 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15277,13 +15287,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -15301,7 +15311,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15328,7 +15338,7 @@
         <v>79</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>153</v>
@@ -15337,15 +15347,15 @@
         <v>79</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15466,10 +15476,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15495,10 +15505,10 @@
         <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>181</v>
@@ -15592,10 +15602,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15621,16 +15631,16 @@
         <v>167</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15679,7 +15689,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15706,7 +15716,7 @@
         <v>79</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>79</v>
@@ -15715,15 +15725,15 @@
         <v>79</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15844,10 +15854,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15873,10 +15883,10 @@
         <v>135</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>181</v>
@@ -15970,10 +15980,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15999,16 +16009,16 @@
         <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -16057,7 +16067,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16084,7 +16094,7 @@
         <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>79</v>
@@ -16093,15 +16103,15 @@
         <v>79</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16127,13 +16137,13 @@
         <v>149</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16183,7 +16193,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16210,7 +16220,7 @@
         <v>79</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>79</v>
@@ -16219,15 +16229,15 @@
         <v>79</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16253,14 +16263,14 @@
         <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>79</v>
@@ -16270,7 +16280,7 @@
         <v>79</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>79</v>
@@ -16309,7 +16319,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16324,7 +16334,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>79</v>
@@ -16336,7 +16346,7 @@
         <v>79</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>79</v>
@@ -16345,15 +16355,15 @@
         <v>79</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16379,14 +16389,14 @@
         <v>149</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -16435,7 +16445,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16462,7 +16472,7 @@
         <v>79</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>79</v>
@@ -16471,15 +16481,15 @@
         <v>79</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16502,19 +16512,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -16563,7 +16573,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16590,7 +16600,7 @@
         <v>79</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>79</v>
@@ -16599,15 +16609,15 @@
         <v>79</v>
       </c>
       <c r="AR115" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16633,16 +16643,16 @@
         <v>149</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16691,7 +16701,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16718,7 +16728,7 @@
         <v>79</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>79</v>
@@ -16727,15 +16737,15 @@
         <v>79</v>
       </c>
       <c r="AR116" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16758,13 +16768,13 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16815,7 +16825,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16830,10 +16840,10 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>79</v>
@@ -16842,24 +16852,24 @@
         <v>79</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16885,10 +16895,10 @@
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16918,10 +16928,10 @@
         <v>170</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -16939,7 +16949,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16966,10 +16976,10 @@
         <v>79</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>79</v>
@@ -16980,10 +16990,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17009,10 +17019,10 @@
         <v>110</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17024,7 +17034,7 @@
         <v>79</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>79</v>
@@ -17042,10 +17052,10 @@
         <v>170</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>79</v>
@@ -17063,7 +17073,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>90</v>
@@ -17078,7 +17088,7 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>79</v>
@@ -17090,24 +17100,24 @@
         <v>79</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17130,13 +17140,13 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17187,7 +17197,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17228,10 +17238,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17254,16 +17264,16 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17313,7 +17323,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17337,10 +17347,10 @@
         <v>79</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>79</v>
@@ -17349,7 +17359,7 @@
         <v>79</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,7 +556,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-2033:If (2.98-9.5 &gt; 409.1-.01) is SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}a-11-2034:If (2.98-9.5 &gt; 409.1-.01) is Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
+a-11-2033:If (2.98-9.5 &gt; 409.1-.01) is SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {true}a-11-2034:If (2.98-9.5 &gt; 409.1-.01) is Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {true}</t>
   </si>
   <si>
     <t>2034: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when APPOINTMENT - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (2.98-9.5 &gt; 409.1-.01) if Not SERVICE CONNECTED</t>
@@ -640,7 +640,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-732:If (2.98-3) is I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #booked {null}a-11-733:If (2.98-3) is I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #arrived {null}a-11-734:If (2.98-3) is I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then fixed value #fulfilled {null}a-11-748:If (409.3-.01) is not null then fixed value #waitlist {null}</t>
+a-11-732:If (2.98-3) is I, NT, Null; Null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #booked {true}a-11-733:If (2.98-3) is I, NT, Null; Non-null check-in date (44.003-309), null check-out date (44.003-303) then fixed value #arrived {true}a-11-734:If (2.98-3) is I, NT, Null; Non-null check-in date (44.003-309), non-null check-out date (44.003-303) then fixed value #fulfilled {true}a-11-748:If (409.3-.01) is not null then fixed value #waitlist {true}</t>
   </si>
   <si>
     <t>748: fixed value = #waitlist when SD WAIT LIST - PATIENT (409.3-.01) if not null</t>
@@ -1448,17 +1448,184 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device|HealthcareService|Location)
+</t>
+  </si>
+  <si>
+    <t>Person, Location/HealthcareService or Device</t>
+  </si>
+  <si>
+    <t>A Person, Location/HealthcareService or Device that is participating in the appointment.</t>
+  </si>
+  <si>
+    <t>performer.person | reusableDevice.manufacturedDevice | subject.patient | location.serviceDeliveryLocation</t>
+  </si>
+  <si>
+    <t>ATTENDEE: (Need to provide the common name CN and also the MAILTO properties from the practitioner resource) where the participant type is not "information-only"</t>
+  </si>
+  <si>
+    <t>FiveWs.who</t>
+  </si>
+  <si>
+    <t>PID-3-Patient ID List | AIL-3 | AIG-3 | AIP-3</t>
+  </si>
+  <si>
+    <t>Appointment.participant.required</t>
+  </si>
+  <si>
+    <t>required | optional | information-only</t>
+  </si>
+  <si>
+    <t>Whether this participant is required to be present at the meeting. This covers a use-case where two doctors need to meet to discuss the results for a specific patient, and the patient is not required to be present.</t>
+  </si>
+  <si>
+    <t>Is the Participant required to attend the appointment.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/participantrequired|4.0.1</t>
+  </si>
+  <si>
+    <t>(performer | reusableDevice | subject | location).@performInd</t>
+  </si>
+  <si>
+    <t>ROLE=REQ-PARTICIPANT (roleparam)</t>
+  </si>
+  <si>
+    <t>Appointment.participant.status</t>
+  </si>
+  <si>
+    <t>accepted | declined | tentative | needs-action</t>
+  </si>
+  <si>
+    <t>Participation status of the actor.</t>
+  </si>
+  <si>
+    <t>The Participation status of an appointment.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/participationstatus|4.0.1</t>
+  </si>
+  <si>
+    <t>(performer | reusableDevice | subject | location).statusCode</t>
+  </si>
+  <si>
+    <t>ATTENDEE;CN="John Doe";RSVP=TRUE:mailto:john@doe.com (rsvpparam | partstatparam)</t>
+  </si>
+  <si>
+    <t>AIP-12, AIG-14</t>
+  </si>
+  <si>
+    <t>Appointment.participant.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Participation period of the actor</t>
+  </si>
+  <si>
+    <t>Participation period of the actor.</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic</t>
+  </si>
+  <si>
+    <t>va-clinic</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.modifierExtension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.code</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.code</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>746-1: fixed value = #PART</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.actor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
-    <t>Person, Location/HealthcareService or Device</t>
-  </si>
-  <si>
-    <t>A Person, Location/HealthcareService or Device that is participating in the appointment.</t>
-  </si>
-  <si>
-    <t>2038: reference based on APPOINTMENT - CLINIC (2.98-.01)</t>
+    <t>746: reference based on APPOINTMENT - CLINIC (2.98-.01)</t>
   </si>
   <si>
     <t>Appt.Appointment.LocationIEN</t>
@@ -1467,332 +1634,167 @@
     <t>Appointment.CareProvider,Appointment.EnteredAt,Appointment.Location,Appointment.PlacerApptId,Appointment.Type</t>
   </si>
   <si>
-    <t>performer.person | reusableDevice.manufacturedDevice | subject.patient | location.serviceDeliveryLocation</t>
-  </si>
-  <si>
-    <t>ATTENDEE: (Need to provide the common name CN and also the MAILTO properties from the practitioner resource) where the participant type is not "information-only"</t>
-  </si>
-  <si>
-    <t>FiveWs.who</t>
-  </si>
-  <si>
-    <t>PID-3-Patient ID List | AIL-3 | AIG-3 | AIP-3</t>
-  </si>
-  <si>
-    <t>Appointment.participant.required</t>
-  </si>
-  <si>
-    <t>required | optional | information-only</t>
-  </si>
-  <si>
-    <t>Whether this participant is required to be present at the meeting. This covers a use-case where two doctors need to meet to discuss the results for a specific patient, and the patient is not required to be present.</t>
-  </si>
-  <si>
-    <t>Is the Participant required to attend the appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/participantrequired|4.0.1</t>
-  </si>
-  <si>
-    <t>(performer | reusableDevice | subject | location).@performInd</t>
-  </si>
-  <si>
-    <t>ROLE=REQ-PARTICIPANT (roleparam)</t>
-  </si>
-  <si>
-    <t>Appointment.participant.status</t>
-  </si>
-  <si>
-    <t>accepted | declined | tentative | needs-action</t>
-  </si>
-  <si>
-    <t>Participation status of the actor.</t>
+    <t>Appointment.participant:va-clinic.required</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.status</t>
+  </si>
+  <si>
+    <t>accepted</t>
+  </si>
+  <si>
+    <t>746-2: fixed value = #accepted</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-clinic.period</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient</t>
+  </si>
+  <si>
+    <t>va-patient</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.code</t>
+  </si>
+  <si>
+    <t>1722-1: fixed value = #PART</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.actor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+</t>
+  </si>
+  <si>
+    <t>1722: reference based on PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.required</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.status</t>
+  </si>
+  <si>
+    <t>1722-2: fixed value = #accepted</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-patient.period</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic</t>
+  </si>
+  <si>
+    <t>va-apptclinic</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.modifierExtension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.system</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.version</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.code</t>
+  </si>
+  <si>
+    <t>754-1: fixed value = #PART</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.display</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.type.text</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.actor</t>
+  </si>
+  <si>
+    <t>754: reference based on SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
+  </si>
+  <si>
+    <t>Appt.WaitList.AppointmentLocationIEN</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.required</t>
+  </si>
+  <si>
+    <t>Appointment.participant:va-apptclinic.status</t>
   </si>
   <si>
     <t>tentative</t>
-  </si>
-  <si>
-    <t>The Participation status of an appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/participationstatus|4.0.1</t>
-  </si>
-  <si>
-    <t>2038-1: fixed value = #tentative</t>
-  </si>
-  <si>
-    <t>(performer | reusableDevice | subject | location).statusCode</t>
-  </si>
-  <si>
-    <t>ATTENDEE;CN="John Doe";RSVP=TRUE:mailto:john@doe.com (rsvpparam | partstatparam)</t>
-  </si>
-  <si>
-    <t>AIP-12, AIG-14</t>
-  </si>
-  <si>
-    <t>Appointment.participant.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Participation period of the actor</t>
-  </si>
-  <si>
-    <t>Participation period of the actor.</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic</t>
-  </si>
-  <si>
-    <t>va-clinic</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.modifierExtension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.code</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.code</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>746-1: fixed value = #PART</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.actor</t>
-  </si>
-  <si>
-    <t>746: reference based on APPOINTMENT - CLINIC (2.98-.01)</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.required</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.status</t>
-  </si>
-  <si>
-    <t>accepted</t>
-  </si>
-  <si>
-    <t>746-2: fixed value = #accepted</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-clinic.period</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient</t>
-  </si>
-  <si>
-    <t>va-patient</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.code</t>
-  </si>
-  <si>
-    <t>1722-1: fixed value = #PART</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.actor</t>
-  </si>
-  <si>
-    <t>1722: reference based on PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.required</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.status</t>
-  </si>
-  <si>
-    <t>1722-2: fixed value = #accepted</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-patient.period</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic</t>
-  </si>
-  <si>
-    <t>va-apptclinic</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.modifierExtension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.id</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.system</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.version</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.code</t>
-  </si>
-  <si>
-    <t>754-1: fixed value = #PART</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.display</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.type.text</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.actor</t>
-  </si>
-  <si>
-    <t>754: reference based on SD WAIT LIST - APPT CLINIC (409.3-13.2)</t>
-  </si>
-  <si>
-    <t>Appt.WaitList.AppointmentLocationIEN</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.required</t>
-  </si>
-  <si>
-    <t>Appointment.participant:va-apptclinic.status</t>
   </si>
   <si>
     <t>754-2: fixed value = #tentative</t>
@@ -2147,7 +2149,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.71875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.39453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -9211,7 +9213,7 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
@@ -9292,36 +9294,36 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AQ57" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AR57" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9347,10 +9349,10 @@
         <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9380,10 +9382,10 @@
         <v>170</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -9401,7 +9403,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9428,10 +9430,10 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>79</v>
@@ -9442,10 +9444,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9459,7 +9461,7 @@
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>79</v>
@@ -9471,10 +9473,10 @@
         <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9486,7 +9488,7 @@
         <v>79</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>480</v>
+        <v>79</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>79</v>
@@ -9504,10 +9506,10 @@
         <v>170</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9525,7 +9527,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>90</v>
@@ -9540,7 +9542,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>483</v>
+        <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>79</v>
@@ -9552,24 +9554,24 @@
         <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9592,13 +9594,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9649,7 +9651,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9690,13 +9692,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>434</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9816,7 +9818,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>443</v>
@@ -9940,7 +9942,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>444</v>
@@ -10066,7 +10068,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>445</v>
@@ -10194,7 +10196,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>450</v>
@@ -10320,10 +10322,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10444,10 +10446,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10570,10 +10572,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10698,10 +10700,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10822,10 +10824,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10948,10 +10950,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11076,10 +11078,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11202,10 +11204,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11248,7 +11250,7 @@
         <v>79</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>79</v>
@@ -11302,7 +11304,7 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>79</v>
@@ -11328,10 +11330,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11454,10 +11456,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11582,10 +11584,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11710,7 +11712,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>459</v>
@@ -11736,7 +11738,7 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>460</v>
+        <v>517</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>461</v>
@@ -11808,36 +11810,36 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AQ77" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AR77" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11863,10 +11865,10 @@
         <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11896,10 +11898,10 @@
         <v>170</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -11917,7 +11919,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11944,10 +11946,10 @@
         <v>79</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>79</v>
@@ -11958,10 +11960,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11987,10 +11989,10 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12002,7 +12004,7 @@
         <v>79</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>79</v>
@@ -12020,10 +12022,10 @@
         <v>170</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -12041,7 +12043,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>90</v>
@@ -12056,7 +12058,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>79</v>
@@ -12068,24 +12070,24 @@
         <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12108,13 +12110,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12165,7 +12167,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12206,13 +12208,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>434</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>79</v>
@@ -12332,7 +12334,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>443</v>
@@ -12456,7 +12458,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>444</v>
@@ -12582,7 +12584,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>445</v>
@@ -12710,7 +12712,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>450</v>
@@ -12836,10 +12838,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12960,10 +12962,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13086,10 +13088,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13214,10 +13216,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13338,10 +13340,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13464,10 +13466,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13592,10 +13594,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13718,10 +13720,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13764,7 +13766,7 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>79</v>
@@ -13818,7 +13820,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>79</v>
@@ -13844,10 +13846,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13970,10 +13972,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14098,10 +14100,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14226,7 +14228,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>459</v>
@@ -14252,7 +14254,7 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>460</v>
+        <v>545</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>461</v>
@@ -14324,7 +14326,7 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>79</v>
@@ -14336,24 +14338,24 @@
         <v>79</v>
       </c>
       <c r="AO97" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AR97" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14379,10 +14381,10 @@
         <v>110</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14412,10 +14414,10 @@
         <v>170</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>79</v>
@@ -14433,7 +14435,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14460,10 +14462,10 @@
         <v>79</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>79</v>
@@ -14474,10 +14476,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14503,10 +14505,10 @@
         <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14518,7 +14520,7 @@
         <v>79</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>79</v>
@@ -14536,10 +14538,10 @@
         <v>170</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -14557,7 +14559,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>90</v>
@@ -14572,7 +14574,7 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
@@ -14584,24 +14586,24 @@
         <v>79</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14624,13 +14626,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14681,7 +14683,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14722,13 +14724,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>434</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>79</v>
@@ -14848,7 +14850,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>443</v>
@@ -14972,7 +14974,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>444</v>
@@ -15098,7 +15100,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>445</v>
@@ -15226,7 +15228,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>450</v>
@@ -15352,10 +15354,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15476,10 +15478,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15602,10 +15604,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15730,10 +15732,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15854,10 +15856,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15980,10 +15982,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16108,10 +16110,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16234,10 +16236,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16280,7 +16282,7 @@
         <v>79</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>79</v>
@@ -16334,7 +16336,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>79</v>
@@ -16360,10 +16362,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16486,10 +16488,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16614,10 +16616,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16742,7 +16744,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>459</v>
@@ -16768,7 +16770,7 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>460</v>
+        <v>517</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>461</v>
@@ -16840,11 +16842,11 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AL117" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AL117" t="s" s="2">
-        <v>572</v>
-      </c>
       <c r="AM117" t="s" s="2">
         <v>79</v>
       </c>
@@ -16852,24 +16854,24 @@
         <v>79</v>
       </c>
       <c r="AO117" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AQ117" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AR117" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AQ117" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AR117" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16895,10 +16897,10 @@
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16928,10 +16930,10 @@
         <v>170</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -16949,7 +16951,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16976,10 +16978,10 @@
         <v>79</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>79</v>
@@ -16990,10 +16992,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17019,10 +17021,10 @@
         <v>110</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17034,7 +17036,7 @@
         <v>79</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>480</v>
+        <v>574</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>79</v>
@@ -17052,10 +17054,10 @@
         <v>170</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>79</v>
@@ -17073,7 +17075,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>90</v>
@@ -17100,16 +17102,16 @@
         <v>79</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="120" hidden="true">
@@ -17117,7 +17119,7 @@
         <v>576</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17140,13 +17142,13 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17197,7 +17199,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17264,7 +17266,7 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>578</v>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4844" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4844" uniqueCount="586">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1691,7 +1691,11 @@
     <t>Appointment.participant:va-patient.type.coding.code</t>
   </si>
   <si>
-    <t>1722-1: fixed value = #PART</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+a-11-1722-1:If PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98) then fixed value #PART {true}</t>
+  </si>
+  <si>
+    <t>1722-1: fixed value = #PART if PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.type.coding.display</t>
@@ -1710,7 +1714,11 @@
 </t>
   </si>
   <si>
-    <t>1722: reference based on PATIENT - APPOINTMENT &gt; APPOINTMENT (2-1900 &gt; 2.98)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+a-11-1722:If PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98) then reference /Patient based on (2-) {true}</t>
+  </si>
+  <si>
+    <t>1722: reference based on PATIENT - (2-) if PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.required</t>
@@ -1719,7 +1727,11 @@
     <t>Appointment.participant:va-patient.status</t>
   </si>
   <si>
-    <t>1722-2: fixed value = #accepted</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+a-11-1722-2:If PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98) then fixed value #accepted {true}</t>
+  </si>
+  <si>
+    <t>1722-2: fixed value = #accepted if PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.period</t>
@@ -13766,7 +13778,7 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>508</v>
+        <v>79</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>79</v>
@@ -13817,10 +13829,10 @@
         <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>102</v>
+        <v>540</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>79</v>
@@ -13846,7 +13858,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>511</v>
@@ -13972,7 +13984,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>513</v>
@@ -14100,7 +14112,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>515</v>
@@ -14228,7 +14240,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>459</v>
@@ -14254,7 +14266,7 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>461</v>
@@ -14323,10 +14335,10 @@
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>547</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>79</v>
@@ -14352,7 +14364,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>467</v>
@@ -14476,7 +14488,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>474</v>
@@ -14520,7 +14532,7 @@
         <v>79</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>523</v>
+        <v>79</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>79</v>
@@ -14571,10 +14583,10 @@
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>551</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
@@ -14600,7 +14612,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>482</v>
@@ -14724,13 +14736,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>434</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>79</v>
@@ -14850,7 +14862,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>443</v>
@@ -14974,7 +14986,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>444</v>
@@ -15100,7 +15112,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>445</v>
@@ -15228,7 +15240,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>450</v>
@@ -15354,7 +15366,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>493</v>
@@ -15478,7 +15490,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>495</v>
@@ -15604,7 +15616,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>497</v>
@@ -15732,7 +15744,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>499</v>
@@ -15856,7 +15868,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>501</v>
@@ -15982,7 +15994,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>503</v>
@@ -16110,7 +16122,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>505</v>
@@ -16236,7 +16248,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>507</v>
@@ -16336,7 +16348,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>79</v>
@@ -16362,7 +16374,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>511</v>
@@ -16488,7 +16500,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>513</v>
@@ -16616,7 +16628,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>515</v>
@@ -16744,7 +16756,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>459</v>
@@ -16842,10 +16854,10 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>79</v>
@@ -16868,7 +16880,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>467</v>
@@ -16992,7 +17004,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>474</v>
@@ -17036,7 +17048,7 @@
         <v>79</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>79</v>
@@ -17090,7 +17102,7 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>79</v>
@@ -17116,7 +17128,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>482</v>
@@ -17240,10 +17252,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17269,13 +17281,13 @@
         <v>483</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17325,7 +17337,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17352,7 +17364,7 @@
         <v>374</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>79</v>
@@ -17361,7 +17373,7 @@
         <v>79</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Appointment.xlsx
+++ b/docs/StructureDefinition-Appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1692,10 +1692,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-1722-1:If PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98) then fixed value #PART {true}</t>
-  </si>
-  <si>
-    <t>1722-1: fixed value = #PART if PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98)</t>
+a-11-1722-1:If PATIENT – APPOINTMENT (2-1900) = APPOINTMENT (2.98) then fixed value #PART {true}</t>
+  </si>
+  <si>
+    <t>1722-1: fixed value = #PART if PATIENT – APPOINTMENT (2-1900) = APPOINTMENT (2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.type.coding.display</t>
@@ -1715,10 +1715,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-1722:If PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98) then reference /Patient based on (2-) {true}</t>
-  </si>
-  <si>
-    <t>1722: reference based on PATIENT - (2-) if PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98)</t>
+a-11-1722:If PATIENT – APPOINTMENT (2-1900) = APPOINTMENT (2.98) then reference /Patient based on (2-) {true}</t>
+  </si>
+  <si>
+    <t>1722: reference based on PATIENT - (2-) if PATIENT – APPOINTMENT (2-1900) = APPOINTMENT (2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.required</t>
@@ -1728,10 +1728,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-a-11-1722-2:If PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98) then fixed value #accepted {true}</t>
-  </si>
-  <si>
-    <t>1722-2: fixed value = #accepted if PATIENT – APPOINTMENT (2-1900) == APPOINTMENT (2.98)</t>
+a-11-1722-2:If PATIENT – APPOINTMENT (2-1900) = APPOINTMENT (2.98) then fixed value #accepted {true}</t>
+  </si>
+  <si>
+    <t>1722-2: fixed value = #accepted if PATIENT – APPOINTMENT (2-1900) = APPOINTMENT (2.98)</t>
   </si>
   <si>
     <t>Appointment.participant:va-patient.period</t>
